--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="490">
   <si>
     <t xml:space="preserve">Tsuji — cost overview</t>
   </si>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Pricing: pushing the annual Pro plan, with Max as the upgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">Old prices are your first grid; new prices come from Assumptions (change them there).</t>
+    <t xml:space="preserve">Old prices are your first grid; full prices come from Assumptions (change them there); regional prices are at the bottom.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">Old price (€)</t>
   </si>
   <si>
-    <t xml:space="preserve">New price (€)</t>
+    <t xml:space="preserve">Full price, tier 1 (€)</t>
   </si>
   <si>
     <t xml:space="preserve">Per month (€)</t>
@@ -557,6 +557,81 @@
     <t xml:space="preserve">The numbers to re-check after launch: conversion, the annual share, and how many Pro users reach a limit. Change them in Assumptions.</t>
   </si>
   <si>
+    <t xml:space="preserve">Regional prices, by purchasing power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Countries (examples)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of payers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro monthly (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro annual (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max monthly (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual margin/mo, worst case (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro annual margin/mo, expected (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – Full price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium, France, Switzerland, Luxembourg, Germany, Netherlands, Nordics, UK, US, Canada, Australia, Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 – Reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain, Italy, Portugal, Greece, Poland, Czechia, the Baltics, Korea, Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 – Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco, Algeria, Tunisia, Turkey, Romania, Brazil, Mexico, Southeast Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 – Lowest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal, Côte d'Ivoire, Cameroon and French-speaking Africa, India, Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average price paid (index)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 'Unit economics' and 'Projection' sheets use these average indexes, so revenue already reflects regional prices. The shares of payers must add up to 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max has a higher floor (60%) than Pro (30%). The LLM costs the same in every country: at 50%, a Max user hitting every cap would cost more than they pay in tier 4 (see the worst-case column). Pro can go lower because credits cap its usage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which price applies: the store account's country in-app (Apple and Google set prices per country); on the web, the country of the card (Stripe), so a VPN doesn't unlock a cheaper price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outside the EU the stores add the local sales tax (e.g. India 18%). The margin columns use the EU rate as an approximation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">One-off costs to start</t>
   </si>
   <si>
@@ -890,10 +965,10 @@
     <t xml:space="preserve">Unit economics: what one subscriber brings in and costs, per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual plans are spread over 12 months · in-app and web sales are blended by the channel mix · VAT shown as if charged on the web too (the exemption is added back in 'Projection').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List price incl. VAT (€)</t>
+    <t xml:space="preserve">Prices are averaged over the regional tiers (Pricing) · annual plans are spread over 12 months · in-app and web sales are blended by the channel mix · VAT shown as if charged on the web too (the exemption is added back in 'Projection').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average price paid incl. VAT (€)</t>
   </si>
   <si>
     <t xml:space="preserve">Months covered</t>
@@ -953,7 +1028,7 @@
     <t xml:space="preserve">All payers</t>
   </si>
   <si>
-    <t xml:space="preserve">Where Pro annual is bought: what you keep of €59.99-type prices</t>
+    <t xml:space="preserve">Where Pro annual is bought: what you keep (average regional price)</t>
   </si>
   <si>
     <t xml:space="preserve">Channel</t>
@@ -1169,7 +1244,7 @@
     <t xml:space="preserve">Status / what to build</t>
   </si>
   <si>
-    <t xml:space="preserve">Price</t>
+    <t xml:space="preserve">Price (tier 1)</t>
   </si>
   <si>
     <t xml:space="preserve">€0</t>
@@ -1405,16 +1480,40 @@
     <t xml:space="preserve">Downgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">Grace period, then over-limit decks and favourites deleted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same</t>
+    <t xml:space="preserve">30-day grace period to export and delete over-limit decks; then favourites over the limit are removed, most recently added first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same, down to Pro's limits</t>
   </si>
   <si>
     <t xml:space="preserve">Deck CSV export exists (GET /api/decks/{id}/export), plus the full progress export.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decided. Cards already started can still be reviewed. To build: the grace period and its warnings.</t>
+    <t xml:space="preserve">Decided. Cards already started can still be reviewed, at 1 credit a review once on Free: no free reviews after leaving Pro. To build: the grace period and its reminders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit packs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decided: yes, but not at launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By purchasing power, 4 tiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By purchasing power, 4 tiers (floor 60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decided. Tiers and prices on the 'Pricing' sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Daily safety caps (LLM)</t>
@@ -1432,25 +1531,19 @@
     <t xml:space="preserve">Publish them as a fair-use policy for Max.</t>
   </si>
   <si>
-    <t xml:space="preserve">Still to decide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grace period length. Suggestion: 60 days, with reminders at 30, 7 and 1 day. Meanwhile, block adding cards to a deck that's over the limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews after a downgrade. A Free user reviewing N2/N1 cards they had started: does each review cost 1 credit like any other? (Assumed yes.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favourites over 30 after the grace period: delete the newest ones and keep the oldest 30, or let the user choose which to keep?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal texts: the 14-day withdrawal right (waived when the user starts using the content, with their consent), renewal reminders for annual plans, and a one-click way to cancel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buying credits. Can a Free or Pro user who runs out buy a credit pack? It would be another source of revenue, and a first step towards buying Pro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prices in other currencies (¥, $, CHF, CAD) for the stores.</t>
+    <t xml:space="preserve">Still to do or check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal texts: the 14-day withdrawal right (waived when the user starts using the content, with their consent), renewal reminders for annual plans, a one-click way to cancel, and the 30-day grace period written into the terms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace-period reminders: when the 30 days start, 7 days before the end, and the day before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional tiers: check the country lists and multipliers against the store price grids, and correct the shares of payers with real data after launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit packs (later): sizes and prices. For example 100 credits for €1.99, tiered by region like the subscriptions.</t>
   </si>
   <si>
     <t xml:space="preserve">Student status and your family: income from the activity can change whether you're still a dependent for tax, and your family allowance (allocations familiales). The rules depend on your region, so check with your fund.</t>
@@ -1669,7 +1762,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1790,6 +1883,14 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1815,10 +1916,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2054,28 +2151,28 @@
                 <c:formatCode>\€#,##0.00;"(€"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>34.6883150829201</c:v>
+                  <c:v>30.6535386110957</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163.441740061432</c:v>
+                  <c:v>144.50161669974</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>321.883562446281</c:v>
+                  <c:v>284.620195221612</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>807.208864953995</c:v>
+                  <c:v>713.742007142964</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1609.41781223141</c:v>
+                  <c:v>1423.10097610806</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2941.99661619835</c:v>
+                  <c:v>2601.19409746405</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7354.99154049587</c:v>
+                  <c:v>6502.98524366013</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14709.9830809917</c:v>
+                  <c:v>13005.9704873203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2210,11 +2307,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="85416840"/>
-        <c:axId val="21256931"/>
+        <c:axId val="68326944"/>
+        <c:axId val="6816520"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85416840"/>
+        <c:axId val="68326944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2280,7 +2377,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21256931"/>
+        <c:crossAx val="6816520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2288,7 +2385,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21256931"/>
+        <c:axId val="6816520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2364,7 +2461,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85416840"/>
+        <c:crossAx val="68326944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2758,7 +2855,7 @@
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">'Unit economics'!$O$11</f>
-        <v>4.2687912137741</v>
+        <v>3.70460686175344</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2767,7 +2864,7 @@
       </c>
       <c r="B20" s="6" t="n">
         <f aca="false">'Unit economics'!$O$12</f>
-        <v>8.3782127</v>
+        <v>7.50901709675</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2776,7 +2873,7 @@
       </c>
       <c r="B21" s="8" t="n">
         <f aca="false">'Unit economics'!$O$13</f>
-        <v>5.01595875672427</v>
+        <v>4.396317813571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2785,7 +2882,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">'Unit economics'!$R$13</f>
-        <v>3.59128275672427</v>
+        <v>2.971641813571</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2809,7 +2906,7 @@
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">'Unit economics'!$D$23</f>
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,7 +2915,7 @@
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">'Unit economics'!$E$23</f>
-        <v>855</v>
+        <v>964</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2870,35 +2967,35 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">Projection!B17</f>
-        <v>34.6883150829201</v>
+        <v>30.6535386110957</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">Projection!C17</f>
-        <v>163.441740061432</v>
+        <v>144.50161669974</v>
       </c>
       <c r="D31" s="10" t="n">
         <f aca="false">Projection!D17</f>
-        <v>321.883562446281</v>
+        <v>284.620195221612</v>
       </c>
       <c r="E31" s="10" t="n">
         <f aca="false">Projection!E17</f>
-        <v>807.208864953995</v>
+        <v>713.742007142964</v>
       </c>
       <c r="F31" s="10" t="n">
         <f aca="false">Projection!F17</f>
-        <v>1609.41781223141</v>
+        <v>1423.10097610806</v>
       </c>
       <c r="G31" s="10" t="n">
         <f aca="false">Projection!G17</f>
-        <v>2941.99661619835</v>
+        <v>2601.19409746405</v>
       </c>
       <c r="H31" s="10" t="n">
         <f aca="false">Projection!H17</f>
-        <v>7354.99154049587</v>
+        <v>6502.98524366013</v>
       </c>
       <c r="I31" s="10" t="n">
         <f aca="false">Projection!I17</f>
-        <v>14709.9830809917</v>
+        <v>13005.9704873203</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2960,19 +3057,19 @@
       </c>
       <c r="F33" s="10" t="n">
         <f aca="false">Projection!F33</f>
-        <v>80.219926007438</v>
+        <v>42.0249746021519</v>
       </c>
       <c r="G33" s="10" t="n">
         <f aca="false">Projection!G33</f>
-        <v>473.335952570661</v>
+        <v>403.47143623013</v>
       </c>
       <c r="H33" s="10" t="n">
         <f aca="false">Projection!H33</f>
-        <v>1214.44390105165</v>
+        <v>1039.78261020033</v>
       </c>
       <c r="I33" s="10" t="n">
         <f aca="false">Projection!I33</f>
-        <v>2579.88602560331</v>
+        <v>2230.56344390065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2981,35 +3078,35 @@
       </c>
       <c r="B34" s="10" t="n">
         <f aca="false">Projection!B34</f>
-        <v>-200.91680891708</v>
+        <v>-204.951585388904</v>
       </c>
       <c r="C34" s="10" t="n">
         <f aca="false">Projection!C34</f>
-        <v>-83.2721559385675</v>
+        <v>-102.21227930026</v>
       </c>
       <c r="D34" s="10" t="n">
         <f aca="false">Projection!D34</f>
-        <v>61.429182446281</v>
+        <v>24.1658152216116</v>
       </c>
       <c r="E34" s="10" t="n">
         <f aca="false">Projection!E34</f>
-        <v>382.312108953995</v>
+        <v>288.845251142964</v>
       </c>
       <c r="F34" s="10" t="n">
         <f aca="false">Projection!F34</f>
-        <v>1035.01678622397</v>
+        <v>886.894901505906</v>
       </c>
       <c r="G34" s="10" t="n">
         <f aca="false">Projection!G34</f>
-        <v>1835.61991362769</v>
+        <v>1564.68191123392</v>
       </c>
       <c r="H34" s="10" t="n">
         <f aca="false">Projection!H34</f>
-        <v>4709.67268944422</v>
+        <v>4032.3276834598</v>
       </c>
       <c r="I34" s="10" t="n">
         <f aca="false">Projection!I34</f>
-        <v>10004.9238553884</v>
+        <v>8650.2338434196</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3740,13 +3837,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4182,6 +4280,257 @@
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D35,1)-0.01)</f>
+        <v>8.99</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D35,1)-0.01)</f>
+        <v>59.99</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E35,1)-0.01)</f>
+        <v>14.99</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E35,1)-0.01)</f>
+        <v>99.99</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <f aca="false">I35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>2.50348909090909</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <f aca="false">G35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>3.21084929476584</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D36,1)-0.01)</f>
+        <v>6.99</v>
+      </c>
+      <c r="G36" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D36,1)-0.01)</f>
+        <v>44.99</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E36,1)-0.01)</f>
+        <v>11.99</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E36,1)-0.01)</f>
+        <v>74.99</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <f aca="false">I36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>1.03999046831956</v>
+      </c>
+      <c r="K36" s="26" t="n">
+        <f aca="false">G36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>2.33275012121212</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D37,1)-0.01)</f>
+        <v>4.99</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D37,1)-0.01)</f>
+        <v>29.99</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E37,1)-0.01)</f>
+        <v>8.99</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E37,1)-0.01)</f>
+        <v>59.99</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <f aca="false">I37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>0.16189129476584</v>
+      </c>
+      <c r="K37" s="26" t="n">
+        <f aca="false">G37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>1.4546509476584</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F38" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D38,1)-0.01)</f>
+        <v>2.99</v>
+      </c>
+      <c r="G38" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D38,1)-0.01)</f>
+        <v>17.99</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E38,1)-0.01)</f>
+        <v>8.99</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E38,1)-0.01)</f>
+        <v>59.99</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <f aca="false">I38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>0.16189129476584</v>
+      </c>
+      <c r="K38" s="26" t="n">
+        <f aca="false">G38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
+        <v>0.752171608815427</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <f aca="false">SUM(C35:C38)</f>
+        <v>1</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <f aca="false">IF(C39=0,1,SUMPRODUCT(C35:C38,D35:D38)/C39)</f>
+        <v>0.8775</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <f aca="false">IF(C39=0,1,SUMPRODUCT(C35:C38,E35:E38)/C39)</f>
+        <v>0.9025</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="25" t="s">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4225,69 +4574,69 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E5" s="32" t="n">
+      <c r="D5" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>111.5</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="34" t="n">
         <v>111.5</v>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="34" t="n">
         <v>111.5</v>
       </c>
       <c r="H5" s="26" t="n">
@@ -4303,29 +4652,29 @@
         <v>111.5</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="32" t="n">
+      <c r="D6" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="34" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="26" t="n">
@@ -4341,29 +4690,29 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="32" t="n">
+      <c r="D7" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="34" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="26" t="n">
@@ -4379,29 +4728,29 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" s="32" t="n">
+      <c r="D8" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="34" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="26" t="n">
@@ -4417,29 +4766,29 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E9" s="32" t="n">
+        <v>215</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" s="34" t="n">
         <v>1000</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="34" t="n">
         <v>1400</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="34" t="n">
         <v>2000</v>
       </c>
       <c r="H9" s="26" t="n">
@@ -4455,29 +4804,29 @@
         <v>2000</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="32" t="n">
+      <c r="D10" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" s="34" t="n">
         <v>271</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="34" t="n">
         <v>271</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="34" t="n">
         <v>271</v>
       </c>
       <c r="H10" s="26" t="n">
@@ -4493,29 +4842,29 @@
         <v>271</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="32" t="n">
+        <v>215</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="34" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="34" t="n">
         <v>900</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="34" t="n">
         <v>900</v>
       </c>
       <c r="H11" s="26" t="n">
@@ -4531,29 +4880,29 @@
         <v>900</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E12" s="32" t="n">
+        <v>215</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="34" t="n">
         <v>500</v>
       </c>
       <c r="H12" s="26" t="n">
@@ -4569,29 +4918,29 @@
         <v>500</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="32" t="n">
+      <c r="D13" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="34" t="n">
         <v>1500</v>
       </c>
       <c r="H13" s="26" t="n">
@@ -4607,29 +4956,29 @@
         <v>1500</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E14" s="32" t="n">
+      <c r="D14" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="34" t="n">
         <v>300</v>
       </c>
       <c r="H14" s="26" t="n">
@@ -4645,29 +4994,29 @@
         <v>300</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E15" s="32" t="n">
+      <c r="D15" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="34" t="n">
         <v>25</v>
       </c>
       <c r="H15" s="26" t="n">
@@ -4683,29 +5032,29 @@
         <v>26.015</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="34" t="n">
         <v>700</v>
       </c>
       <c r="H16" s="26" t="n">
@@ -4721,29 +5070,29 @@
         <v>700</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" s="32" t="n">
+        <v>238</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="34" t="n">
         <v>400</v>
       </c>
       <c r="H17" s="26" t="n">
@@ -4762,24 +5111,24 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E18" s="32" t="n">
+      <c r="D18" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="34" t="n">
         <v>10</v>
       </c>
       <c r="H18" s="26" t="n">
@@ -4795,29 +5144,29 @@
         <v>10.406</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="32" t="n">
+      <c r="D19" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="32" t="n">
+      <c r="G19" s="34" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="26" t="n">
@@ -4833,29 +5182,29 @@
         <v>0</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C20" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="32" t="n">
+      <c r="D20" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="34" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="26" t="n">
@@ -4871,29 +5220,29 @@
         <v>0</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="32" t="n">
+      <c r="D21" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="34" t="n">
         <v>300</v>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="34" t="n">
         <v>1500</v>
       </c>
       <c r="H21" s="26" t="n">
@@ -4909,39 +5258,39 @@
         <v>1500</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="H23" s="33" t="n">
+        <v>253</v>
+      </c>
+      <c r="H23" s="35" t="n">
         <f aca="false">SUMIFS(H5:H21,$C$5:$C$21,"Y")</f>
         <v>412.6774</v>
       </c>
-      <c r="I23" s="33" t="n">
+      <c r="I23" s="35" t="n">
         <f aca="false">SUMIFS(I5:I21,$C$5:$C$21,"Y")</f>
         <v>963.718</v>
       </c>
-      <c r="J23" s="33" t="n">
+      <c r="J23" s="35" t="n">
         <f aca="false">SUMIFS(J5:J21,$C$5:$C$21,"Y")</f>
         <v>2218.921</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="H24" s="33" t="n">
+        <v>254</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <f aca="false">SUM(H5:H21)</f>
         <v>2312.6774</v>
       </c>
-      <c r="I24" s="33" t="n">
+      <c r="I24" s="35" t="n">
         <f aca="false">SUM(I5:I21)</f>
         <v>3713.718</v>
       </c>
-      <c r="J24" s="33" t="n">
+      <c r="J24" s="35" t="n">
         <f aca="false">SUM(J5:J21)</f>
         <v>8218.921</v>
       </c>
@@ -4974,75 +5323,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F5" s="32" t="n">
+      <c r="E5" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F5" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="32" t="n">
+      <c r="G5" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="32" t="n">
+      <c r="H5" s="34" t="n">
         <v>85</v>
       </c>
       <c r="I5" s="26" t="n">
@@ -5058,32 +5407,32 @@
         <v>88.451</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F6" s="32" t="n">
+      <c r="D6" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="34" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="34" t="n">
         <v>1.25</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="34" t="n">
         <v>5</v>
       </c>
       <c r="I6" s="26" t="n">
@@ -5099,32 +5448,32 @@
         <v>5.203</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F7" s="32" t="n">
+      <c r="D7" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="34" t="n">
         <v>25</v>
       </c>
       <c r="I7" s="26" t="n">
@@ -5140,32 +5489,32 @@
         <v>26.015</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="32" t="n">
+      <c r="D8" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="34" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="26" t="n">
@@ -5181,32 +5530,32 @@
         <v>19.7714</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F9" s="32" t="n">
+      <c r="D9" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="34" t="n">
         <v>20</v>
       </c>
       <c r="I9" s="26" t="n">
@@ -5222,32 +5571,32 @@
         <v>20.812</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F10" s="32" t="n">
+      <c r="D10" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="H10" s="32" t="n">
+      <c r="H10" s="34" t="n">
         <v>75</v>
       </c>
       <c r="I10" s="26" t="n">
@@ -5263,32 +5612,32 @@
         <v>78.045</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C11" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F11" s="32" t="n">
+      <c r="D11" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="34" t="n">
         <v>20</v>
       </c>
       <c r="I11" s="26" t="n">
@@ -5304,32 +5653,32 @@
         <v>20.812</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C12" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12" s="32" t="n">
+      <c r="D12" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="32" t="n">
+      <c r="H12" s="34" t="n">
         <v>26</v>
       </c>
       <c r="I12" s="26" t="n">
@@ -5345,32 +5694,32 @@
         <v>27.0556</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F13" s="32" t="n">
+      <c r="D13" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="34" t="n">
         <v>10</v>
       </c>
       <c r="I13" s="26" t="n">
@@ -5386,32 +5735,32 @@
         <v>10.406</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F14" s="32" t="n">
+        <v>283</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" s="34" t="n">
         <v>3.5</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="34" t="n">
         <v>14</v>
       </c>
       <c r="I14" s="26" t="n">
@@ -5427,32 +5776,32 @@
         <v>14.5684</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C15" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="F15" s="32" t="n">
+      <c r="D15" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F15" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="H15" s="34" t="n">
         <v>15</v>
       </c>
       <c r="I15" s="26" t="n">
@@ -5468,32 +5817,32 @@
         <v>1.30075</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="H16" s="34" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="26" t="n">
@@ -5509,32 +5858,32 @@
         <v>7</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C17" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="F17" s="32" t="n">
+      <c r="D17" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="F17" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="H17" s="34" t="n">
         <v>99</v>
       </c>
       <c r="I17" s="26" t="n">
@@ -5550,32 +5899,32 @@
         <v>8.58495</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C18" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F18" s="32" t="n">
+      <c r="D18" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="32" t="n">
+      <c r="H18" s="34" t="n">
         <v>200</v>
       </c>
       <c r="I18" s="26" t="n">
@@ -5591,32 +5940,32 @@
         <v>200</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C19" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F19" s="32" t="n">
+      <c r="D19" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="32" t="n">
+      <c r="G19" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="32" t="n">
+      <c r="H19" s="34" t="n">
         <v>15</v>
       </c>
       <c r="I19" s="26" t="n">
@@ -5632,32 +5981,32 @@
         <v>15</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" s="32" t="n">
+        <v>297</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F20" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="H20" s="32" t="n">
+      <c r="H20" s="34" t="n">
         <v>40</v>
       </c>
       <c r="I20" s="26" t="n">
@@ -5673,32 +6022,32 @@
         <v>40</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C21" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F21" s="34" t="n">
+      <c r="D21" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="36" t="n">
         <v>200</v>
       </c>
       <c r="I21" s="26" t="n">
@@ -5714,32 +6063,32 @@
         <v>208.12</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C22" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="34" t="n">
         <v>200</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="F22" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="32" t="n">
-        <v>200</v>
-      </c>
-      <c r="H22" s="32" t="n">
+      <c r="H22" s="34" t="n">
         <v>1000</v>
       </c>
       <c r="I22" s="26" t="n">
@@ -5755,63 +6104,63 @@
         <v>1000</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="I24" s="33" t="n">
+        <v>307</v>
+      </c>
+      <c r="I24" s="35" t="n">
         <f aca="false">SUMIFS(I5:I22,$C$5:$C$22,"Y")</f>
         <v>232.68245</v>
       </c>
-      <c r="J24" s="33" t="n">
+      <c r="J24" s="35" t="n">
         <f aca="false">SUMIFS(J5:J22,$C$5:$C$22,"Y")</f>
         <v>355.32145</v>
       </c>
-      <c r="K24" s="33" t="n">
+      <c r="K24" s="35" t="n">
         <f aca="false">SUMIFS(K5:K22,$C$5:$C$22,"Y")</f>
         <v>736.5767</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I25" s="33" t="n">
+        <v>308</v>
+      </c>
+      <c r="I25" s="35" t="n">
         <f aca="false">I24*12</f>
         <v>2792.1894</v>
       </c>
-      <c r="J25" s="33" t="n">
+      <c r="J25" s="35" t="n">
         <f aca="false">J24*12</f>
         <v>4263.8574</v>
       </c>
-      <c r="K25" s="33" t="n">
+      <c r="K25" s="35" t="n">
         <f aca="false">K24*12</f>
         <v>8838.9204</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="I26" s="33" t="n">
+        <v>309</v>
+      </c>
+      <c r="I26" s="35" t="n">
         <f aca="false">SUM(I5:I22)</f>
         <v>236.32455</v>
       </c>
-      <c r="J26" s="33" t="n">
+      <c r="J26" s="35" t="n">
         <f aca="false">SUM(J5:J22)</f>
         <v>587.60565</v>
       </c>
-      <c r="K26" s="33" t="n">
+      <c r="K26" s="35" t="n">
         <f aca="false">SUM(K5:K22)</f>
         <v>1791.1451</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5840,12 +6189,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5856,55 +6205,55 @@
         <v>131</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5915,43 +6264,43 @@
         <v>139</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">Assumptions!$B$10</f>
-        <v>8.99</v>
-      </c>
-      <c r="D5" s="31" t="n">
+        <f aca="false">Assumptions!$B$10*Pricing!$D$39</f>
+        <v>7.888725</v>
+      </c>
+      <c r="D5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="37" t="n">
         <f aca="false">1/D5</f>
         <v>1</v>
       </c>
       <c r="F5" s="26" t="n">
         <f aca="false">C5/D5</f>
-        <v>8.99</v>
+        <v>7.888725</v>
       </c>
       <c r="G5" s="26" t="n">
         <f aca="false">F5-H5</f>
-        <v>1.5602479338843</v>
+        <v>1.36911756198347</v>
       </c>
       <c r="H5" s="26" t="n">
         <f aca="false">F5/(1+Assumptions!$B$7)</f>
-        <v>7.4297520661157</v>
+        <v>6.51960743801653</v>
       </c>
       <c r="I5" s="26" t="n">
         <f aca="false">H5*Assumptions!$B$21</f>
-        <v>1.11446280991736</v>
+        <v>0.977941115702479</v>
       </c>
       <c r="J5" s="26" t="n">
         <f aca="false">F5*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E5</f>
-        <v>0.44778</v>
+        <v>0.42355195</v>
       </c>
       <c r="K5" s="26" t="n">
         <f aca="false">Assumptions!$B$19*I5+(1-Assumptions!$B$19)*J5</f>
-        <v>0.847789685950413</v>
+        <v>0.756185449421488</v>
       </c>
       <c r="L5" s="26" t="n">
         <f aca="false">H5-K5</f>
-        <v>6.58196238016529</v>
+        <v>5.76342198859504</v>
       </c>
       <c r="M5" s="26" t="n">
         <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -5963,11 +6312,11 @@
       </c>
       <c r="O5" s="26" t="n">
         <f aca="false">L5-M5-N5</f>
-        <v>6.28100038016529</v>
+        <v>5.46245998859504</v>
       </c>
       <c r="P5" s="27" t="n">
         <f aca="false">IF(F5=0,0,O5/F5)</f>
-        <v>0.698665225824838</v>
+        <v>0.692438890770694</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -5975,7 +6324,7 @@
       </c>
       <c r="R5" s="26" t="n">
         <f aca="false">L5-Q5-N5</f>
-        <v>5.17796438016529</v>
+        <v>4.35942398859504</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5986,43 +6335,43 @@
         <v>140</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">Assumptions!$B$11</f>
-        <v>59.99</v>
-      </c>
-      <c r="D6" s="31" t="n">
+        <f aca="false">Assumptions!$B$11*Pricing!$D$39</f>
+        <v>52.641225</v>
+      </c>
+      <c r="D6" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="37" t="n">
         <f aca="false">1/D6</f>
         <v>0.0833333333333333</v>
       </c>
       <c r="F6" s="26" t="n">
         <f aca="false">C6/D6</f>
-        <v>4.99916666666667</v>
+        <v>4.38676875</v>
       </c>
       <c r="G6" s="26" t="n">
         <f aca="false">F6-H6</f>
-        <v>0.867623966942149</v>
+        <v>0.761340030991736</v>
       </c>
       <c r="H6" s="26" t="n">
         <f aca="false">F6/(1+Assumptions!$B$7)</f>
-        <v>4.13154269972452</v>
+        <v>3.62542871900826</v>
       </c>
       <c r="I6" s="26" t="n">
         <f aca="false">H6*Assumptions!$B$21</f>
-        <v>0.619731404958678</v>
+        <v>0.54381430785124</v>
       </c>
       <c r="J6" s="26" t="n">
         <f aca="false">F6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E6</f>
-        <v>0.130815</v>
+        <v>0.117342245833333</v>
       </c>
       <c r="K6" s="26" t="n">
         <f aca="false">Assumptions!$B$19*I6+(1-Assumptions!$B$19)*J6</f>
-        <v>0.424164842975207</v>
+        <v>0.373225483044077</v>
       </c>
       <c r="L6" s="26" t="n">
         <f aca="false">H6-K6</f>
-        <v>3.70737785674931</v>
+        <v>3.25220323596419</v>
       </c>
       <c r="M6" s="26" t="n">
         <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6034,11 +6383,11 @@
       </c>
       <c r="O6" s="26" t="n">
         <f aca="false">L6-M6-N6</f>
-        <v>3.40641585674931</v>
+        <v>2.95124123596419</v>
       </c>
       <c r="P6" s="27" t="n">
         <f aca="false">IF(F6=0,0,O6/F6)</f>
-        <v>0.681396737472774</v>
+        <v>0.672759701765494</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6046,7 +6395,7 @@
       </c>
       <c r="R6" s="26" t="n">
         <f aca="false">L6-Q6-N6</f>
-        <v>2.30337985674931</v>
+        <v>1.84820523596419</v>
       </c>
       <c r="S6" s="27" t="n">
         <f aca="false">1-C6/(12*C5)</f>
@@ -6061,43 +6410,43 @@
         <v>139</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">Assumptions!$B$12</f>
-        <v>14.99</v>
-      </c>
-      <c r="D7" s="31" t="n">
+        <f aca="false">Assumptions!$B$12*Pricing!$E$39</f>
+        <v>13.528475</v>
+      </c>
+      <c r="D7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="37" t="n">
         <f aca="false">1/D7</f>
         <v>1</v>
       </c>
       <c r="F7" s="26" t="n">
         <f aca="false">C7/D7</f>
-        <v>14.99</v>
+        <v>13.528475</v>
       </c>
       <c r="G7" s="26" t="n">
         <f aca="false">F7-H7</f>
-        <v>2.60157024793388</v>
+        <v>2.34791714876033</v>
       </c>
       <c r="H7" s="26" t="n">
         <f aca="false">F7/(1+Assumptions!$B$7)</f>
-        <v>12.3884297520661</v>
+        <v>11.1805578512397</v>
       </c>
       <c r="I7" s="26" t="n">
         <f aca="false">H7*Assumptions!$B$21</f>
-        <v>1.85826446280992</v>
+        <v>1.67708367768595</v>
       </c>
       <c r="J7" s="26" t="n">
         <f aca="false">F7*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E7</f>
-        <v>0.57978</v>
+        <v>0.54762645</v>
       </c>
       <c r="K7" s="26" t="n">
         <f aca="false">Assumptions!$B$19*I7+(1-Assumptions!$B$19)*J7</f>
-        <v>1.34687067768595</v>
+        <v>1.22530078661157</v>
       </c>
       <c r="L7" s="26" t="n">
         <f aca="false">H7-K7</f>
-        <v>11.0415590743802</v>
+        <v>9.9552570646281</v>
       </c>
       <c r="M7" s="26" t="n">
         <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6109,11 +6458,11 @@
       </c>
       <c r="O7" s="26" t="n">
         <f aca="false">L7-M7-N7</f>
-        <v>10.5636950743802</v>
+        <v>9.4773930646281</v>
       </c>
       <c r="P7" s="27" t="n">
         <f aca="false">IF(F7=0,0,O7/F7)</f>
-        <v>0.70471614905805</v>
+        <v>0.700551471221117</v>
       </c>
       <c r="Q7" s="26" t="n">
         <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6121,7 +6470,7 @@
       </c>
       <c r="R7" s="26" t="n">
         <f aca="false">L7-Q7-N7</f>
-        <v>7.69163907438017</v>
+        <v>6.6053370646281</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6132,43 +6481,43 @@
         <v>140</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">Assumptions!$B$13</f>
-        <v>99.99</v>
-      </c>
-      <c r="D8" s="31" t="n">
+        <f aca="false">Assumptions!$B$13*Pricing!$E$39</f>
+        <v>90.240975</v>
+      </c>
+      <c r="D8" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="37" t="n">
         <f aca="false">1/D8</f>
         <v>0.0833333333333333</v>
       </c>
       <c r="F8" s="26" t="n">
         <f aca="false">C8/D8</f>
-        <v>8.3325</v>
+        <v>7.52008125</v>
       </c>
       <c r="G8" s="26" t="n">
         <f aca="false">F8-H8</f>
-        <v>1.44613636363636</v>
+        <v>1.30513806818182</v>
       </c>
       <c r="H8" s="26" t="n">
         <f aca="false">F8/(1+Assumptions!$B$7)</f>
-        <v>6.88636363636364</v>
+        <v>6.21494318181818</v>
       </c>
       <c r="I8" s="26" t="n">
         <f aca="false">H8*Assumptions!$B$21</f>
-        <v>1.03295454545455</v>
+        <v>0.932241477272727</v>
       </c>
       <c r="J8" s="26" t="n">
         <f aca="false">F8*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E8</f>
-        <v>0.204148333333333</v>
+        <v>0.186275120833333</v>
       </c>
       <c r="K8" s="26" t="n">
         <f aca="false">Assumptions!$B$19*I8+(1-Assumptions!$B$19)*J8</f>
-        <v>0.70143206060606</v>
+        <v>0.63385493469697</v>
       </c>
       <c r="L8" s="26" t="n">
         <f aca="false">H8-K8</f>
-        <v>6.18493157575758</v>
+        <v>5.58108824712121</v>
       </c>
       <c r="M8" s="26" t="n">
         <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6180,11 +6529,11 @@
       </c>
       <c r="O8" s="26" t="n">
         <f aca="false">L8-M8-N8</f>
-        <v>5.70706757575758</v>
+        <v>5.10322424712121</v>
       </c>
       <c r="P8" s="27" t="n">
         <f aca="false">IF(F8=0,0,O8/F8)</f>
-        <v>0.684916600750984</v>
+        <v>0.678612913540158</v>
       </c>
       <c r="Q8" s="26" t="n">
         <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -6192,7 +6541,7 @@
       </c>
       <c r="R8" s="26" t="n">
         <f aca="false">L8-Q8-N8</f>
-        <v>2.83501157575758</v>
+        <v>2.23116824712121</v>
       </c>
       <c r="S8" s="27" t="n">
         <f aca="false">1-C8/(12*C7)</f>
@@ -6201,7 +6550,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6209,51 +6558,51 @@
         <v>138</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="F11" s="36" t="n">
+        <v>331</v>
+      </c>
+      <c r="F11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*F5+Assumptions!$B$17*F6</f>
-        <v>6.19641666666667</v>
-      </c>
-      <c r="G11" s="36" t="n">
+        <v>5.437355625</v>
+      </c>
+      <c r="G11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*G5+Assumptions!$B$17*G6</f>
-        <v>1.07541115702479</v>
-      </c>
-      <c r="H11" s="36" t="n">
+        <v>0.943673290289256</v>
+      </c>
+      <c r="H11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*H5+Assumptions!$B$17*H6</f>
-        <v>5.12100550964187</v>
-      </c>
-      <c r="K11" s="36" t="n">
+        <v>4.49368233471074</v>
+      </c>
+      <c r="K11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*K5+Assumptions!$B$17*K6</f>
-        <v>0.551252295867769</v>
-      </c>
-      <c r="L11" s="36" t="n">
+        <v>0.4881134729573</v>
+      </c>
+      <c r="L11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*L5+Assumptions!$B$17*L6</f>
-        <v>4.56975321377411</v>
-      </c>
-      <c r="M11" s="36" t="n">
+        <v>4.00556886175344</v>
+      </c>
+      <c r="M11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*M5+Assumptions!$B$17*M6</f>
         <v>0.280962</v>
       </c>
-      <c r="N11" s="36" t="n">
+      <c r="N11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*N5+Assumptions!$B$17*N6</f>
         <v>0.02</v>
       </c>
-      <c r="O11" s="36" t="n">
+      <c r="O11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*O5+Assumptions!$B$17*O6</f>
-        <v>4.2687912137741</v>
-      </c>
-      <c r="P11" s="37" t="n">
+        <v>3.70460686175344</v>
+      </c>
+      <c r="P11" s="31" t="n">
         <f aca="false">IF(F11=0,0,O11/F11)</f>
-        <v>0.688912873909508</v>
-      </c>
-      <c r="Q11" s="36" t="n">
+        <v>0.681325099414193</v>
+      </c>
+      <c r="Q11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*Q5+Assumptions!$B$17*Q6</f>
         <v>1.383998</v>
       </c>
-      <c r="R11" s="36" t="n">
+      <c r="R11" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$17)*R5+Assumptions!$B$17*R6</f>
-        <v>3.16575521377411</v>
+        <v>2.60157086175344</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6261,108 +6610,108 @@
         <v>141</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="F12" s="36" t="n">
+        <v>331</v>
+      </c>
+      <c r="F12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*F7+Assumptions!$B$18*F8</f>
-        <v>11.994125</v>
-      </c>
-      <c r="G12" s="36" t="n">
+        <v>10.8246978125</v>
+      </c>
+      <c r="G12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*G7+Assumptions!$B$18*G8</f>
-        <v>2.081625</v>
-      </c>
-      <c r="H12" s="36" t="n">
+        <v>1.8786665625</v>
+      </c>
+      <c r="H12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*H7+Assumptions!$B$18*H8</f>
-        <v>9.9125</v>
-      </c>
-      <c r="K12" s="36" t="n">
+        <v>8.94603125</v>
+      </c>
+      <c r="K12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*K7+Assumptions!$B$18*K8</f>
-        <v>1.0564233</v>
-      </c>
-      <c r="L12" s="36" t="n">
+        <v>0.95915015325</v>
+      </c>
+      <c r="L12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*L7+Assumptions!$B$18*L8</f>
-        <v>8.8560767</v>
-      </c>
-      <c r="M12" s="36" t="n">
+        <v>7.98688109675</v>
+      </c>
+      <c r="M12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*M7+Assumptions!$B$18*M8</f>
         <v>0.457864</v>
       </c>
-      <c r="N12" s="36" t="n">
+      <c r="N12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*N7+Assumptions!$B$18*N8</f>
         <v>0.02</v>
       </c>
-      <c r="O12" s="36" t="n">
+      <c r="O12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*O7+Assumptions!$B$18*O8</f>
-        <v>8.3782127</v>
-      </c>
-      <c r="P12" s="37" t="n">
+        <v>7.50901709675</v>
+      </c>
+      <c r="P12" s="31" t="n">
         <f aca="false">IF(F12=0,0,O12/F12)</f>
-        <v>0.698526378539493</v>
-      </c>
-      <c r="Q12" s="36" t="n">
+        <v>0.693692999732412</v>
+      </c>
+      <c r="Q12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*Q7+Assumptions!$B$18*Q8</f>
         <v>3.32992</v>
       </c>
-      <c r="R12" s="36" t="n">
+      <c r="R12" s="38" t="n">
         <f aca="false">(1-Assumptions!$B$18)*R7+Assumptions!$B$18*R8</f>
-        <v>5.5061567</v>
+        <v>4.63696109675</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="F13" s="36" t="n">
+        <v>331</v>
+      </c>
+      <c r="F13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*F11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*F12)</f>
-        <v>7.25054545454546</v>
-      </c>
-      <c r="G13" s="36" t="n">
+        <v>6.41687238636364</v>
+      </c>
+      <c r="G13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*G11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*G12)</f>
-        <v>1.25835912847483</v>
-      </c>
-      <c r="H13" s="36" t="n">
+        <v>1.11367206705485</v>
+      </c>
+      <c r="H13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*H11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*H12)</f>
-        <v>5.99218632607063</v>
-      </c>
-      <c r="K13" s="36" t="n">
+        <v>5.30320031930879</v>
+      </c>
+      <c r="K13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*K11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*K12)</f>
-        <v>0.643101569346356</v>
-      </c>
-      <c r="L13" s="36" t="n">
+        <v>0.573756505737791</v>
+      </c>
+      <c r="L13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*L11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*L12)</f>
-        <v>5.34908475672427</v>
-      </c>
-      <c r="M13" s="36" t="n">
+        <v>4.729443813571</v>
+      </c>
+      <c r="M13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*M11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*M12)</f>
         <v>0.313126</v>
       </c>
-      <c r="N13" s="36" t="n">
+      <c r="N13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*N11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*N12)</f>
         <v>0.02</v>
       </c>
-      <c r="O13" s="36" t="n">
+      <c r="O13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*O11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*O12)</f>
-        <v>5.01595875672427</v>
-      </c>
-      <c r="P13" s="37" t="n">
+        <v>4.396317813571</v>
+      </c>
+      <c r="P13" s="31" t="n">
         <f aca="false">IF(F13=0,0,O13/F13)</f>
-        <v>0.691804332262989</v>
-      </c>
-      <c r="Q13" s="36" t="n">
+        <v>0.685118473434741</v>
+      </c>
+      <c r="Q13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*Q11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*Q12)</f>
         <v>1.737802</v>
       </c>
-      <c r="R13" s="36" t="n">
+      <c r="R13" s="38" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*R11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*R12)</f>
-        <v>3.59128275672427</v>
+        <v>2.971641813571</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -6373,44 +6722,44 @@
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C17" s="26" t="n">
         <f aca="false">C6</f>
-        <v>59.99</v>
+        <v>52.641225</v>
       </c>
       <c r="D17" s="26" t="n">
         <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
-        <v>10.4114876033058</v>
+        <v>9.13608037190083</v>
       </c>
       <c r="E17" s="26" t="n">
         <f aca="false">C6/(1+Assumptions!$B$7)*Assumptions!$B$21</f>
-        <v>7.43677685950413</v>
-      </c>
-      <c r="F17" s="38" t="n">
+        <v>6.52577169421488</v>
+      </c>
+      <c r="F17" s="39" t="n">
         <f aca="false">C17-D17-E17</f>
-        <v>42.1417355371901</v>
+        <v>36.9793729338843</v>
       </c>
       <c r="G17" s="27" t="n">
         <f aca="false">IF(C17=0,0,F17/C17)</f>
@@ -6419,36 +6768,36 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C18" s="26" t="n">
         <f aca="false">C6</f>
-        <v>59.99</v>
+        <v>52.641225</v>
       </c>
       <c r="D18" s="26" t="n">
         <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
-        <v>10.4114876033058</v>
+        <v>9.13608037190083</v>
       </c>
       <c r="E18" s="26" t="n">
         <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
-        <v>1.56978</v>
-      </c>
-      <c r="F18" s="38" t="n">
+        <v>1.40810695</v>
+      </c>
+      <c r="F18" s="39" t="n">
         <f aca="false">C18-D18-E18</f>
-        <v>48.0087323966942</v>
+        <v>42.0970376780992</v>
       </c>
       <c r="G18" s="27" t="n">
         <f aca="false">IF(C18=0,0,F18/C18)</f>
-        <v>0.800278919764864</v>
+        <v>0.799697151388464</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C19" s="26" t="n">
         <f aca="false">C6</f>
-        <v>59.99</v>
+        <v>52.641225</v>
       </c>
       <c r="D19" s="26" t="n">
         <f aca="false">0</f>
@@ -6456,20 +6805,20 @@
       </c>
       <c r="E19" s="26" t="n">
         <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
-        <v>1.56978</v>
-      </c>
-      <c r="F19" s="38" t="n">
+        <v>1.40810695</v>
+      </c>
+      <c r="F19" s="39" t="n">
         <f aca="false">C19-D19-E19</f>
-        <v>58.42022</v>
+        <v>51.23311805</v>
       </c>
       <c r="G19" s="27" t="n">
         <f aca="false">IF(C19=0,0,F19/C19)</f>
-        <v>0.973832638773129</v>
+        <v>0.973250870396728</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -6480,80 +6829,80 @@
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C23" s="6" t="n">
         <f aca="false">'Fixed costs'!$I$24</f>
         <v>232.68245</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="40" t="n">
         <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C23/O13,0))</f>
-        <v>47</v>
-      </c>
-      <c r="E23" s="39" t="n">
+        <v>53</v>
+      </c>
+      <c r="E23" s="40" t="n">
         <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>855</v>
+        <v>964</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C24" s="6" t="n">
         <f aca="false">'Fixed costs'!$J$24</f>
         <v>355.32145</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="40" t="n">
         <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C24/O13,0))</f>
-        <v>71</v>
-      </c>
-      <c r="E24" s="39" t="n">
+        <v>81</v>
+      </c>
+      <c r="E24" s="40" t="n">
         <f aca="false">IF(ISNUMBER(D24),ROUNDUP(D24/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>1291</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C25" s="6" t="n">
         <f aca="false">'Fixed costs'!$K$24</f>
         <v>736.5767</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="40" t="n">
         <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C25/O13,0))</f>
-        <v>147</v>
-      </c>
-      <c r="E25" s="39" t="n">
+        <v>168</v>
+      </c>
+      <c r="E25" s="40" t="n">
         <f aca="false">IF(ISNUMBER(D25),ROUNDUP(D25/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>2673</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C29" s="6" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -6585,46 +6934,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>100</v>
@@ -6653,192 +7002,192 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B6" s="40" t="n">
+        <v>360</v>
+      </c>
+      <c r="B6" s="41" t="n">
         <f aca="false">IF(B5&gt;=Assumptions!$B$39,3,IF(B5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="41" t="n">
         <f aca="false">IF(C5&gt;=Assumptions!$B$39,3,IF(C5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="41" t="n">
         <f aca="false">IF(D5&gt;=Assumptions!$B$39,3,IF(D5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="41" t="n">
         <f aca="false">IF(E5&gt;=Assumptions!$B$39,3,IF(E5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="41" t="n">
         <f aca="false">IF(F5&gt;=Assumptions!$B$39,3,IF(F5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="G6" s="40" t="n">
+      <c r="G6" s="41" t="n">
         <f aca="false">IF(G5&gt;=Assumptions!$B$39,3,IF(G5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="H6" s="40" t="n">
+      <c r="H6" s="41" t="n">
         <f aca="false">IF(H5&gt;=Assumptions!$B$39,3,IF(H5&gt;=Assumptions!$B$38,2,1))</f>
         <v>3</v>
       </c>
-      <c r="I6" s="40" t="n">
+      <c r="I6" s="41" t="n">
         <f aca="false">IF(I5&gt;=Assumptions!$B$39,3,IF(I5&gt;=Assumptions!$B$38,2,1))</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B7" s="39" t="n">
+        <v>361</v>
+      </c>
+      <c r="B7" s="40" t="n">
         <f aca="false">B5-B8-B9</f>
         <v>94</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">C5-C8-C9</f>
         <v>472</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">D5-D8-D9</f>
         <v>945</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <f aca="false">E5-E8-E9</f>
         <v>2362</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">F5-F8-F9</f>
         <v>4725</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="40" t="n">
         <f aca="false">G5-G8-G9</f>
         <v>9450</v>
       </c>
-      <c r="H7" s="39" t="n">
+      <c r="H7" s="40" t="n">
         <f aca="false">H5-H8-H9</f>
         <v>23625</v>
       </c>
-      <c r="I7" s="39" t="n">
+      <c r="I7" s="40" t="n">
         <f aca="false">I5-I8-I9</f>
         <v>47250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B8" s="39" t="n">
+        <v>362</v>
+      </c>
+      <c r="B8" s="40" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$15,0)</f>
         <v>5</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">ROUND(C5*Assumptions!$B$15,0)</f>
         <v>23</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">ROUND(D5*Assumptions!$B$15,0)</f>
         <v>45</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <f aca="false">ROUND(E5*Assumptions!$B$15,0)</f>
         <v>113</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">ROUND(F5*Assumptions!$B$15,0)</f>
         <v>225</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="40" t="n">
         <f aca="false">ROUND(G5*Assumptions!$B$15,0)</f>
         <v>450</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="40" t="n">
         <f aca="false">ROUND(H5*Assumptions!$B$15,0)</f>
         <v>1125</v>
       </c>
-      <c r="I8" s="39" t="n">
+      <c r="I8" s="40" t="n">
         <f aca="false">ROUND(I5*Assumptions!$B$15,0)</f>
         <v>2250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B9" s="39" t="n">
+        <v>363</v>
+      </c>
+      <c r="B9" s="40" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$16,0)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="40" t="n">
         <f aca="false">ROUND(C5*Assumptions!$B$16,0)</f>
         <v>5</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <f aca="false">ROUND(D5*Assumptions!$B$16,0)</f>
         <v>10</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <f aca="false">ROUND(E5*Assumptions!$B$16,0)</f>
         <v>25</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="40" t="n">
         <f aca="false">ROUND(F5*Assumptions!$B$16,0)</f>
         <v>50</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="40" t="n">
         <f aca="false">ROUND(G5*Assumptions!$B$16,0)</f>
         <v>100</v>
       </c>
-      <c r="H9" s="39" t="n">
+      <c r="H9" s="40" t="n">
         <f aca="false">ROUND(H5*Assumptions!$B$16,0)</f>
         <v>250</v>
       </c>
-      <c r="I9" s="39" t="n">
+      <c r="I9" s="40" t="n">
         <f aca="false">ROUND(I5*Assumptions!$B$16,0)</f>
         <v>500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B10" s="41" t="n">
+        <v>364</v>
+      </c>
+      <c r="B10" s="42" t="n">
         <f aca="false">B8+B9</f>
         <v>6</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="42" t="n">
         <f aca="false">C8+C9</f>
         <v>28</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="42" t="n">
         <f aca="false">D8+D9</f>
         <v>55</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="42" t="n">
         <f aca="false">E8+E9</f>
         <v>138</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="42" t="n">
         <f aca="false">F8+F9</f>
         <v>275</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">G8+G9</f>
         <v>550</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="42" t="n">
         <f aca="false">H8+H9</f>
         <v>1375</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I10" s="42" t="n">
         <f aca="false">I8+I9</f>
         <v>2750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -6851,101 +7200,101 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$F$11+B9*'Unit economics'!$F$12</f>
-        <v>42.9762083333333</v>
+        <v>38.0114759375</v>
       </c>
       <c r="C13" s="26" t="n">
         <f aca="false">C8*'Unit economics'!$F$11+C9*'Unit economics'!$F$12</f>
-        <v>202.488208333333</v>
+        <v>179.1826684375</v>
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">D8*'Unit economics'!$F$11+D9*'Unit economics'!$F$12</f>
-        <v>398.78</v>
+        <v>352.92798125</v>
       </c>
       <c r="E13" s="26" t="n">
         <f aca="false">E8*'Unit economics'!$F$11+E9*'Unit economics'!$F$12</f>
-        <v>1000.04820833333</v>
+        <v>885.0386309375</v>
       </c>
       <c r="F13" s="26" t="n">
         <f aca="false">F8*'Unit economics'!$F$11+F9*'Unit economics'!$F$12</f>
-        <v>1993.9</v>
+        <v>1764.63990625</v>
       </c>
       <c r="G13" s="26" t="n">
         <f aca="false">G8*'Unit economics'!$F$11+G9*'Unit economics'!$F$12</f>
-        <v>3987.8</v>
+        <v>3529.2798125</v>
       </c>
       <c r="H13" s="26" t="n">
         <f aca="false">H8*'Unit economics'!$F$11+H9*'Unit economics'!$F$12</f>
-        <v>9969.5</v>
+        <v>8823.19953125</v>
       </c>
       <c r="I13" s="26" t="n">
         <f aca="false">I8*'Unit economics'!$F$11+I9*'Unit economics'!$F$12</f>
-        <v>19939</v>
+        <v>17646.3990625</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">-(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>-7.45868078512397</v>
+        <v>-6.59703301394628</v>
       </c>
       <c r="C14" s="26" t="n">
         <f aca="false">-(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>-35.1425816115702</v>
+        <v>-31.0978184891529</v>
       </c>
       <c r="D14" s="26" t="n">
         <f aca="false">-(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>-69.2097520661157</v>
+        <v>-61.2519636880165</v>
       </c>
       <c r="E14" s="26" t="n">
         <f aca="false">-(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>-173.562085743802</v>
+        <v>-153.601745865186</v>
       </c>
       <c r="F14" s="26" t="n">
         <f aca="false">-(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>-346.048760330579</v>
+        <v>-306.259818440083</v>
       </c>
       <c r="G14" s="26" t="n">
         <f aca="false">-(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
-        <v>-692.097520661157</v>
+        <v>-612.519636880165</v>
       </c>
       <c r="H14" s="26" t="n">
         <f aca="false">-(H8*'Unit economics'!$G$11+H9*'Unit economics'!$G$12)</f>
-        <v>-1730.24380165289</v>
+        <v>-1531.29909220041</v>
       </c>
       <c r="I14" s="26" t="n">
         <f aca="false">-(I8*'Unit economics'!$G$11+I9*'Unit economics'!$G$12)</f>
-        <v>-3460.48760330579</v>
+        <v>-3062.59818440083</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B22*(1-Assumptions!$B$19)*(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>2.98347231404959</v>
+        <v>2.63881320557851</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">C22*(1-Assumptions!$B$19)*(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>14.0570326446281</v>
+        <v>12.4391273956612</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">D22*(1-Assumptions!$B$19)*(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>27.6839008264463</v>
+        <v>24.5007854752066</v>
       </c>
       <c r="E15" s="26" t="n">
         <f aca="false">E22*(1-Assumptions!$B$19)*(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>69.4248342975207</v>
+        <v>61.4406983460744</v>
       </c>
       <c r="F15" s="26" t="n">
         <f aca="false">F22*(1-Assumptions!$B$19)*(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>138.419504132231</v>
+        <v>122.503927376033</v>
       </c>
       <c r="G15" s="26" t="n">
         <f aca="false">G22*(1-Assumptions!$B$19)*(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
@@ -6962,81 +7311,81 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">-(B8*'Unit economics'!$K$11+B9*'Unit economics'!$K$12)</f>
-        <v>-3.81268477933884</v>
+        <v>-3.3997175180365</v>
       </c>
       <c r="C16" s="26" t="n">
         <f aca="false">-(C8*'Unit economics'!$K$11+C9*'Unit economics'!$K$12)</f>
-        <v>-17.9609193049587</v>
+        <v>-16.0223606442679</v>
       </c>
       <c r="D16" s="26" t="n">
         <f aca="false">-(D8*'Unit economics'!$K$11+D9*'Unit economics'!$K$12)</f>
-        <v>-35.3705863140496</v>
+        <v>-31.5566078155785</v>
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">-(E8*'Unit economics'!$K$11+E9*'Unit economics'!$K$12)</f>
-        <v>-88.7020919330578</v>
+        <v>-79.1355762754249</v>
       </c>
       <c r="F16" s="26" t="n">
         <f aca="false">-(F8*'Unit economics'!$K$11+F9*'Unit economics'!$K$12)</f>
-        <v>-176.852931570248</v>
+        <v>-157.783039077893</v>
       </c>
       <c r="G16" s="26" t="n">
         <f aca="false">-(G8*'Unit economics'!$K$11+G9*'Unit economics'!$K$12)</f>
-        <v>-353.705863140496</v>
+        <v>-315.566078155785</v>
       </c>
       <c r="H16" s="26" t="n">
         <f aca="false">-(H8*'Unit economics'!$K$11+H9*'Unit economics'!$K$12)</f>
-        <v>-884.26465785124</v>
+        <v>-788.915195389463</v>
       </c>
       <c r="I16" s="26" t="n">
         <f aca="false">-(I8*'Unit economics'!$K$11+I9*'Unit economics'!$K$12)</f>
-        <v>-1768.52931570248</v>
+        <v>-1577.83039077893</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="B17" s="38" t="n">
+        <v>370</v>
+      </c>
+      <c r="B17" s="39" t="n">
         <f aca="false">B13+B14+B15+B16</f>
-        <v>34.6883150829201</v>
-      </c>
-      <c r="C17" s="38" t="n">
+        <v>30.6535386110957</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <f aca="false">C13+C14+C15+C16</f>
-        <v>163.441740061432</v>
-      </c>
-      <c r="D17" s="38" t="n">
+        <v>144.50161669974</v>
+      </c>
+      <c r="D17" s="39" t="n">
         <f aca="false">D13+D14+D15+D16</f>
-        <v>321.883562446281</v>
-      </c>
-      <c r="E17" s="38" t="n">
+        <v>284.620195221612</v>
+      </c>
+      <c r="E17" s="39" t="n">
         <f aca="false">E13+E14+E15+E16</f>
-        <v>807.208864953995</v>
-      </c>
-      <c r="F17" s="38" t="n">
+        <v>713.742007142964</v>
+      </c>
+      <c r="F17" s="39" t="n">
         <f aca="false">F13+F14+F15+F16</f>
-        <v>1609.41781223141</v>
-      </c>
-      <c r="G17" s="38" t="n">
+        <v>1423.10097610806</v>
+      </c>
+      <c r="G17" s="39" t="n">
         <f aca="false">G13+G14+G15+G16</f>
-        <v>2941.99661619835</v>
-      </c>
-      <c r="H17" s="38" t="n">
+        <v>2601.19409746405</v>
+      </c>
+      <c r="H17" s="39" t="n">
         <f aca="false">H13+H14+H15+H16</f>
-        <v>7354.99154049587</v>
-      </c>
-      <c r="I17" s="38" t="n">
+        <v>6502.98524366013</v>
+      </c>
+      <c r="I17" s="39" t="n">
         <f aca="false">I13+I14+I15+I16</f>
-        <v>14709.9830809917</v>
+        <v>13005.9704873203</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -7049,118 +7398,118 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B20" s="26" t="n">
         <f aca="false">(B13+B14)*12</f>
-        <v>426.210330578512</v>
+        <v>376.973315082645</v>
       </c>
       <c r="C20" s="26" t="n">
         <f aca="false">(C13+C14)*12</f>
-        <v>2008.14752066116</v>
+        <v>1777.01819938017</v>
       </c>
       <c r="D20" s="26" t="n">
         <f aca="false">(D13+D14)*12</f>
-        <v>3954.84297520661</v>
+        <v>3500.1122107438</v>
       </c>
       <c r="E20" s="26" t="n">
         <f aca="false">(E13+E14)*12</f>
-        <v>9917.83347107438</v>
+        <v>8777.24262086777</v>
       </c>
       <c r="F20" s="26" t="n">
         <f aca="false">(F13+F14)*12</f>
-        <v>19774.2148760331</v>
+        <v>17500.561053719</v>
       </c>
       <c r="G20" s="26" t="n">
         <f aca="false">(G13+G14)*12</f>
-        <v>39548.4297520661</v>
+        <v>35001.122107438</v>
       </c>
       <c r="H20" s="26" t="n">
         <f aca="false">(H13+H14)*12</f>
-        <v>98871.0743801653</v>
+        <v>87502.8052685951</v>
       </c>
       <c r="I20" s="26" t="n">
         <f aca="false">(I13+I14)*12</f>
-        <v>197742.148760331</v>
+        <v>175005.61053719</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="B21" s="26" t="n">
         <f aca="false">B13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>165.02864</v>
+        <v>145.9640676</v>
       </c>
       <c r="C21" s="26" t="n">
         <f aca="false">C13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>777.55472</v>
+        <v>688.0614468</v>
       </c>
       <c r="D21" s="26" t="n">
         <f aca="false">D13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>1531.3152</v>
+        <v>1355.243448</v>
       </c>
       <c r="E21" s="26" t="n">
         <f aca="false">E13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>3840.18512</v>
+        <v>3398.5483428</v>
       </c>
       <c r="F21" s="26" t="n">
         <f aca="false">F13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>7656.576</v>
+        <v>6776.21724</v>
       </c>
       <c r="G21" s="26" t="n">
         <f aca="false">G13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>15313.152</v>
+        <v>13552.43448</v>
       </c>
       <c r="H21" s="26" t="n">
         <f aca="false">H13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>38282.88</v>
+        <v>33881.0862</v>
       </c>
       <c r="I21" s="26" t="n">
         <f aca="false">I13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>76565.76</v>
+        <v>67762.1724</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="B22" s="40" t="n">
+        <v>374</v>
+      </c>
+      <c r="B22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",B20&lt;=Assumptions!$B$27,B21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="C22" s="40" t="n">
+      <c r="C22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",C20&lt;=Assumptions!$B$27,C21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="D22" s="40" t="n">
+      <c r="D22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",D20&lt;=Assumptions!$B$27,D21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",E20&lt;=Assumptions!$B$27,E21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",F20&lt;=Assumptions!$B$27,F21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="40" t="n">
+      <c r="G22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",G20&lt;=Assumptions!$B$27,G21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="40" t="n">
+      <c r="H22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",H20&lt;=Assumptions!$B$27,H21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="40" t="n">
+      <c r="I22" s="41" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",I20&lt;=Assumptions!$B$27,I21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -7173,7 +7522,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="B25" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$M$11+B9*'Unit economics'!$M$12</f>
@@ -7210,7 +7559,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">B7*Assumptions!$B$35+B10*Assumptions!$B$36</f>
@@ -7247,7 +7596,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">CHOOSE(B6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
@@ -7284,44 +7633,44 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B28" s="36" t="n">
+        <v>379</v>
+      </c>
+      <c r="B28" s="38" t="n">
         <f aca="false">B25+B26+B27</f>
         <v>235.605124</v>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="38" t="n">
         <f aca="false">C25+C26+C27</f>
         <v>246.713896</v>
       </c>
-      <c r="D28" s="36" t="n">
+      <c r="D28" s="38" t="n">
         <f aca="false">D25+D26+D27</f>
         <v>260.45438</v>
       </c>
-      <c r="E28" s="36" t="n">
+      <c r="E28" s="38" t="n">
         <f aca="false">E25+E26+E27</f>
         <v>424.896756</v>
       </c>
-      <c r="F28" s="36" t="n">
+      <c r="F28" s="38" t="n">
         <f aca="false">F25+F26+F27</f>
         <v>494.1811</v>
       </c>
-      <c r="G28" s="36" t="n">
+      <c r="G28" s="38" t="n">
         <f aca="false">G25+G26+G27</f>
         <v>633.04075</v>
       </c>
-      <c r="H28" s="36" t="n">
+      <c r="H28" s="38" t="n">
         <f aca="false">H25+H26+H27</f>
         <v>1430.87495</v>
       </c>
-      <c r="I28" s="36" t="n">
+      <c r="I28" s="38" t="n">
         <f aca="false">I25+I26+I27</f>
         <v>2125.1732</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -7334,44 +7683,44 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B31" s="36" t="n">
+        <v>381</v>
+      </c>
+      <c r="B31" s="38" t="n">
         <f aca="false">B17-B28</f>
-        <v>-200.91680891708</v>
-      </c>
-      <c r="C31" s="36" t="n">
+        <v>-204.951585388904</v>
+      </c>
+      <c r="C31" s="38" t="n">
         <f aca="false">C17-C28</f>
-        <v>-83.2721559385675</v>
-      </c>
-      <c r="D31" s="36" t="n">
+        <v>-102.21227930026</v>
+      </c>
+      <c r="D31" s="38" t="n">
         <f aca="false">D17-D28</f>
-        <v>61.429182446281</v>
-      </c>
-      <c r="E31" s="36" t="n">
+        <v>24.1658152216116</v>
+      </c>
+      <c r="E31" s="38" t="n">
         <f aca="false">E17-E28</f>
-        <v>382.312108953995</v>
-      </c>
-      <c r="F31" s="36" t="n">
+        <v>288.845251142964</v>
+      </c>
+      <c r="F31" s="38" t="n">
         <f aca="false">F17-F28</f>
-        <v>1115.23671223141</v>
-      </c>
-      <c r="G31" s="36" t="n">
+        <v>928.919876108058</v>
+      </c>
+      <c r="G31" s="38" t="n">
         <f aca="false">G17-G28</f>
-        <v>2308.95586619835</v>
-      </c>
-      <c r="H31" s="36" t="n">
+        <v>1968.15334746405</v>
+      </c>
+      <c r="H31" s="38" t="n">
         <f aca="false">H17-H28</f>
-        <v>5924.11659049587</v>
-      </c>
-      <c r="I31" s="36" t="n">
+        <v>5072.11029366013</v>
+      </c>
+      <c r="I31" s="38" t="n">
         <f aca="false">I17-I28</f>
-        <v>12584.8098809917</v>
+        <v>10880.7972873202</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="B32" s="26" t="n">
         <f aca="false">MAX(0,B31)*12</f>
@@ -7383,32 +7732,32 @@
       </c>
       <c r="D32" s="26" t="n">
         <f aca="false">MAX(0,D31)*12</f>
-        <v>737.150189355371</v>
+        <v>289.989782659339</v>
       </c>
       <c r="E32" s="26" t="n">
         <f aca="false">MAX(0,E31)*12</f>
-        <v>4587.74530744793</v>
+        <v>3466.14301371556</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">MAX(0,F31)*12</f>
-        <v>13382.8405467769</v>
+        <v>11147.0385132967</v>
       </c>
       <c r="G32" s="26" t="n">
         <f aca="false">MAX(0,G31)*12</f>
-        <v>27707.4703943802</v>
+        <v>23617.8401695686</v>
       </c>
       <c r="H32" s="26" t="n">
         <f aca="false">MAX(0,H31)*12</f>
-        <v>71089.3990859504</v>
+        <v>60865.3235239215</v>
       </c>
       <c r="I32" s="26" t="n">
         <f aca="false">MAX(0,I31)*12</f>
-        <v>151017.718571901</v>
+        <v>130569.567447843</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="B33" s="26" t="n">
         <f aca="false">IF(B32&lt;=Assumptions!$B$41,0,IF(B32&lt;Assumptions!$B$42,Assumptions!$B$43*(B32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*B32)))/12</f>
@@ -7428,135 +7777,135 @@
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">IF(F32&lt;=Assumptions!$B$41,0,IF(F32&lt;Assumptions!$B$42,Assumptions!$B$43*(F32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*F32)))/12</f>
-        <v>80.219926007438</v>
+        <v>42.0249746021519</v>
       </c>
       <c r="G33" s="26" t="n">
         <f aca="false">IF(G32&lt;=Assumptions!$B$41,0,IF(G32&lt;Assumptions!$B$42,Assumptions!$B$43*(G32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*G32)))/12</f>
-        <v>473.335952570661</v>
+        <v>403.47143623013</v>
       </c>
       <c r="H33" s="26" t="n">
         <f aca="false">IF(H32&lt;=Assumptions!$B$41,0,IF(H32&lt;Assumptions!$B$42,Assumptions!$B$43*(H32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*H32)))/12</f>
-        <v>1214.44390105165</v>
+        <v>1039.78261020033</v>
       </c>
       <c r="I33" s="26" t="n">
         <f aca="false">IF(I32&lt;=Assumptions!$B$41,0,IF(I32&lt;Assumptions!$B$42,Assumptions!$B$43*(I32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*I32)))/12</f>
-        <v>2579.88602560331</v>
+        <v>2230.56344390065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B34" s="36" t="n">
+        <v>384</v>
+      </c>
+      <c r="B34" s="38" t="n">
         <f aca="false">B31-B33</f>
-        <v>-200.91680891708</v>
-      </c>
-      <c r="C34" s="36" t="n">
+        <v>-204.951585388904</v>
+      </c>
+      <c r="C34" s="38" t="n">
         <f aca="false">C31-C33</f>
-        <v>-83.2721559385675</v>
-      </c>
-      <c r="D34" s="36" t="n">
+        <v>-102.21227930026</v>
+      </c>
+      <c r="D34" s="38" t="n">
         <f aca="false">D31-D33</f>
-        <v>61.429182446281</v>
-      </c>
-      <c r="E34" s="36" t="n">
+        <v>24.1658152216116</v>
+      </c>
+      <c r="E34" s="38" t="n">
         <f aca="false">E31-E33</f>
-        <v>382.312108953995</v>
-      </c>
-      <c r="F34" s="36" t="n">
+        <v>288.845251142964</v>
+      </c>
+      <c r="F34" s="38" t="n">
         <f aca="false">F31-F33</f>
-        <v>1035.01678622397</v>
-      </c>
-      <c r="G34" s="36" t="n">
+        <v>886.894901505906</v>
+      </c>
+      <c r="G34" s="38" t="n">
         <f aca="false">G31-G33</f>
-        <v>1835.61991362769</v>
-      </c>
-      <c r="H34" s="36" t="n">
+        <v>1564.68191123392</v>
+      </c>
+      <c r="H34" s="38" t="n">
         <f aca="false">H31-H33</f>
-        <v>4709.67268944422</v>
-      </c>
-      <c r="I34" s="36" t="n">
+        <v>4032.3276834598</v>
+      </c>
+      <c r="I34" s="38" t="n">
         <f aca="false">I31-I33</f>
-        <v>10004.9238553884</v>
+        <v>8650.2338434196</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="B35" s="26" t="n">
         <f aca="false">B34*12</f>
-        <v>-2411.00170700496</v>
+        <v>-2459.41902466685</v>
       </c>
       <c r="C35" s="26" t="n">
         <f aca="false">C34*12</f>
-        <v>-999.26587126281</v>
+        <v>-1226.54735160312</v>
       </c>
       <c r="D35" s="26" t="n">
         <f aca="false">D34*12</f>
-        <v>737.150189355371</v>
+        <v>289.989782659339</v>
       </c>
       <c r="E35" s="26" t="n">
         <f aca="false">E34*12</f>
-        <v>4587.74530744793</v>
+        <v>3466.14301371556</v>
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">F34*12</f>
-        <v>12420.2014346876</v>
+        <v>10642.7388180709</v>
       </c>
       <c r="G35" s="26" t="n">
         <f aca="false">G34*12</f>
-        <v>22027.4389635322</v>
+        <v>18776.182934807</v>
       </c>
       <c r="H35" s="26" t="n">
         <f aca="false">H34*12</f>
-        <v>56516.0722733306</v>
+        <v>48387.9322015176</v>
       </c>
       <c r="I35" s="26" t="n">
         <f aca="false">I34*12</f>
-        <v>120059.086264661</v>
+        <v>103802.806121035</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B36" s="42" t="str">
+        <v>386</v>
+      </c>
+      <c r="B36" s="43" t="str">
         <f aca="false">IF(B32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="C36" s="42" t="str">
+      <c r="C36" s="43" t="str">
         <f aca="false">IF(C32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="D36" s="42" t="str">
+      <c r="D36" s="43" t="str">
         <f aca="false">IF(D32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="E36" s="42" t="str">
+      <c r="E36" s="43" t="str">
         <f aca="false">IF(E32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="F36" s="42" t="str">
+      <c r="F36" s="43" t="str">
         <f aca="false">IF(F32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="G36" s="42" t="str">
+      <c r="G36" s="43" t="str">
         <f aca="false">IF(G32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
-      <c r="H36" s="42" t="str">
+      <c r="H36" s="43" t="str">
         <f aca="false">IF(H32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
-      <c r="I36" s="42" t="str">
+      <c r="I36" s="43" t="str">
         <f aca="false">IF(I32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -7569,7 +7918,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="B39" s="26" t="n">
         <f aca="false">IF(B5=0,0,B28/B5)</f>
@@ -7606,7 +7955,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="B40" s="26" t="n">
         <f aca="false">IF(B10=0,0,B28/B10)</f>
@@ -7643,44 +7992,44 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="B41" s="26" t="n">
         <f aca="false">IF(B10=0,0,B17/B10)</f>
-        <v>5.78138584715335</v>
+        <v>5.10892310184929</v>
       </c>
       <c r="C41" s="26" t="n">
         <f aca="false">IF(C10=0,0,C17/C10)</f>
-        <v>5.83720500219402</v>
+        <v>5.16077202499073</v>
       </c>
       <c r="D41" s="26" t="n">
         <f aca="false">IF(D10=0,0,D17/D10)</f>
-        <v>5.8524284081142</v>
+        <v>5.17491264039294</v>
       </c>
       <c r="E41" s="26" t="n">
         <f aca="false">IF(E10=0,0,E17/E10)</f>
-        <v>5.8493396011159</v>
+        <v>5.17204353002148</v>
       </c>
       <c r="F41" s="26" t="n">
         <f aca="false">IF(F10=0,0,F17/F10)</f>
-        <v>5.8524284081142</v>
+        <v>5.17491264039294</v>
       </c>
       <c r="G41" s="26" t="n">
         <f aca="false">IF(G10=0,0,G17/G10)</f>
-        <v>5.34908475672427</v>
+        <v>4.729443813571</v>
       </c>
       <c r="H41" s="26" t="n">
         <f aca="false">IF(H10=0,0,H17/H10)</f>
-        <v>5.34908475672427</v>
+        <v>4.729443813571</v>
       </c>
       <c r="I41" s="26" t="n">
         <f aca="false">IF(I10=0,0,I17/I10)</f>
-        <v>5.34908475672427</v>
+        <v>4.729443813571</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -7717,44 +8066,44 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="B43" s="27" t="n">
         <f aca="false">IF(B17=0,0,B31/B17)</f>
-        <v>-5.792060191935</v>
+        <v>-6.68606610118146</v>
       </c>
       <c r="C43" s="27" t="n">
         <f aca="false">IF(C17=0,0,C31/C17)</f>
-        <v>-0.509491369262639</v>
+        <v>-0.707343499918387</v>
       </c>
       <c r="D43" s="27" t="n">
         <f aca="false">IF(D17=0,0,D31/D17)</f>
-        <v>0.190842868705148</v>
+        <v>0.0849054832626882</v>
       </c>
       <c r="E43" s="27" t="n">
         <f aca="false">IF(E17=0,0,E31/E17)</f>
-        <v>0.473622287306996</v>
+        <v>0.404691398645824</v>
       </c>
       <c r="F43" s="27" t="n">
         <f aca="false">IF(F17=0,0,F31/F17)</f>
-        <v>0.692944183763672</v>
+        <v>0.652743474780333</v>
       </c>
       <c r="G43" s="27" t="n">
         <f aca="false">IF(G17=0,0,G31/G17)</f>
-        <v>0.784826146123167</v>
+        <v>0.756634558483289</v>
       </c>
       <c r="H43" s="27" t="n">
         <f aca="false">IF(H17=0,0,H31/H17)</f>
-        <v>0.805455255506177</v>
+        <v>0.779966446733831</v>
       </c>
       <c r="I43" s="27" t="n">
         <f aca="false">IF(I17=0,0,I31/I17)</f>
-        <v>0.855528508204326</v>
+        <v>0.836600182810512</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -7767,7 +8116,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B46" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$Q$11+B9*'Unit economics'!$Q$12</f>
@@ -7804,54 +8153,54 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B47" s="38" t="n">
+        <v>395</v>
+      </c>
+      <c r="B47" s="39" t="n">
         <f aca="false">B17-(B46+B26+B27)</f>
-        <v>-209.30404491708</v>
-      </c>
-      <c r="C47" s="38" t="n">
+        <v>-213.338821388904</v>
+      </c>
+      <c r="C47" s="39" t="n">
         <f aca="false">C17-(C46+C26+C27)</f>
-        <v>-123.002263938568</v>
-      </c>
-      <c r="D47" s="38" t="n">
+        <v>-141.94238730026</v>
+      </c>
+      <c r="D47" s="39" t="n">
         <f aca="false">D17-(D46+D26+D27)</f>
-        <v>-16.927997553719</v>
-      </c>
-      <c r="E47" s="38" t="n">
+        <v>-54.1913647783884</v>
+      </c>
+      <c r="E47" s="39" t="n">
         <f aca="false">E17-(E46+E26+E27)</f>
-        <v>185.867640953995</v>
-      </c>
-      <c r="F47" s="38" t="n">
+        <v>92.4007831429636</v>
+      </c>
+      <c r="F47" s="39" t="n">
         <f aca="false">F17-(F46+F26+F27)</f>
-        <v>723.450812231405</v>
-      </c>
-      <c r="G47" s="38" t="n">
+        <v>537.133976108058</v>
+      </c>
+      <c r="G47" s="39" t="n">
         <f aca="false">G17-(G46+G26+G27)</f>
-        <v>1525.38406619835</v>
-      </c>
-      <c r="H47" s="38" t="n">
+        <v>1184.58154746405</v>
+      </c>
+      <c r="H47" s="39" t="n">
         <f aca="false">H17-(H46+H26+H27)</f>
-        <v>3965.18709049587</v>
-      </c>
-      <c r="I47" s="38" t="n">
+        <v>3113.18079366013</v>
+      </c>
+      <c r="I47" s="39" t="n">
         <f aca="false">I17-(I46+I26+I27)</f>
-        <v>8666.95088099174</v>
+        <v>6962.93828732025</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -7884,20 +8233,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>138</v>
@@ -7906,38 +8255,38 @@
         <v>141</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
-        <v>380</v>
+      <c r="A5" s="44" t="s">
+        <v>405</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>386</v>
+      <c r="A6" s="44" t="s">
+        <v>411</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>138</v>
@@ -7946,312 +8295,328 @@
         <v>141</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>389</v>
+      <c r="A7" s="44" t="s">
+        <v>414</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>394</v>
+      <c r="A8" s="44" t="s">
+        <v>419</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
-        <v>398</v>
+      <c r="A9" s="44" t="s">
+        <v>423</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>403</v>
+      <c r="A10" s="44" t="s">
+        <v>428</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
-        <v>408</v>
+      <c r="A11" s="44" t="s">
+        <v>433</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
-        <v>412</v>
+      <c r="A12" s="44" t="s">
+        <v>437</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="s">
-        <v>414</v>
+      <c r="A13" s="44" t="s">
+        <v>439</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="s">
-        <v>419</v>
+      <c r="A14" s="44" t="s">
+        <v>444</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
-        <v>424</v>
+      <c r="A15" s="44" t="s">
+        <v>449</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
-        <v>430</v>
+      <c r="A16" s="44" t="s">
+        <v>455</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
-        <v>436</v>
+      <c r="A17" s="44" t="s">
+        <v>461</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>440</v>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="44" t="s">
+        <v>465</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>159</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43" t="s">
-        <v>445</v>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="44" t="s">
+        <v>470</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>447</v>
-      </c>
       <c r="E19" s="15" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-    </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="44" t="s">
+        <v>474</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="C24" s="29"/>
       <c r="D24" s="29"/>
@@ -8260,10 +8625,10 @@
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -8272,10 +8637,10 @@
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
@@ -8284,10 +8649,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -8296,10 +8661,10 @@
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
@@ -8308,10 +8673,10 @@
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="C29" s="29"/>
       <c r="D29" s="29"/>
@@ -8319,9 +8684,7 @@
       <c r="F29" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
+  <mergeCells count="6">
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -11,11 +11,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Pricing" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Start-up costs" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Fixed costs" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Unit economics" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Projection" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Offer review" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="AI worst case" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Start-up costs" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Fixed costs" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Unit economics" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Projection" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Offer review" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="550">
   <si>
     <t xml:space="preserve">Tsuji — cost overview</t>
   </si>
@@ -335,7 +336,7 @@
     <t xml:space="preserve">LLM cost – Pro user, worst case</t>
   </si>
   <si>
-    <t xml:space="preserve">A heavy user (3× typical). Practice plays, chatbot questions and mock exams all take a credit, so 30 credits a day caps Pro.</t>
+    <t xml:space="preserve">From 'AI worst case' (full-price tier): every AI allowance used to the full, every day.</t>
   </si>
   <si>
     <t xml:space="preserve">LLM cost – Max user, expected</t>
@@ -347,9 +348,6 @@
     <t xml:space="preserve">LLM cost – Max user, worst case</t>
   </si>
   <si>
-    <t xml:space="preserve">Every daily safety cap reached every day (photos 20, new comprehension texts 10, composition 30, questions 40). Only true while those caps exist.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Variable infrastructure – free user</t>
   </si>
   <si>
@@ -569,67 +567,241 @@
     <t xml:space="preserve">Share of payers</t>
   </si>
   <si>
+    <t xml:space="preserve">Pro price &amp; AI multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max price &amp; AI multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro monthly (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro annual (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max monthly (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro monthly: worst-case margin/mo (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro annual: worst-case margin/mo (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max monthly: worst-case margin/mo (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual: worst-case margin/mo (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every plan covers its worst case?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – Full price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium, France, Switzerland, Luxembourg, Germany, Netherlands, Nordics, UK, US, Canada, Australia, Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 – Reduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain, Italy, Portugal, Greece, Poland, Czechia, the Baltics, Korea, Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 – Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco, Algeria, Tunisia, Turkey, Romania, Brazil, Mexico, Southeast Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 – Lowest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal, Côte d'Ivoire, Cameroon and French-speaking Africa, India, Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average price paid (index)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rule: in every tier, even a subscriber using every AI allowance to the full every day must still bring in more than they cost. The margins above are that case, in the channel that keeps least (in-app or web).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The multiplier sets both the price and the AI allowances (new explanations, new exam papers, new texts, photos) in that tier: pay 45% of the price, get 45% of the allowances. Reviews, the dictionary and the credits are the same everywhere; they cost almost nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro can't go much below 45%: its 30 daily credits aren't scaled, and a user can spend them all on AI-reviewed sentences. The old tier 4 (€17.99 a year, 30%) lost money on such a user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which price applies: the store account's country in-app (Apple and Google set prices per country); on the web, the country of the card (Stripe), so a VPN doesn't unlock a cheaper price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outside the EU the stores add the local sales tax (e.g. India 18%). The margins use the EU rate as an approximation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Unit economics' and 'Projection' use the average indexes, so revenue already reflects regional prices. The shares of payers must add up to 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI worst case: a subscriber who uses every allowance to the full, every day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowances are per month at the full price (tier 1) · cheaper tiers scale them by their multiplier (Pricing) · only this sheet decides whether a price can lose money.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model prices (Gemini 3.1 Flash-Lite, the primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ per 1M tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/llm-commercial-plan.md. No batch discount in the worst case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of input served from the provider's cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cached input billed at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the full price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro credits per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 a day. The welcome bonus is paid once, so it's left out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum margin per subscriber per month, worst case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = break even; a little above leaves room for error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature (one unit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calls per unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input tokens per call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output tokens per call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per unit ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costs a Pro credit?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro allowance / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max allowance / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max ($/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowance, and what the code does today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New mock-exam paper generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro 4 / Max 8 new papers a month. Papers already in the pool stay unlimited (1 credit each on Pro). TODAY: NO LIMIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New comprehension text generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 a day (1.3 attempts each). Texts from the pool are free. TODAY: 10 a day (COMPREHENSION_DAILY_LIMIT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition review (one sentence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 30 a day, as today (COMPOSITION_DAILY_LIMIT). Pro: every credit left after papers and texts, spent here, the dearest per credit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translation review (one sentence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 40 a day. Pro: 0 here, as its credits are counted on composition. TODAY: NO LIMIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatbot question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 40 a day, as today (ASK_DAILY_LIMIT). Pro: counted on composition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explain (a sentence not already in the cache)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free, but Pro 15 / Max 30 new explanations a day; ones already in the cache stay unlimited. TODAY: NO LIMIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo reading (OCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro 10 / Max 20 a day. TODAY: 20 a day for everyone (OCR_DAILY_LIMIT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst case per month, full price ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">… in €, with the non-deductible VAT on services bought abroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By regional tier (allowances scaled by the tier's multiplier)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pro multiplier</t>
   </si>
   <si>
     <t xml:space="preserve">Max multiplier</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro monthly (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro annual (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max monthly (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max annual (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max annual margin/mo, worst case (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro annual margin/mo, expected (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 – Full price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium, France, Switzerland, Luxembourg, Germany, Netherlands, Nordics, UK, US, Canada, Australia, Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 – Reduced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain, Italy, Portugal, Greece, Poland, Czechia, the Baltics, Korea, Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 – Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco, Algeria, Tunisia, Turkey, Romania, Brazil, Mexico, Southeast Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 – Lowest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senegal, Côte d'Ivoire, Cameroon and French-speaking Africa, India, Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average price paid (index)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 'Unit economics' and 'Projection' sheets use these average indexes, so revenue already reflects regional prices. The shares of payers must add up to 100%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max has a higher floor (60%) than Pro (30%). The LLM costs the same in every country: at 50%, a Max user hitting every cap would cost more than they pay in tier 4 (see the worst-case column). Pro can go lower because credits cap its usage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which price applies: the store account's country in-app (Apple and Google set prices per country); on the web, the country of the card (Stripe), so a VPN doesn't unlock a cheaper price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outside the EU the stores add the local sales tax (e.g. India 18%). The margin columns use the EU rate as an approximation.</t>
+    <t xml:space="preserve">Pro worst case ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max worst case ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro worst case (€/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max worst case (€/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected use is far below this (Assumptions: ≈ $0.27 Pro, $0.44 Max). This sheet is a floor for prices, not a forecast.</t>
   </si>
   <si>
     <t xml:space="preserve">One-off costs to start</t>
@@ -761,10 +933,10 @@
     <t xml:space="preserve">Test devices (a used iPhone and Android phone)</t>
   </si>
   <si>
-    <t xml:space="preserve">First fill of the LLM pools (comprehension, exam papers, phrase cache)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docs/llm-commercial-plan.md §5.4: every offline job run once ≈ $4.17.</t>
+    <t xml:space="preserve">First fill of the LLM pools (exam papers, comprehension, phrase cache)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 papers for each of the 15 exam ids ≈ $17 (≈ $0.11 a paper), comprehension pool ≈ $2, phrase cache ≈ $0.20. A deep paper pool means the new-paper allowance is almost never reached.</t>
   </si>
   <si>
     <t xml:space="preserve">Payment integration (Stripe / RevenueCat)</t>
@@ -1350,25 +1522,37 @@
     <t xml:space="preserve">Pass only; practice never spends credits.</t>
   </si>
   <si>
-    <t xml:space="preserve">To build: charge 1 credit per play for Pro.</t>
+    <t xml:space="preserve">To build: 1 credit per play for Pro. Assumed: a play is one exercise the model marks or writes (one sentence reviewed, one text, one paper). If a play were a whole run, Pro's worst case would be several times higher.</t>
   </si>
   <si>
     <t xml:space="preserve">Mock exam</t>
   </si>
   <si>
-    <t xml:space="preserve">1 credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decided: 1 credit, a deliberate bargain. Exam papers are shared, so this costs little.</t>
+    <t xml:space="preserve">1 credit; 4 new papers generated a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included; 8 new papers a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass only; no limit on generating new papers (≈ $0.11 each).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decided: 1 credit. Papers already in the pool stay unlimited; only generating a new one is capped. To build: that cap, and filling the pool before launch.</t>
   </si>
   <si>
     <t xml:space="preserve">Explain button</t>
   </si>
   <si>
-    <t xml:space="preserve">Decided: free. Its LLM call is mostly served from the phrase cache.</t>
+    <t xml:space="preserve">Free; 15 new explanations a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free; 30 new a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass only; no limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decided: free. Explanations already in the cache stay unlimited; only new ones count. To build: that daily limit.</t>
   </si>
   <si>
     <r>
@@ -1417,16 +1601,16 @@
     <t xml:space="preserve">Analyser (text, photo, video)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes, 30 in history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, e.g. 100 in history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass only; history 30 for everyone (core/history.py).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick Max's history number.</t>
+    <t xml:space="preserve">Yes, 30 in history, 10 photos a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, e.g. 100 in history, 20 photos a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass only; history 30 and 20 photos a day for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick Max's history number. To build: Pro's 10 photos a day.</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -1468,9 +1652,6 @@
     <t xml:space="preserve">Deck library (publish / follow)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open to everyone.</t>
   </si>
   <si>
@@ -1507,28 +1688,25 @@
     <t xml:space="preserve">Regional prices</t>
   </si>
   <si>
-    <t xml:space="preserve">By purchasing power, 4 tiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By purchasing power, 4 tiers (floor 60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decided. Tiers and prices on the 'Pricing' sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily safety caps (LLM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Through credits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair-use caps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Photos 20, new comprehension texts 10, composition 30, questions 40, YouTube fetches 10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish them as a fair-use policy for Max.</t>
+    <t xml:space="preserve">4 tiers, 45% to 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decided. In each tier the AI allowances scale with the price, so no tier loses money ('Pricing', 'AI worst case').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI allowances (fair use)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credits + the limits above; 5 new texts a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per day: 5 new texts, 30 composition, 40 translation, 40 questions, 30 Explain, 20 photos; 8 new papers a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos 20, new texts 10, composition 30, questions 40; translation, Explain and new papers not capped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish them as Max's fair-use policy. They are what keep every subscriber profitable ('AI worst case').</t>
   </si>
   <si>
     <t xml:space="preserve">Still to do or check</t>
@@ -1538,6 +1716,9 @@
   </si>
   <si>
     <t xml:space="preserve">Grace-period reminders: when the 30 days start, 7 days before the end, and the day before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the missing AI limits before charging: new Explain calls a day, new exam papers a month, translation reviews a day (none is capped today), plus comprehension down to 5 a day, Pro photos down to 10, and every allowance scaled by the regional tier.</t>
   </si>
   <si>
     <t xml:space="preserve">Regional tiers: check the country lists and multipliers against the store price grids, and correct the shares of payers with real data after launch.</t>
@@ -1556,7 +1737,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\€#,##0.00;&quot;(€&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -1566,8 +1747,10 @@
     <numFmt numFmtId="170" formatCode="0.00"/>
     <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="172" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="0.000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="174" formatCode="\$0.0000"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1699,7 +1882,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1762,7 +1945,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1855,7 +2038,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1879,6 +2062,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1891,6 +2078,42 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1899,7 +2122,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1907,23 +2130,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1952,6 +2163,28 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1962,7 +2195,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -1988,12 +2221,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD9EAD3"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF4CCCC"/>
       <rgbColor rgb="FF4A7EBB"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2151,28 +2384,28 @@
                 <c:formatCode>\€#,##0.00;"(€"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>30.6535386110957</c:v>
+                  <c:v>30.8464295904656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>144.50161669974</c:v>
+                  <c:v>145.340177821342</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>284.620195221612</c:v>
+                  <c:v>286.23437057719</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>713.742007142964</c:v>
+                  <c:v>717.808918975722</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1423.10097610806</c:v>
+                  <c:v>1431.17185288595</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2601.19409746405</c:v>
+                  <c:v>2615.95698841653</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6502.98524366013</c:v>
+                  <c:v>6539.89247104132</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13005.9704873203</c:v>
+                  <c:v>13079.7849420826</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2307,11 +2540,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68326944"/>
-        <c:axId val="6816520"/>
+        <c:axId val="5244941"/>
+        <c:axId val="35062061"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68326944"/>
+        <c:axId val="5244941"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2377,7 +2610,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6816520"/>
+        <c:crossAx val="35062061"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2385,7 +2618,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6816520"/>
+        <c:axId val="35062061"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2461,7 +2694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68326944"/>
+        <c:crossAx val="5244941"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2789,7 +3022,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">'Start-up costs'!$I$23</f>
-        <v>963.718</v>
+        <v>979.327</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2798,7 +3031,7 @@
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">'Start-up costs'!$I$24</f>
-        <v>3713.718</v>
+        <v>3729.327</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2840,7 +3073,7 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">'Start-up costs'!$I$23+12*'Fixed costs'!$I$24</f>
-        <v>3755.9074</v>
+        <v>3771.5164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2855,7 +3088,7 @@
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">'Unit economics'!$O$11</f>
-        <v>3.70460686175344</v>
+        <v>3.76217669359229</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2864,7 +3097,7 @@
       </c>
       <c r="B20" s="6" t="n">
         <f aca="false">'Unit economics'!$O$12</f>
-        <v>7.50901709675</v>
+        <v>7.397581763</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,7 +3106,7 @@
       </c>
       <c r="B21" s="8" t="n">
         <f aca="false">'Unit economics'!$O$13</f>
-        <v>4.396317813571</v>
+        <v>4.4231594334846</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2882,7 +3115,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">'Unit economics'!$R$13</f>
-        <v>2.971641813571</v>
+        <v>1.7006933255846</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2967,35 +3200,35 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">Projection!B17</f>
-        <v>30.6535386110957</v>
+        <v>30.8464295904656</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">Projection!C17</f>
-        <v>144.50161669974</v>
+        <v>145.340177821342</v>
       </c>
       <c r="D31" s="10" t="n">
         <f aca="false">Projection!D17</f>
-        <v>284.620195221612</v>
+        <v>286.23437057719</v>
       </c>
       <c r="E31" s="10" t="n">
         <f aca="false">Projection!E17</f>
-        <v>713.742007142964</v>
+        <v>717.808918975722</v>
       </c>
       <c r="F31" s="10" t="n">
         <f aca="false">Projection!F17</f>
-        <v>1423.10097610806</v>
+        <v>1431.17185288595</v>
       </c>
       <c r="G31" s="10" t="n">
         <f aca="false">Projection!G17</f>
-        <v>2601.19409746405</v>
+        <v>2615.95698841653</v>
       </c>
       <c r="H31" s="10" t="n">
         <f aca="false">Projection!H17</f>
-        <v>6502.98524366013</v>
+        <v>6539.89247104132</v>
       </c>
       <c r="I31" s="10" t="n">
         <f aca="false">Projection!I17</f>
-        <v>13005.9704873203</v>
+        <v>13079.7849420826</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3057,19 +3290,19 @@
       </c>
       <c r="F33" s="10" t="n">
         <f aca="false">Projection!F33</f>
-        <v>42.0249746021519</v>
+        <v>43.6795043416197</v>
       </c>
       <c r="G33" s="10" t="n">
         <f aca="false">Projection!G33</f>
-        <v>403.47143623013</v>
+        <v>406.497828875388</v>
       </c>
       <c r="H33" s="10" t="n">
         <f aca="false">Projection!H33</f>
-        <v>1039.78261020033</v>
+        <v>1047.34859181347</v>
       </c>
       <c r="I33" s="10" t="n">
         <f aca="false">Projection!I33</f>
-        <v>2230.56344390065</v>
+        <v>2245.69540712694</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3078,35 +3311,35 @@
       </c>
       <c r="B34" s="10" t="n">
         <f aca="false">Projection!B34</f>
-        <v>-204.951585388904</v>
+        <v>-204.758694409534</v>
       </c>
       <c r="C34" s="10" t="n">
         <f aca="false">Projection!C34</f>
-        <v>-102.21227930026</v>
+        <v>-101.373718178658</v>
       </c>
       <c r="D34" s="10" t="n">
         <f aca="false">Projection!D34</f>
-        <v>24.1658152216116</v>
+        <v>25.77999057719</v>
       </c>
       <c r="E34" s="10" t="n">
         <f aca="false">Projection!E34</f>
-        <v>288.845251142964</v>
+        <v>292.912162975722</v>
       </c>
       <c r="F34" s="10" t="n">
         <f aca="false">Projection!F34</f>
-        <v>886.894901505906</v>
+        <v>893.31124854433</v>
       </c>
       <c r="G34" s="10" t="n">
         <f aca="false">Projection!G34</f>
-        <v>1564.68191123392</v>
+        <v>1576.41840954114</v>
       </c>
       <c r="H34" s="10" t="n">
         <f aca="false">Projection!H34</f>
-        <v>4032.3276834598</v>
+        <v>4061.66892922785</v>
       </c>
       <c r="I34" s="10" t="n">
         <f aca="false">Projection!I34</f>
-        <v>8650.2338434196</v>
+        <v>8708.9163349557</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3653,7 +3886,8 @@
         <v>101</v>
       </c>
       <c r="B32" s="23" t="n">
-        <v>1.33</v>
+        <f aca="false">'AI worst case'!$I$19</f>
+        <v>2.4902885</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>99</v>
@@ -3680,19 +3914,20 @@
       <c r="A34" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="22" t="n">
-        <v>3.2</v>
+      <c r="B34" s="23" t="n">
+        <f aca="false">'AI worst case'!$J$19</f>
+        <v>4.8380575</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>99</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B35" s="19" t="n">
         <v>0.01</v>
@@ -3701,12 +3936,12 @@
         <v>49</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="19" t="n">
         <v>0.02</v>
@@ -3715,12 +3950,12 @@
         <v>49</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3728,33 +3963,33 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B38" s="24" t="n">
         <v>2000</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="24" t="n">
         <v>20000</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3762,35 +3997,35 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B41" s="19" t="n">
         <v>8687.04</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>118</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B42" s="19" t="n">
         <v>17374.08</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B43" s="18" t="n">
         <v>0.205</v>
@@ -3799,26 +4034,26 @@
         <v>43</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B44" s="19" t="n">
         <v>925.59</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>125</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3837,58 +4072,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>8</v>
@@ -3912,10 +4149,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" s="19" t="n">
         <v>52</v>
@@ -3943,10 +4180,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>12</v>
@@ -3970,10 +4207,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>65</v>
@@ -4001,7 +4238,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4013,7 +4250,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" s="26" t="n">
         <f aca="false">D8-D6</f>
@@ -4022,7 +4259,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="26" t="n">
         <f aca="false">(D8-D6)/12</f>
@@ -4031,7 +4268,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">D7-D5</f>
@@ -4040,12 +4277,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4057,109 +4294,109 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="E17" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>299</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>89</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>299</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="23" t="s">
+      <c r="E19" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="E19" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="29" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>109.99</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>109.99</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="C21" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4173,117 +4410,117 @@
       <c r="A24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
+      <c r="B24" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
+      <c r="B25" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
+      <c r="B26" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
+      <c r="B27" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
+      <c r="B28" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
+      <c r="B29" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
+      <c r="B30" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="B31" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -4295,56 +4532,68 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="C34" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="E34" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="F34" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="G34" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="H34" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="I34" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="J34" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="K34" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="K34" s="13" t="s">
+      <c r="L34" s="13" t="s">
         <v>187</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C35" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="16" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="26" t="n">
@@ -4364,28 +4613,40 @@
         <v>99.99</v>
       </c>
       <c r="J35" s="26" t="n">
-        <f aca="false">I35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>2.50348909090909</v>
+        <f aca="false">MIN(F35/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F35/(1+Assumptions!$B$7)-(F35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$25-Assumptions!$B$36</f>
+        <v>3.70389504309835</v>
       </c>
       <c r="K35" s="26" t="n">
-        <f aca="false">G35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>3.21084929476584</v>
+        <f aca="false">MIN(G35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G35/(1+Assumptions!$B$7)-(G35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$25-Assumptions!$B$36</f>
+        <v>0.90041708166584</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <f aca="false">MIN(H35/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H35/(1+Assumptions!$B$7)-(H35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$25-Assumptions!$B$36</f>
+        <v>5.4756826547562</v>
+      </c>
+      <c r="M35" s="26" t="n">
+        <f aca="false">MIN(I35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(I35/(1+Assumptions!$B$7)-(I35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$G$25-Assumptions!$B$36</f>
+        <v>0.79892645640909</v>
+      </c>
+      <c r="N35" s="7" t="str">
+        <f aca="false">IF(MIN(J35:M35)&gt;='AI worst case'!$B$10,"yes","NO: raise the price or lower the allowance")</f>
+        <v>yes</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C36" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="F36" s="26" t="n">
@@ -4405,29 +4666,41 @@
         <v>74.99</v>
       </c>
       <c r="J36" s="26" t="n">
-        <f aca="false">I36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>1.03999046831956</v>
+        <f aca="false">MIN(F36/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F36/(1+Assumptions!$B$7)-(F36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$26-Assumptions!$B$36</f>
+        <v>2.7853728480324</v>
       </c>
       <c r="K36" s="26" t="n">
-        <f aca="false">G36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>2.33275012121212</v>
+        <f aca="false">MIN(G36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G36/(1+Assumptions!$B$7)-(G36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$26-Assumptions!$B$36</f>
+        <v>0.508754390732122</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <f aca="false">MIN(H36/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H36/(1+Assumptions!$B$7)-(H36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$26-Assumptions!$B$36</f>
+        <v>4.63011907094727</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <f aca="false">MIN(I36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(I36/(1+Assumptions!$B$7)-(I36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$G$26-Assumptions!$B$36</f>
+        <v>0.597302266539558</v>
+      </c>
+      <c r="N36" s="7" t="str">
+        <f aca="false">IF(MIN(J36:M36)&gt;='AI worst case'!$B$10,"yes","NO: raise the price or lower the allowance")</f>
+        <v>yes</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C37" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D37" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>0.6</v>
+      <c r="D37" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.55</v>
       </c>
       <c r="F37" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D37,1)-0.01)</f>
@@ -4435,7 +4708,7 @@
       </c>
       <c r="G37" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D37,1)-0.01)</f>
-        <v>29.99</v>
+        <v>32.99</v>
       </c>
       <c r="H37" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E37,1)-0.01)</f>
@@ -4443,93 +4716,127 @@
       </c>
       <c r="I37" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E37,1)-0.01)</f>
-        <v>59.99</v>
+        <v>54.99</v>
       </c>
       <c r="J37" s="26" t="n">
-        <f aca="false">I37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>0.16189129476584</v>
+        <f aca="false">MIN(F37/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F37/(1+Assumptions!$B$7)-(F37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$27-Assumptions!$B$36</f>
+        <v>1.78971701044645</v>
       </c>
       <c r="K37" s="26" t="n">
-        <f aca="false">G37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>1.4546509476584</v>
+        <f aca="false">MIN(G37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G37/(1+Assumptions!$B$7)-(G37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$27-Assumptions!$B$36</f>
+        <v>0.215577891989146</v>
+      </c>
+      <c r="L37" s="26" t="n">
+        <f aca="false">MIN(H37/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H37/(1+Assumptions!$B$7)-(H37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$27-Assumptions!$B$36</f>
+        <v>3.57546075711835</v>
+      </c>
+      <c r="M37" s="26" t="n">
+        <f aca="false">MIN(I37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(I37/(1+Assumptions!$B$7)-(I37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$G$27-Assumptions!$B$36</f>
+        <v>0.479283071167935</v>
+      </c>
+      <c r="N37" s="7" t="str">
+        <f aca="false">IF(MIN(J37:M37)&gt;='AI worst case'!$B$10,"yes","NO: raise the price or lower the allowance")</f>
+        <v>yes</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C38" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="D38" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>0.6</v>
+      <c r="D38" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.45</v>
       </c>
       <c r="F38" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$10*D38,1)-0.01)</f>
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
       <c r="G38" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$11*D38,1)-0.01)</f>
-        <v>17.99</v>
+        <v>26.99</v>
       </c>
       <c r="H38" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$12*E38,1)-0.01)</f>
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="I38" s="26" t="n">
         <f aca="false">MAX(0.99,CEILING(Assumptions!$B$13*E38,1)-0.01)</f>
-        <v>59.99</v>
+        <v>44.99</v>
       </c>
       <c r="J38" s="26" t="n">
-        <f aca="false">I38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>0.16189129476584</v>
+        <f aca="false">MIN(F38/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F38/(1+Assumptions!$B$7)-(F38*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$28-Assumptions!$B$36</f>
+        <v>2.05135636919645</v>
       </c>
       <c r="K38" s="26" t="n">
-        <f aca="false">G38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)-Assumptions!$B$36</f>
-        <v>0.752171608815427</v>
+        <f aca="false">MIN(G38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G38/(1+Assumptions!$B$7)-(G38*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$28-Assumptions!$B$36</f>
+        <v>0.125977581317658</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <f aca="false">MIN(H38/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H38/(1+Assumptions!$B$7)-(H38*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$28-Assumptions!$B$36</f>
+        <v>2.6968919307824</v>
+      </c>
+      <c r="M38" s="26" t="n">
+        <f aca="false">MIN(I38/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(I38/(1+Assumptions!$B$7)-(I38*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$G$28-Assumptions!$B$36</f>
+        <v>0.420273473482121</v>
+      </c>
+      <c r="N38" s="7" t="str">
+        <f aca="false">IF(MIN(J38:M38)&gt;='AI worst case'!$B$10,"yes","NO: raise the price or lower the allowance")</f>
+        <v>yes</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C39" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="C39" s="31" t="n">
         <f aca="false">SUM(C35:C38)</f>
         <v>1</v>
       </c>
-      <c r="D39" s="31" t="n">
+      <c r="D39" s="32" t="n">
         <f aca="false">IF(C39=0,1,SUMPRODUCT(C35:C38,D35:D38)/C39)</f>
-        <v>0.8775</v>
-      </c>
-      <c r="E39" s="31" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E39" s="32" t="n">
         <f aca="false">IF(C39=0,1,SUMPRODUCT(C35:C38,E35:E38)/C39)</f>
-        <v>0.9025</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4543,6 +4850,14 @@
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B31:H31"/>
   </mergeCells>
+  <conditionalFormatting sqref="J35:M38">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>'AI worst case'!$B$10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>'AI worst case'!$B$10</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4554,6 +4869,625 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="80"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>900</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <f aca="false">B12*(C12*$B$5*(1-$B$7+$B$7*$B$8)+D12*$B$6)/1000000</f>
+        <v>0.1102325</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <f aca="false">G12*E12</f>
+        <v>0.44093</v>
+      </c>
+      <c r="J12" s="35" t="n">
+        <f aca="false">H12*E12</f>
+        <v>0.88186</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <f aca="false">B13*(C13*$B$5*(1-$B$7+$B$7*$B$8)+D13*$B$6)/1000000</f>
+        <v>0.00625365</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <f aca="false">G13*E13</f>
+        <v>0.9380475</v>
+      </c>
+      <c r="J13" s="35" t="n">
+        <f aca="false">H13*E13</f>
+        <v>0.9380475</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>900</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <f aca="false">B14*(C14*$B$5*(1-$B$7+$B$7*$B$8)+D14*$B$6)/1000000</f>
+        <v>0.0007035</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G14" s="36" t="n">
+        <f aca="false">MAX(0,$B$9-G12-G13)</f>
+        <v>746</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>900</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <f aca="false">G14*E14</f>
+        <v>0.524811</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <f aca="false">H14*E14</f>
+        <v>0.63315</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>600</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="E15" s="34" t="n">
+        <f aca="false">B15*(C15*$B$5*(1-$B$7+$B$7*$B$8)+D15*$B$6)/1000000</f>
+        <v>0.000669</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <f aca="false">G15*E15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <f aca="false">H15*E15</f>
+        <v>0.8028</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <f aca="false">B16*(C16*$B$5*(1-$B$7+$B$7*$B$8)+D16*$B$6)/1000000</f>
+        <v>0.000341</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <f aca="false">G16*E16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <f aca="false">H16*E16</f>
+        <v>0.4092</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="34" t="n">
+        <f aca="false">B17*(C17*$B$5*(1-$B$7+$B$7*$B$8)+D17*$B$6)/1000000</f>
+        <v>0.000796</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>450</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>900</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <f aca="false">G17*E17</f>
+        <v>0.3582</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <f aca="false">H17*E17</f>
+        <v>0.7164</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="34" t="n">
+        <f aca="false">B18*(C18*$B$5*(1-$B$7+$B$7*$B$8)+D18*$B$6)/1000000</f>
+        <v>0.000761</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>600</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <f aca="false">G18*E18</f>
+        <v>0.2283</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <f aca="false">H18*E18</f>
+        <v>0.4566</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I19" s="37" t="n">
+        <f aca="false">SUM(I12:I18)</f>
+        <v>2.4902885</v>
+      </c>
+      <c r="J19" s="37" t="n">
+        <f aca="false">SUM(J12:J18)</f>
+        <v>4.8380575</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I20" s="38" t="n">
+        <f aca="false">I19*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.5913942131</v>
+      </c>
+      <c r="J20" s="38" t="n">
+        <f aca="false">J19*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>5.0344826345</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="39" t="str">
+        <f aca="false">Pricing!A35</f>
+        <v>1 – Full price</v>
+      </c>
+      <c r="B25" s="40" t="n">
+        <f aca="false">Pricing!D35</f>
+        <v>1</v>
+      </c>
+      <c r="C25" s="40" t="n">
+        <f aca="false">Pricing!E35</f>
+        <v>1</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <f aca="false">ROUNDDOWN(G12*B25,0)*E12+ROUNDDOWN(G13*B25,0)*E13+MAX(0,$B$9-ROUNDDOWN(G12*B25,0)-ROUNDDOWN(G13*B25,0))*E14+ROUNDDOWN(G17*B25,0)*E17+ROUNDDOWN(G18*B25,0)*E18</f>
+        <v>2.4902885</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <f aca="false">ROUNDDOWN(H12*C25,0)*E12+ROUNDDOWN(H13*C25,0)*E13+ROUNDDOWN(H14*C25,0)*E14+ROUNDDOWN(H15*C25,0)*E15+ROUNDDOWN(H16*C25,0)*E16+ROUNDDOWN(H17*C25,0)*E17+ROUNDDOWN(H18*C25,0)*E18</f>
+        <v>4.8380575</v>
+      </c>
+      <c r="F25" s="41" t="n">
+        <f aca="false">D25*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.5913942131</v>
+      </c>
+      <c r="G25" s="41" t="n">
+        <f aca="false">E25*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>5.0344826345</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="39" t="str">
+        <f aca="false">Pricing!A36</f>
+        <v>2 – Reduced</v>
+      </c>
+      <c r="B26" s="40" t="n">
+        <f aca="false">Pricing!D36</f>
+        <v>0.75</v>
+      </c>
+      <c r="C26" s="40" t="n">
+        <f aca="false">Pricing!E36</f>
+        <v>0.75</v>
+      </c>
+      <c r="D26" s="35" t="n">
+        <f aca="false">ROUNDDOWN(G12*B26,0)*E12+ROUNDDOWN(G13*B26,0)*E13+MAX(0,$B$9-ROUNDDOWN(G12*B26,0)-ROUNDDOWN(G13*B26,0))*E14+ROUNDDOWN(G17*B26,0)*E17+ROUNDDOWN(G18*B26,0)*E18</f>
+        <v>2.0228308</v>
+      </c>
+      <c r="E26" s="35" t="n">
+        <f aca="false">ROUNDDOWN(H12*C26,0)*E12+ROUNDDOWN(H13*C26,0)*E13+ROUNDDOWN(H14*C26,0)*E14+ROUNDDOWN(H15*C26,0)*E15+ROUNDDOWN(H16*C26,0)*E16+ROUNDDOWN(H17*C26,0)*E17+ROUNDDOWN(H18*C26,0)*E18</f>
+        <v>3.6254163</v>
+      </c>
+      <c r="F26" s="41" t="n">
+        <f aca="false">D26*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.10495773048</v>
+      </c>
+      <c r="G26" s="41" t="n">
+        <f aca="false">E26*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>3.77260820178</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="39" t="str">
+        <f aca="false">Pricing!A37</f>
+        <v>3 – Low</v>
+      </c>
+      <c r="B27" s="40" t="n">
+        <f aca="false">Pricing!D37</f>
+        <v>0.55</v>
+      </c>
+      <c r="C27" s="40" t="n">
+        <f aca="false">Pricing!E37</f>
+        <v>0.55</v>
+      </c>
+      <c r="D27" s="35" t="n">
+        <f aca="false">ROUNDDOWN(G12*B27,0)*E12+ROUNDDOWN(G13*B27,0)*E13+MAX(0,$B$9-ROUNDDOWN(G12*B27,0)-ROUNDDOWN(G13*B27,0))*E14+ROUNDDOWN(G17*B27,0)*E17+ROUNDDOWN(G18*B27,0)*E18</f>
+        <v>1.6294973</v>
+      </c>
+      <c r="E27" s="35" t="n">
+        <f aca="false">ROUNDDOWN(H12*C27,0)*E12+ROUNDDOWN(H13*C27,0)*E13+ROUNDDOWN(H14*C27,0)*E14+ROUNDDOWN(H15*C27,0)*E15+ROUNDDOWN(H16*C27,0)*E16+ROUNDDOWN(H17*C27,0)*E17+ROUNDDOWN(H18*C27,0)*E18</f>
+        <v>2.6137118</v>
+      </c>
+      <c r="F27" s="41" t="n">
+        <f aca="false">D27*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>1.69565489038</v>
+      </c>
+      <c r="G27" s="41" t="n">
+        <f aca="false">E27*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.71982849908</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="39" t="str">
+        <f aca="false">Pricing!A38</f>
+        <v>4 – Lowest</v>
+      </c>
+      <c r="B28" s="40" t="n">
+        <f aca="false">Pricing!D38</f>
+        <v>0.45</v>
+      </c>
+      <c r="C28" s="40" t="n">
+        <f aca="false">Pricing!E38</f>
+        <v>0.45</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <f aca="false">ROUNDDOWN(G12*B28,0)*E12+ROUNDDOWN(G13*B28,0)*E13+MAX(0,$B$9-ROUNDDOWN(G12*B28,0)-ROUNDDOWN(G13*B28,0))*E14+ROUNDDOWN(G17*B28,0)*E17+ROUNDDOWN(G18*B28,0)*E18</f>
+        <v>1.37806605</v>
+      </c>
+      <c r="E28" s="35" t="n">
+        <f aca="false">ROUNDDOWN(H12*C28,0)*E12+ROUNDDOWN(H13*C28,0)*E13+ROUNDDOWN(H14*C28,0)*E14+ROUNDDOWN(H15*C28,0)*E15+ROUNDDOWN(H16*C28,0)*E16+ROUNDDOWN(H17*C28,0)*E17+ROUNDDOWN(H18*C28,0)*E18</f>
+        <v>2.10785955</v>
+      </c>
+      <c r="F28" s="41" t="n">
+        <f aca="false">D28*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>1.43401553163</v>
+      </c>
+      <c r="G28" s="41" t="n">
+        <f aca="false">E28*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.19343864773</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4574,69 +5508,69 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="D5" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="44" t="n">
         <v>111.5</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="44" t="n">
         <v>111.5</v>
       </c>
-      <c r="G5" s="34" t="n">
+      <c r="G5" s="44" t="n">
         <v>111.5</v>
       </c>
       <c r="H5" s="26" t="n">
@@ -4652,29 +5586,29 @@
         <v>111.5</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="34" t="n">
+      <c r="D6" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="26" t="n">
@@ -4690,29 +5624,29 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E7" s="34" t="n">
+      <c r="D7" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="44" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="26" t="n">
@@ -4728,29 +5662,29 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" s="34" t="n">
+      <c r="D8" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="26" t="n">
@@ -4766,29 +5700,29 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E9" s="34" t="n">
+        <v>272</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>1000</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="44" t="n">
         <v>1400</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="44" t="n">
         <v>2000</v>
       </c>
       <c r="H9" s="26" t="n">
@@ -4804,29 +5738,29 @@
         <v>2000</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="34" t="n">
+      <c r="D10" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>271</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="44" t="n">
         <v>271</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="44" t="n">
         <v>271</v>
       </c>
       <c r="H10" s="26" t="n">
@@ -4842,29 +5776,29 @@
         <v>271</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>228</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" s="34" t="n">
+        <v>272</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="44" t="n">
         <v>900</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="44" t="n">
         <v>900</v>
       </c>
       <c r="H11" s="26" t="n">
@@ -4880,29 +5814,29 @@
         <v>900</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E12" s="34" t="n">
+        <v>272</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="44" t="n">
         <v>500</v>
       </c>
       <c r="H12" s="26" t="n">
@@ -4918,29 +5852,29 @@
         <v>500</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E13" s="34" t="n">
+      <c r="D13" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="44" t="n">
         <v>400</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="44" t="n">
         <v>1500</v>
       </c>
       <c r="H13" s="26" t="n">
@@ -4956,29 +5890,29 @@
         <v>1500</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C14" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C14" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E14" s="34" t="n">
+      <c r="D14" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="44" t="n">
         <v>300</v>
       </c>
       <c r="H14" s="26" t="n">
@@ -4994,29 +5928,29 @@
         <v>300</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" s="34" t="n">
+      <c r="D15" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="44" t="n">
         <v>25</v>
       </c>
       <c r="H15" s="26" t="n">
@@ -5032,29 +5966,29 @@
         <v>26.015</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E16" s="34" t="n">
+        <v>295</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="44" t="n">
         <v>700</v>
       </c>
       <c r="H16" s="26" t="n">
@@ -5070,29 +6004,29 @@
         <v>700</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E17" s="34" t="n">
+        <v>295</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="44" t="n">
         <v>400</v>
       </c>
       <c r="H17" s="26" t="n">
@@ -5109,64 +6043,64 @@
       </c>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C18" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E18" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="34" t="n">
+      <c r="D18" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="44" t="n">
         <v>10</v>
+      </c>
+      <c r="F18" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="44" t="n">
+        <v>40</v>
       </c>
       <c r="H18" s="26" t="n">
         <f aca="false">E18*IF($D18="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)</f>
-        <v>4.1624</v>
+        <v>10.406</v>
       </c>
       <c r="I18" s="26" t="n">
         <f aca="false">F18*IF($D18="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)</f>
-        <v>5.203</v>
+        <v>20.812</v>
       </c>
       <c r="J18" s="26" t="n">
         <f aca="false">G18*IF($D18="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)</f>
-        <v>10.406</v>
+        <v>41.624</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C19" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="34" t="n">
+      <c r="D19" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="44" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="26" t="n">
@@ -5182,29 +6116,29 @@
         <v>0</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>247</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E20" s="34" t="n">
+      <c r="D20" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="44" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="26" t="n">
@@ -5220,29 +6154,29 @@
         <v>0</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E21" s="34" t="n">
+        <v>308</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E21" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="44" t="n">
         <v>300</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="44" t="n">
         <v>1500</v>
       </c>
       <c r="H21" s="26" t="n">
@@ -5258,41 +6192,41 @@
         <v>1500</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H23" s="35" t="n">
+        <v>310</v>
+      </c>
+      <c r="H23" s="45" t="n">
         <f aca="false">SUMIFS(H5:H21,$C$5:$C$21,"Y")</f>
-        <v>412.6774</v>
-      </c>
-      <c r="I23" s="35" t="n">
+        <v>418.921</v>
+      </c>
+      <c r="I23" s="45" t="n">
         <f aca="false">SUMIFS(I5:I21,$C$5:$C$21,"Y")</f>
-        <v>963.718</v>
-      </c>
-      <c r="J23" s="35" t="n">
+        <v>979.327</v>
+      </c>
+      <c r="J23" s="45" t="n">
         <f aca="false">SUMIFS(J5:J21,$C$5:$C$21,"Y")</f>
-        <v>2218.921</v>
+        <v>2250.139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="H24" s="35" t="n">
+        <v>311</v>
+      </c>
+      <c r="H24" s="45" t="n">
         <f aca="false">SUM(H5:H21)</f>
-        <v>2312.6774</v>
-      </c>
-      <c r="I24" s="35" t="n">
+        <v>2318.921</v>
+      </c>
+      <c r="I24" s="45" t="n">
         <f aca="false">SUM(I5:I21)</f>
-        <v>3713.718</v>
-      </c>
-      <c r="J24" s="35" t="n">
+        <v>3729.327</v>
+      </c>
+      <c r="J24" s="45" t="n">
         <f aca="false">SUM(J5:J21)</f>
-        <v>8218.921</v>
+        <v>8250.139</v>
       </c>
     </row>
   </sheetData>
@@ -5306,7 +6240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5323,75 +6257,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C5" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="34" t="n">
+      <c r="D5" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="34" t="n">
+      <c r="G5" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="34" t="n">
+      <c r="H5" s="44" t="n">
         <v>85</v>
       </c>
       <c r="I5" s="26" t="n">
@@ -5407,32 +6341,32 @@
         <v>88.451</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="34" t="n">
+      <c r="D6" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" s="44" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="44" t="n">
         <v>1.25</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="44" t="n">
         <v>5</v>
       </c>
       <c r="I6" s="26" t="n">
@@ -5448,32 +6382,32 @@
         <v>5.203</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="34" t="n">
+      <c r="D7" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F7" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="H7" s="34" t="n">
+      <c r="H7" s="44" t="n">
         <v>25</v>
       </c>
       <c r="I7" s="26" t="n">
@@ -5489,32 +6423,32 @@
         <v>26.015</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C8" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="34" t="n">
+      <c r="D8" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="34" t="n">
+      <c r="H8" s="44" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="26" t="n">
@@ -5530,32 +6464,32 @@
         <v>19.7714</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="34" t="n">
+      <c r="D9" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F9" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="44" t="n">
         <v>20</v>
       </c>
       <c r="I9" s="26" t="n">
@@ -5571,32 +6505,32 @@
         <v>20.812</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C10" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="34" t="n">
+      <c r="D10" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F10" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="H10" s="34" t="n">
+      <c r="H10" s="44" t="n">
         <v>75</v>
       </c>
       <c r="I10" s="26" t="n">
@@ -5612,32 +6546,32 @@
         <v>78.045</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C11" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="34" t="n">
+      <c r="D11" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F11" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="H11" s="34" t="n">
+      <c r="H11" s="44" t="n">
         <v>20</v>
       </c>
       <c r="I11" s="26" t="n">
@@ -5653,32 +6587,32 @@
         <v>20.812</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C12" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="34" t="n">
+      <c r="D12" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="44" t="n">
         <v>26</v>
       </c>
       <c r="I12" s="26" t="n">
@@ -5694,32 +6628,32 @@
         <v>27.0556</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="34" t="n">
+      <c r="D13" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F13" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="44" t="n">
         <v>10</v>
       </c>
       <c r="I13" s="26" t="n">
@@ -5735,32 +6669,32 @@
         <v>10.406</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="34" t="n">
+        <v>340</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F14" s="44" t="n">
         <v>3.5</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="34" t="n">
+      <c r="H14" s="44" t="n">
         <v>14</v>
       </c>
       <c r="I14" s="26" t="n">
@@ -5776,32 +6710,32 @@
         <v>14.5684</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="C15" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F15" s="34" t="n">
+      <c r="D15" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F15" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="44" t="n">
         <v>15</v>
       </c>
       <c r="I15" s="26" t="n">
@@ -5817,32 +6751,32 @@
         <v>1.30075</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="C16" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" s="34" t="n">
+      <c r="D16" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F16" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="34" t="n">
+      <c r="H16" s="44" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="26" t="n">
@@ -5858,32 +6792,32 @@
         <v>7</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C17" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="F17" s="34" t="n">
+      <c r="D17" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="44" t="n">
         <v>99</v>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="44" t="n">
         <v>99</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="44" t="n">
         <v>99</v>
       </c>
       <c r="I17" s="26" t="n">
@@ -5899,32 +6833,32 @@
         <v>8.58495</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>295</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C18" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="34" t="n">
+      <c r="D18" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="44" t="n">
         <v>200</v>
       </c>
       <c r="I18" s="26" t="n">
@@ -5940,32 +6874,32 @@
         <v>200</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C19" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="C19" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="34" t="n">
+      <c r="D19" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F19" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="44" t="n">
         <v>15</v>
       </c>
       <c r="I19" s="26" t="n">
@@ -5981,32 +6915,32 @@
         <v>15</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E20" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F20" s="34" t="n">
+        <v>354</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="44" t="n">
         <v>40</v>
       </c>
       <c r="I20" s="26" t="n">
@@ -6022,32 +6956,32 @@
         <v>40</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C21" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="C21" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F21" s="36" t="n">
+      <c r="D21" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F21" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="46" t="n">
         <v>200</v>
       </c>
       <c r="I21" s="26" t="n">
@@ -6063,32 +6997,32 @@
         <v>208.12</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F22" s="34" t="n">
+        <v>308</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F22" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G22" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="44" t="n">
         <v>1000</v>
       </c>
       <c r="I22" s="26" t="n">
@@ -6104,809 +7038,63 @@
         <v>1000</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="I24" s="35" t="n">
+        <v>364</v>
+      </c>
+      <c r="I24" s="45" t="n">
         <f aca="false">SUMIFS(I5:I22,$C$5:$C$22,"Y")</f>
         <v>232.68245</v>
       </c>
-      <c r="J24" s="35" t="n">
+      <c r="J24" s="45" t="n">
         <f aca="false">SUMIFS(J5:J22,$C$5:$C$22,"Y")</f>
         <v>355.32145</v>
       </c>
-      <c r="K24" s="35" t="n">
+      <c r="K24" s="45" t="n">
         <f aca="false">SUMIFS(K5:K22,$C$5:$C$22,"Y")</f>
         <v>736.5767</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="I25" s="35" t="n">
+        <v>365</v>
+      </c>
+      <c r="I25" s="45" t="n">
         <f aca="false">I24*12</f>
         <v>2792.1894</v>
       </c>
-      <c r="J25" s="35" t="n">
+      <c r="J25" s="45" t="n">
         <f aca="false">J24*12</f>
         <v>4263.8574</v>
       </c>
-      <c r="K25" s="35" t="n">
+      <c r="K25" s="45" t="n">
         <f aca="false">K24*12</f>
         <v>8838.9204</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I26" s="35" t="n">
+        <v>366</v>
+      </c>
+      <c r="I26" s="45" t="n">
         <f aca="false">SUM(I5:I22)</f>
         <v>236.32455</v>
       </c>
-      <c r="J26" s="35" t="n">
+      <c r="J26" s="45" t="n">
         <f aca="false">SUM(J5:J22)</f>
         <v>587.60565</v>
       </c>
-      <c r="K26" s="35" t="n">
+      <c r="K26" s="45" t="n">
         <f aca="false">SUM(K5:K22)</f>
         <v>1791.1451</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>310</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:S29"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="3" style="0" width="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <f aca="false">Assumptions!$B$10*Pricing!$D$39</f>
-        <v>7.888725</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="37" t="n">
-        <f aca="false">1/D5</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <f aca="false">C5/D5</f>
-        <v>7.888725</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <f aca="false">F5-H5</f>
-        <v>1.36911756198347</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <f aca="false">F5/(1+Assumptions!$B$7)</f>
-        <v>6.51960743801653</v>
-      </c>
-      <c r="I5" s="26" t="n">
-        <f aca="false">H5*Assumptions!$B$21</f>
-        <v>0.977941115702479</v>
-      </c>
-      <c r="J5" s="26" t="n">
-        <f aca="false">F5*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E5</f>
-        <v>0.42355195</v>
-      </c>
-      <c r="K5" s="26" t="n">
-        <f aca="false">Assumptions!$B$19*I5+(1-Assumptions!$B$19)*J5</f>
-        <v>0.756185449421488</v>
-      </c>
-      <c r="L5" s="26" t="n">
-        <f aca="false">H5-K5</f>
-        <v>5.76342198859504</v>
-      </c>
-      <c r="M5" s="26" t="n">
-        <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.280962</v>
-      </c>
-      <c r="N5" s="26" t="n">
-        <f aca="false">Assumptions!$B$36</f>
-        <v>0.02</v>
-      </c>
-      <c r="O5" s="26" t="n">
-        <f aca="false">L5-M5-N5</f>
-        <v>5.46245998859504</v>
-      </c>
-      <c r="P5" s="27" t="n">
-        <f aca="false">IF(F5=0,0,O5/F5)</f>
-        <v>0.692438890770694</v>
-      </c>
-      <c r="Q5" s="26" t="n">
-        <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>1.383998</v>
-      </c>
-      <c r="R5" s="26" t="n">
-        <f aca="false">L5-Q5-N5</f>
-        <v>4.35942398859504</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <f aca="false">Assumptions!$B$11*Pricing!$D$39</f>
-        <v>52.641225</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="37" t="n">
-        <f aca="false">1/D6</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <f aca="false">C6/D6</f>
-        <v>4.38676875</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <f aca="false">F6-H6</f>
-        <v>0.761340030991736</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <f aca="false">F6/(1+Assumptions!$B$7)</f>
-        <v>3.62542871900826</v>
-      </c>
-      <c r="I6" s="26" t="n">
-        <f aca="false">H6*Assumptions!$B$21</f>
-        <v>0.54381430785124</v>
-      </c>
-      <c r="J6" s="26" t="n">
-        <f aca="false">F6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E6</f>
-        <v>0.117342245833333</v>
-      </c>
-      <c r="K6" s="26" t="n">
-        <f aca="false">Assumptions!$B$19*I6+(1-Assumptions!$B$19)*J6</f>
-        <v>0.373225483044077</v>
-      </c>
-      <c r="L6" s="26" t="n">
-        <f aca="false">H6-K6</f>
-        <v>3.25220323596419</v>
-      </c>
-      <c r="M6" s="26" t="n">
-        <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.280962</v>
-      </c>
-      <c r="N6" s="26" t="n">
-        <f aca="false">Assumptions!$B$36</f>
-        <v>0.02</v>
-      </c>
-      <c r="O6" s="26" t="n">
-        <f aca="false">L6-M6-N6</f>
-        <v>2.95124123596419</v>
-      </c>
-      <c r="P6" s="27" t="n">
-        <f aca="false">IF(F6=0,0,O6/F6)</f>
-        <v>0.672759701765494</v>
-      </c>
-      <c r="Q6" s="26" t="n">
-        <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>1.383998</v>
-      </c>
-      <c r="R6" s="26" t="n">
-        <f aca="false">L6-Q6-N6</f>
-        <v>1.84820523596419</v>
-      </c>
-      <c r="S6" s="27" t="n">
-        <f aca="false">1-C6/(12*C5)</f>
-        <v>0.443919169447534</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <f aca="false">Assumptions!$B$12*Pricing!$E$39</f>
-        <v>13.528475</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <f aca="false">1/D7</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <f aca="false">C7/D7</f>
-        <v>13.528475</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <f aca="false">F7-H7</f>
-        <v>2.34791714876033</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <f aca="false">F7/(1+Assumptions!$B$7)</f>
-        <v>11.1805578512397</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <f aca="false">H7*Assumptions!$B$21</f>
-        <v>1.67708367768595</v>
-      </c>
-      <c r="J7" s="26" t="n">
-        <f aca="false">F7*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E7</f>
-        <v>0.54762645</v>
-      </c>
-      <c r="K7" s="26" t="n">
-        <f aca="false">Assumptions!$B$19*I7+(1-Assumptions!$B$19)*J7</f>
-        <v>1.22530078661157</v>
-      </c>
-      <c r="L7" s="26" t="n">
-        <f aca="false">H7-K7</f>
-        <v>9.9552570646281</v>
-      </c>
-      <c r="M7" s="26" t="n">
-        <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.457864</v>
-      </c>
-      <c r="N7" s="26" t="n">
-        <f aca="false">Assumptions!$B$36</f>
-        <v>0.02</v>
-      </c>
-      <c r="O7" s="26" t="n">
-        <f aca="false">L7-M7-N7</f>
-        <v>9.4773930646281</v>
-      </c>
-      <c r="P7" s="27" t="n">
-        <f aca="false">IF(F7=0,0,O7/F7)</f>
-        <v>0.700551471221117</v>
-      </c>
-      <c r="Q7" s="26" t="n">
-        <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>3.32992</v>
-      </c>
-      <c r="R7" s="26" t="n">
-        <f aca="false">L7-Q7-N7</f>
-        <v>6.6053370646281</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <f aca="false">Assumptions!$B$13*Pricing!$E$39</f>
-        <v>90.240975</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" s="37" t="n">
-        <f aca="false">1/D8</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <f aca="false">C8/D8</f>
-        <v>7.52008125</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <f aca="false">F8-H8</f>
-        <v>1.30513806818182</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <f aca="false">F8/(1+Assumptions!$B$7)</f>
-        <v>6.21494318181818</v>
-      </c>
-      <c r="I8" s="26" t="n">
-        <f aca="false">H8*Assumptions!$B$21</f>
-        <v>0.932241477272727</v>
-      </c>
-      <c r="J8" s="26" t="n">
-        <f aca="false">F8*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E8</f>
-        <v>0.186275120833333</v>
-      </c>
-      <c r="K8" s="26" t="n">
-        <f aca="false">Assumptions!$B$19*I8+(1-Assumptions!$B$19)*J8</f>
-        <v>0.63385493469697</v>
-      </c>
-      <c r="L8" s="26" t="n">
-        <f aca="false">H8-K8</f>
-        <v>5.58108824712121</v>
-      </c>
-      <c r="M8" s="26" t="n">
-        <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.457864</v>
-      </c>
-      <c r="N8" s="26" t="n">
-        <f aca="false">Assumptions!$B$36</f>
-        <v>0.02</v>
-      </c>
-      <c r="O8" s="26" t="n">
-        <f aca="false">L8-M8-N8</f>
-        <v>5.10322424712121</v>
-      </c>
-      <c r="P8" s="27" t="n">
-        <f aca="false">IF(F8=0,0,O8/F8)</f>
-        <v>0.678612913540158</v>
-      </c>
-      <c r="Q8" s="26" t="n">
-        <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>3.32992</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <f aca="false">L8-Q8-N8</f>
-        <v>2.23116824712121</v>
-      </c>
-      <c r="S8" s="27" t="n">
-        <f aca="false">1-C8/(12*C7)</f>
-        <v>0.444129419613075</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*F5+Assumptions!$B$17*F6</f>
-        <v>5.437355625</v>
-      </c>
-      <c r="G11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*G5+Assumptions!$B$17*G6</f>
-        <v>0.943673290289256</v>
-      </c>
-      <c r="H11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*H5+Assumptions!$B$17*H6</f>
-        <v>4.49368233471074</v>
-      </c>
-      <c r="K11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*K5+Assumptions!$B$17*K6</f>
-        <v>0.4881134729573</v>
-      </c>
-      <c r="L11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*L5+Assumptions!$B$17*L6</f>
-        <v>4.00556886175344</v>
-      </c>
-      <c r="M11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*M5+Assumptions!$B$17*M6</f>
-        <v>0.280962</v>
-      </c>
-      <c r="N11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*N5+Assumptions!$B$17*N6</f>
-        <v>0.02</v>
-      </c>
-      <c r="O11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*O5+Assumptions!$B$17*O6</f>
-        <v>3.70460686175344</v>
-      </c>
-      <c r="P11" s="31" t="n">
-        <f aca="false">IF(F11=0,0,O11/F11)</f>
-        <v>0.681325099414193</v>
-      </c>
-      <c r="Q11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*Q5+Assumptions!$B$17*Q6</f>
-        <v>1.383998</v>
-      </c>
-      <c r="R11" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$17)*R5+Assumptions!$B$17*R6</f>
-        <v>2.60157086175344</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*F7+Assumptions!$B$18*F8</f>
-        <v>10.8246978125</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*G7+Assumptions!$B$18*G8</f>
-        <v>1.8786665625</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*H7+Assumptions!$B$18*H8</f>
-        <v>8.94603125</v>
-      </c>
-      <c r="K12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*K7+Assumptions!$B$18*K8</f>
-        <v>0.95915015325</v>
-      </c>
-      <c r="L12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*L7+Assumptions!$B$18*L8</f>
-        <v>7.98688109675</v>
-      </c>
-      <c r="M12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*M7+Assumptions!$B$18*M8</f>
-        <v>0.457864</v>
-      </c>
-      <c r="N12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*N7+Assumptions!$B$18*N8</f>
-        <v>0.02</v>
-      </c>
-      <c r="O12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*O7+Assumptions!$B$18*O8</f>
-        <v>7.50901709675</v>
-      </c>
-      <c r="P12" s="31" t="n">
-        <f aca="false">IF(F12=0,0,O12/F12)</f>
-        <v>0.693692999732412</v>
-      </c>
-      <c r="Q12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*Q7+Assumptions!$B$18*Q8</f>
-        <v>3.32992</v>
-      </c>
-      <c r="R12" s="38" t="n">
-        <f aca="false">(1-Assumptions!$B$18)*R7+Assumptions!$B$18*R8</f>
-        <v>4.63696109675</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*F11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*F12)</f>
-        <v>6.41687238636364</v>
-      </c>
-      <c r="G13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*G11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*G12)</f>
-        <v>1.11367206705485</v>
-      </c>
-      <c r="H13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*H11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*H12)</f>
-        <v>5.30320031930879</v>
-      </c>
-      <c r="K13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*K11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*K12)</f>
-        <v>0.573756505737791</v>
-      </c>
-      <c r="L13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*L11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*L12)</f>
-        <v>4.729443813571</v>
-      </c>
-      <c r="M13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*M11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*M12)</f>
-        <v>0.313126</v>
-      </c>
-      <c r="N13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*N11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*N12)</f>
-        <v>0.02</v>
-      </c>
-      <c r="O13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*O11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*O12)</f>
-        <v>4.396317813571</v>
-      </c>
-      <c r="P13" s="31" t="n">
-        <f aca="false">IF(F13=0,0,O13/F13)</f>
-        <v>0.685118473434741</v>
-      </c>
-      <c r="Q13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*Q11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*Q12)</f>
-        <v>1.737802</v>
-      </c>
-      <c r="R13" s="38" t="n">
-        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*R11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*R12)</f>
-        <v>2.971641813571</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C17" s="26" t="n">
-        <f aca="false">C6</f>
-        <v>52.641225</v>
-      </c>
-      <c r="D17" s="26" t="n">
-        <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
-        <v>9.13608037190083</v>
-      </c>
-      <c r="E17" s="26" t="n">
-        <f aca="false">C6/(1+Assumptions!$B$7)*Assumptions!$B$21</f>
-        <v>6.52577169421488</v>
-      </c>
-      <c r="F17" s="39" t="n">
-        <f aca="false">C17-D17-E17</f>
-        <v>36.9793729338843</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <f aca="false">IF(C17=0,0,F17/C17)</f>
-        <v>0.702479338842975</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="26" t="n">
-        <f aca="false">C6</f>
-        <v>52.641225</v>
-      </c>
-      <c r="D18" s="26" t="n">
-        <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
-        <v>9.13608037190083</v>
-      </c>
-      <c r="E18" s="26" t="n">
-        <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
-        <v>1.40810695</v>
-      </c>
-      <c r="F18" s="39" t="n">
-        <f aca="false">C18-D18-E18</f>
-        <v>42.0970376780992</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <f aca="false">IF(C18=0,0,F18/C18)</f>
-        <v>0.799697151388464</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <f aca="false">C6</f>
-        <v>52.641225</v>
-      </c>
-      <c r="D19" s="26" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
-        <v>1.40810695</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <f aca="false">C19-D19-E19</f>
-        <v>51.23311805</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <f aca="false">IF(C19=0,0,F19/C19)</f>
-        <v>0.973250870396728</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <f aca="false">'Fixed costs'!$I$24</f>
-        <v>232.68245</v>
-      </c>
-      <c r="D23" s="40" t="n">
-        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C23/O13,0))</f>
-        <v>53</v>
-      </c>
-      <c r="E23" s="40" t="n">
-        <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>964</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <f aca="false">'Fixed costs'!$J$24</f>
-        <v>355.32145</v>
-      </c>
-      <c r="D24" s="40" t="n">
-        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C24/O13,0))</f>
-        <v>81</v>
-      </c>
-      <c r="E24" s="40" t="n">
-        <f aca="false">IF(ISNUMBER(D24),ROUNDUP(D24/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <f aca="false">'Fixed costs'!$K$24</f>
-        <v>736.5767</v>
-      </c>
-      <c r="D25" s="40" t="n">
-        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C25/O13,0))</f>
-        <v>168</v>
-      </c>
-      <c r="E25" s="40" t="n">
-        <f aca="false">IF(ISNUMBER(D25),ROUNDUP(D25/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <f aca="false">Assumptions!$B$35</f>
-        <v>0.01</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6925,6 +7113,752 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="3" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <f aca="false">Assumptions!$B$10*Pricing!$D$39</f>
+        <v>8.0011</v>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="47" t="n">
+        <f aca="false">1/D5</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <f aca="false">C5/D5</f>
+        <v>8.0011</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <f aca="false">F5-H5</f>
+        <v>1.38862066115702</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <f aca="false">F5/(1+Assumptions!$B$7)</f>
+        <v>6.61247933884298</v>
+      </c>
+      <c r="I5" s="26" t="n">
+        <f aca="false">H5*Assumptions!$B$21</f>
+        <v>0.991871900826446</v>
+      </c>
+      <c r="J5" s="26" t="n">
+        <f aca="false">F5*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E5</f>
+        <v>0.4260242</v>
+      </c>
+      <c r="K5" s="26" t="n">
+        <f aca="false">Assumptions!$B$19*I5+(1-Assumptions!$B$19)*J5</f>
+        <v>0.765532820495868</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <f aca="false">H5-K5</f>
+        <v>5.84694651834711</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>0.280962</v>
+      </c>
+      <c r="N5" s="26" t="n">
+        <f aca="false">Assumptions!$B$36</f>
+        <v>0.02</v>
+      </c>
+      <c r="O5" s="26" t="n">
+        <f aca="false">L5-M5-N5</f>
+        <v>5.54598451834711</v>
+      </c>
+      <c r="P5" s="27" t="n">
+        <f aca="false">IF(F5=0,0,O5/F5)</f>
+        <v>0.693152756289399</v>
+      </c>
+      <c r="Q5" s="26" t="n">
+        <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.5913942131</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <f aca="false">L5-Q5-N5</f>
+        <v>3.23555230524711</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <f aca="false">Assumptions!$B$11*Pricing!$D$39</f>
+        <v>53.3911</v>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <f aca="false">1/D6</f>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <f aca="false">C6/D6</f>
+        <v>4.44925833333333</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <f aca="false">F6-H6</f>
+        <v>0.772185330578512</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <f aca="false">F6/(1+Assumptions!$B$7)</f>
+        <v>3.67707300275482</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <f aca="false">H6*Assumptions!$B$21</f>
+        <v>0.551560950413223</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <f aca="false">F6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E6</f>
+        <v>0.118717016666667</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <f aca="false">Assumptions!$B$19*I6+(1-Assumptions!$B$19)*J6</f>
+        <v>0.378423376914601</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <f aca="false">H6-K6</f>
+        <v>3.29864962584022</v>
+      </c>
+      <c r="M6" s="26" t="n">
+        <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>0.280962</v>
+      </c>
+      <c r="N6" s="26" t="n">
+        <f aca="false">Assumptions!$B$36</f>
+        <v>0.02</v>
+      </c>
+      <c r="O6" s="26" t="n">
+        <f aca="false">L6-M6-N6</f>
+        <v>2.99768762584022</v>
+      </c>
+      <c r="P6" s="27" t="n">
+        <f aca="false">IF(F6=0,0,O6/F6)</f>
+        <v>0.673749960388204</v>
+      </c>
+      <c r="Q6" s="26" t="n">
+        <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>2.5913942131</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <f aca="false">L6-Q6-N6</f>
+        <v>0.68725541274022</v>
+      </c>
+      <c r="S6" s="27" t="n">
+        <f aca="false">1-C6/(12*C5)</f>
+        <v>0.443919169447534</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <f aca="false">Assumptions!$B$12*Pricing!$E$39</f>
+        <v>13.3411</v>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="47" t="n">
+        <f aca="false">1/D7</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <f aca="false">C7/D7</f>
+        <v>13.3411</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <f aca="false">F7-H7</f>
+        <v>2.31539752066116</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <f aca="false">F7/(1+Assumptions!$B$7)</f>
+        <v>11.0257024793388</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <f aca="false">H7*Assumptions!$B$21</f>
+        <v>1.65385537190083</v>
+      </c>
+      <c r="J7" s="26" t="n">
+        <f aca="false">F7*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E7</f>
+        <v>0.5435042</v>
+      </c>
+      <c r="K7" s="26" t="n">
+        <f aca="false">Assumptions!$B$19*I7+(1-Assumptions!$B$19)*J7</f>
+        <v>1.2097149031405</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <f aca="false">H7-K7</f>
+        <v>9.81598757619835</v>
+      </c>
+      <c r="M7" s="26" t="n">
+        <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>0.457864</v>
+      </c>
+      <c r="N7" s="26" t="n">
+        <f aca="false">Assumptions!$B$36</f>
+        <v>0.02</v>
+      </c>
+      <c r="O7" s="26" t="n">
+        <f aca="false">L7-M7-N7</f>
+        <v>9.33812357619835</v>
+      </c>
+      <c r="P7" s="27" t="n">
+        <f aca="false">IF(F7=0,0,O7/F7)</f>
+        <v>0.699951546439075</v>
+      </c>
+      <c r="Q7" s="26" t="n">
+        <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>5.0344826345</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <f aca="false">L7-Q7-N7</f>
+        <v>4.76150494169835</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <f aca="false">Assumptions!$B$13*Pricing!$E$39</f>
+        <v>88.9911</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="47" t="n">
+        <f aca="false">1/D8</f>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <f aca="false">C8/D8</f>
+        <v>7.415925</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <f aca="false">F8-H8</f>
+        <v>1.28706136363636</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <f aca="false">F8/(1+Assumptions!$B$7)</f>
+        <v>6.12886363636364</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <f aca="false">H8*Assumptions!$B$21</f>
+        <v>0.919329545454545</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <f aca="false">F8*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E8</f>
+        <v>0.183983683333333</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <f aca="false">Assumptions!$B$19*I8+(1-Assumptions!$B$19)*J8</f>
+        <v>0.625191200606061</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <f aca="false">H8-K8</f>
+        <v>5.50367243575758</v>
+      </c>
+      <c r="M8" s="26" t="n">
+        <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>0.457864</v>
+      </c>
+      <c r="N8" s="26" t="n">
+        <f aca="false">Assumptions!$B$36</f>
+        <v>0.02</v>
+      </c>
+      <c r="O8" s="26" t="n">
+        <f aca="false">L8-M8-N8</f>
+        <v>5.02580843575758</v>
+      </c>
+      <c r="P8" s="27" t="n">
+        <f aca="false">IF(F8=0,0,O8/F8)</f>
+        <v>0.677704862947991</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
+        <v>5.0344826345</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <f aca="false">L8-Q8-N8</f>
+        <v>0.449189801257575</v>
+      </c>
+      <c r="S8" s="27" t="n">
+        <f aca="false">1-C8/(12*C7)</f>
+        <v>0.444129419613075</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*F5+Assumptions!$B$17*F6</f>
+        <v>5.51481083333333</v>
+      </c>
+      <c r="G11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*G5+Assumptions!$B$17*G6</f>
+        <v>0.957115929752066</v>
+      </c>
+      <c r="H11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*H5+Assumptions!$B$17*H6</f>
+        <v>4.55769490358127</v>
+      </c>
+      <c r="K11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*K5+Assumptions!$B$17*K6</f>
+        <v>0.494556209988981</v>
+      </c>
+      <c r="L11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*L5+Assumptions!$B$17*L6</f>
+        <v>4.06313869359229</v>
+      </c>
+      <c r="M11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*M5+Assumptions!$B$17*M6</f>
+        <v>0.280962</v>
+      </c>
+      <c r="N11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*N5+Assumptions!$B$17*N6</f>
+        <v>0.02</v>
+      </c>
+      <c r="O11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*O5+Assumptions!$B$17*O6</f>
+        <v>3.76217669359229</v>
+      </c>
+      <c r="P11" s="32" t="n">
+        <f aca="false">IF(F11=0,0,O11/F11)</f>
+        <v>0.682195057508129</v>
+      </c>
+      <c r="Q11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*Q5+Assumptions!$B$17*Q6</f>
+        <v>2.5913942131</v>
+      </c>
+      <c r="R11" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$17)*R5+Assumptions!$B$17*R6</f>
+        <v>1.45174448049229</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*F7+Assumptions!$B$18*F8</f>
+        <v>10.67477125</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*G7+Assumptions!$B$18*G8</f>
+        <v>1.85264625</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*H7+Assumptions!$B$18*H8</f>
+        <v>8.822125</v>
+      </c>
+      <c r="K12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*K7+Assumptions!$B$18*K8</f>
+        <v>0.946679237</v>
+      </c>
+      <c r="L12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*L7+Assumptions!$B$18*L8</f>
+        <v>7.875445763</v>
+      </c>
+      <c r="M12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*M7+Assumptions!$B$18*M8</f>
+        <v>0.457864</v>
+      </c>
+      <c r="N12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*N7+Assumptions!$B$18*N8</f>
+        <v>0.02</v>
+      </c>
+      <c r="O12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*O7+Assumptions!$B$18*O8</f>
+        <v>7.397581763</v>
+      </c>
+      <c r="P12" s="32" t="n">
+        <f aca="false">IF(F12=0,0,O12/F12)</f>
+        <v>0.692996748103619</v>
+      </c>
+      <c r="Q12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*Q7+Assumptions!$B$18*Q8</f>
+        <v>5.0344826345</v>
+      </c>
+      <c r="R12" s="38" t="n">
+        <f aca="false">(1-Assumptions!$B$18)*R7+Assumptions!$B$18*R8</f>
+        <v>2.8209631285</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*F11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*F12)</f>
+        <v>6.45298545454546</v>
+      </c>
+      <c r="G13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*G11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*G12)</f>
+        <v>1.1199396243426</v>
+      </c>
+      <c r="H13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*H11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*H12)</f>
+        <v>5.33304583020286</v>
+      </c>
+      <c r="K13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*K11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*K12)</f>
+        <v>0.576760396718257</v>
+      </c>
+      <c r="L13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*L11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*L12)</f>
+        <v>4.7562854334846</v>
+      </c>
+      <c r="M13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*M11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*M12)</f>
+        <v>0.313126</v>
+      </c>
+      <c r="N13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*N11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*N12)</f>
+        <v>0.02</v>
+      </c>
+      <c r="O13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*O11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*O12)</f>
+        <v>4.4231594334846</v>
+      </c>
+      <c r="P13" s="32" t="n">
+        <f aca="false">IF(F13=0,0,O13/F13)</f>
+        <v>0.685443887118782</v>
+      </c>
+      <c r="Q13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*Q11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*Q12)</f>
+        <v>3.0355921079</v>
+      </c>
+      <c r="R13" s="38" t="n">
+        <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*R11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*R12)</f>
+        <v>1.7006933255846</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C17" s="26" t="n">
+        <f aca="false">C6</f>
+        <v>53.3911</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
+        <v>9.26622396694215</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <f aca="false">C6/(1+Assumptions!$B$7)*Assumptions!$B$21</f>
+        <v>6.61873140495868</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <f aca="false">C17-D17-E17</f>
+        <v>37.5061446280992</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <f aca="false">IF(C17=0,0,F17/C17)</f>
+        <v>0.702479338842975</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <f aca="false">C6</f>
+        <v>53.3911</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <f aca="false">C6-C6/(1+Assumptions!$B$7)</f>
+        <v>9.26622396694215</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
+        <v>1.4246042</v>
+      </c>
+      <c r="F18" s="41" t="n">
+        <f aca="false">C18-D18-E18</f>
+        <v>42.7002718330579</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <f aca="false">IF(C18=0,0,F18/C18)</f>
+        <v>0.799763852646937</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C19" s="26" t="n">
+        <f aca="false">C6</f>
+        <v>53.3911</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <f aca="false">C6*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23</f>
+        <v>1.4246042</v>
+      </c>
+      <c r="F19" s="41" t="n">
+        <f aca="false">C19-D19-E19</f>
+        <v>51.9664958</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <f aca="false">IF(C19=0,0,F19/C19)</f>
+        <v>0.973317571655201</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <f aca="false">'Fixed costs'!$I$24</f>
+        <v>232.68245</v>
+      </c>
+      <c r="D23" s="36" t="n">
+        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C23/O13,0))</f>
+        <v>53</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <f aca="false">IF(ISNUMBER(D23),ROUNDUP(D23/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
+        <v>964</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <f aca="false">'Fixed costs'!$J$24</f>
+        <v>355.32145</v>
+      </c>
+      <c r="D24" s="36" t="n">
+        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C24/O13,0))</f>
+        <v>81</v>
+      </c>
+      <c r="E24" s="36" t="n">
+        <f aca="false">IF(ISNUMBER(D24),ROUNDUP(D24/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <f aca="false">'Fixed costs'!$K$24</f>
+        <v>736.5767</v>
+      </c>
+      <c r="D25" s="36" t="n">
+        <f aca="false">IF(O13&lt;=0,"never",ROUNDUP(C25/O13,0))</f>
+        <v>167</v>
+      </c>
+      <c r="E25" s="36" t="n">
+        <f aca="false">IF(ISNUMBER(D25),ROUNDUP(D25/(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <f aca="false">Assumptions!$B$35</f>
+        <v>0.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6934,46 +7868,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>100</v>
@@ -7002,192 +7936,192 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B6" s="41" t="n">
+        <v>417</v>
+      </c>
+      <c r="B6" s="48" t="n">
         <f aca="false">IF(B5&gt;=Assumptions!$B$39,3,IF(B5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="48" t="n">
         <f aca="false">IF(C5&gt;=Assumptions!$B$39,3,IF(C5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="48" t="n">
         <f aca="false">IF(D5&gt;=Assumptions!$B$39,3,IF(D5&gt;=Assumptions!$B$38,2,1))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="48" t="n">
         <f aca="false">IF(E5&gt;=Assumptions!$B$39,3,IF(E5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="48" t="n">
         <f aca="false">IF(F5&gt;=Assumptions!$B$39,3,IF(F5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="48" t="n">
         <f aca="false">IF(G5&gt;=Assumptions!$B$39,3,IF(G5&gt;=Assumptions!$B$38,2,1))</f>
         <v>2</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H6" s="48" t="n">
         <f aca="false">IF(H5&gt;=Assumptions!$B$39,3,IF(H5&gt;=Assumptions!$B$38,2,1))</f>
         <v>3</v>
       </c>
-      <c r="I6" s="41" t="n">
+      <c r="I6" s="48" t="n">
         <f aca="false">IF(I5&gt;=Assumptions!$B$39,3,IF(I5&gt;=Assumptions!$B$38,2,1))</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B7" s="40" t="n">
+        <v>418</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <f aca="false">B5-B8-B9</f>
         <v>94</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="36" t="n">
         <f aca="false">C5-C8-C9</f>
         <v>472</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="36" t="n">
         <f aca="false">D5-D8-D9</f>
         <v>945</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="36" t="n">
         <f aca="false">E5-E8-E9</f>
         <v>2362</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <f aca="false">F5-F8-F9</f>
         <v>4725</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="G7" s="36" t="n">
         <f aca="false">G5-G8-G9</f>
         <v>9450</v>
       </c>
-      <c r="H7" s="40" t="n">
+      <c r="H7" s="36" t="n">
         <f aca="false">H5-H8-H9</f>
         <v>23625</v>
       </c>
-      <c r="I7" s="40" t="n">
+      <c r="I7" s="36" t="n">
         <f aca="false">I5-I8-I9</f>
         <v>47250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="B8" s="40" t="n">
+        <v>419</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$15,0)</f>
         <v>5</v>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="36" t="n">
         <f aca="false">ROUND(C5*Assumptions!$B$15,0)</f>
         <v>23</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="36" t="n">
         <f aca="false">ROUND(D5*Assumptions!$B$15,0)</f>
         <v>45</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="36" t="n">
         <f aca="false">ROUND(E5*Assumptions!$B$15,0)</f>
         <v>113</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <f aca="false">ROUND(F5*Assumptions!$B$15,0)</f>
         <v>225</v>
       </c>
-      <c r="G8" s="40" t="n">
+      <c r="G8" s="36" t="n">
         <f aca="false">ROUND(G5*Assumptions!$B$15,0)</f>
         <v>450</v>
       </c>
-      <c r="H8" s="40" t="n">
+      <c r="H8" s="36" t="n">
         <f aca="false">ROUND(H5*Assumptions!$B$15,0)</f>
         <v>1125</v>
       </c>
-      <c r="I8" s="40" t="n">
+      <c r="I8" s="36" t="n">
         <f aca="false">ROUND(I5*Assumptions!$B$15,0)</f>
         <v>2250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="B9" s="40" t="n">
+        <v>420</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$16,0)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="36" t="n">
         <f aca="false">ROUND(C5*Assumptions!$B$16,0)</f>
         <v>5</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="36" t="n">
         <f aca="false">ROUND(D5*Assumptions!$B$16,0)</f>
         <v>10</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="36" t="n">
         <f aca="false">ROUND(E5*Assumptions!$B$16,0)</f>
         <v>25</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <f aca="false">ROUND(F5*Assumptions!$B$16,0)</f>
         <v>50</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G9" s="36" t="n">
         <f aca="false">ROUND(G5*Assumptions!$B$16,0)</f>
         <v>100</v>
       </c>
-      <c r="H9" s="40" t="n">
+      <c r="H9" s="36" t="n">
         <f aca="false">ROUND(H5*Assumptions!$B$16,0)</f>
         <v>250</v>
       </c>
-      <c r="I9" s="40" t="n">
+      <c r="I9" s="36" t="n">
         <f aca="false">ROUND(I5*Assumptions!$B$16,0)</f>
         <v>500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B10" s="42" t="n">
+        <v>421</v>
+      </c>
+      <c r="B10" s="49" t="n">
         <f aca="false">B8+B9</f>
         <v>6</v>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="49" t="n">
         <f aca="false">C8+C9</f>
         <v>28</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="49" t="n">
         <f aca="false">D8+D9</f>
         <v>55</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="49" t="n">
         <f aca="false">E8+E9</f>
         <v>138</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="49" t="n">
         <f aca="false">F8+F9</f>
         <v>275</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="49" t="n">
         <f aca="false">G8+G9</f>
         <v>550</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="49" t="n">
         <f aca="false">H8+H9</f>
         <v>1375</v>
       </c>
-      <c r="I10" s="42" t="n">
+      <c r="I10" s="49" t="n">
         <f aca="false">I8+I9</f>
         <v>2750</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -7200,101 +8134,101 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$F$11+B9*'Unit economics'!$F$12</f>
-        <v>38.0114759375</v>
+        <v>38.2488254166667</v>
       </c>
       <c r="C13" s="26" t="n">
         <f aca="false">C8*'Unit economics'!$F$11+C9*'Unit economics'!$F$12</f>
-        <v>179.1826684375</v>
+        <v>180.214505416667</v>
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">D8*'Unit economics'!$F$11+D9*'Unit economics'!$F$12</f>
-        <v>352.92798125</v>
+        <v>354.9142</v>
       </c>
       <c r="E13" s="26" t="n">
         <f aca="false">E8*'Unit economics'!$F$11+E9*'Unit economics'!$F$12</f>
-        <v>885.0386309375</v>
+        <v>890.042905416667</v>
       </c>
       <c r="F13" s="26" t="n">
         <f aca="false">F8*'Unit economics'!$F$11+F9*'Unit economics'!$F$12</f>
-        <v>1764.63990625</v>
+        <v>1774.571</v>
       </c>
       <c r="G13" s="26" t="n">
         <f aca="false">G8*'Unit economics'!$F$11+G9*'Unit economics'!$F$12</f>
-        <v>3529.2798125</v>
+        <v>3549.142</v>
       </c>
       <c r="H13" s="26" t="n">
         <f aca="false">H8*'Unit economics'!$F$11+H9*'Unit economics'!$F$12</f>
-        <v>8823.19953125</v>
+        <v>8872.855</v>
       </c>
       <c r="I13" s="26" t="n">
         <f aca="false">I8*'Unit economics'!$F$11+I9*'Unit economics'!$F$12</f>
-        <v>17646.3990625</v>
+        <v>17745.71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">-(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>-6.59703301394628</v>
+        <v>-6.63822589876033</v>
       </c>
       <c r="C14" s="26" t="n">
         <f aca="false">-(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>-31.0978184891529</v>
+        <v>-31.2768976342975</v>
       </c>
       <c r="D14" s="26" t="n">
         <f aca="false">-(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>-61.2519636880165</v>
+        <v>-61.596679338843</v>
       </c>
       <c r="E14" s="26" t="n">
         <f aca="false">-(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>-153.601745865186</v>
+        <v>-154.470256311983</v>
       </c>
       <c r="F14" s="26" t="n">
         <f aca="false">-(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>-306.259818440083</v>
+        <v>-307.983396694215</v>
       </c>
       <c r="G14" s="26" t="n">
         <f aca="false">-(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
-        <v>-612.519636880165</v>
+        <v>-615.96679338843</v>
       </c>
       <c r="H14" s="26" t="n">
         <f aca="false">-(H8*'Unit economics'!$G$11+H9*'Unit economics'!$G$12)</f>
-        <v>-1531.29909220041</v>
+        <v>-1539.91698347107</v>
       </c>
       <c r="I14" s="26" t="n">
         <f aca="false">-(I8*'Unit economics'!$G$11+I9*'Unit economics'!$G$12)</f>
-        <v>-3062.59818440083</v>
+        <v>-3079.83396694215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B22*(1-Assumptions!$B$19)*(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>2.63881320557851</v>
+        <v>2.65529035950413</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">C22*(1-Assumptions!$B$19)*(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>12.4391273956612</v>
+        <v>12.510759053719</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">D22*(1-Assumptions!$B$19)*(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>24.5007854752066</v>
+        <v>24.6386717355372</v>
       </c>
       <c r="E15" s="26" t="n">
         <f aca="false">E22*(1-Assumptions!$B$19)*(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>61.4406983460744</v>
+        <v>61.7881025247934</v>
       </c>
       <c r="F15" s="26" t="n">
         <f aca="false">F22*(1-Assumptions!$B$19)*(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>122.503927376033</v>
+        <v>123.193358677686</v>
       </c>
       <c r="G15" s="26" t="n">
         <f aca="false">G22*(1-Assumptions!$B$19)*(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
@@ -7311,81 +8245,81 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">-(B8*'Unit economics'!$K$11+B9*'Unit economics'!$K$12)</f>
-        <v>-3.3997175180365</v>
+        <v>-3.4194602869449</v>
       </c>
       <c r="C16" s="26" t="n">
         <f aca="false">-(C8*'Unit economics'!$K$11+C9*'Unit economics'!$K$12)</f>
-        <v>-16.0223606442679</v>
+        <v>-16.1081890147466</v>
       </c>
       <c r="D16" s="26" t="n">
         <f aca="false">-(D8*'Unit economics'!$K$11+D9*'Unit economics'!$K$12)</f>
-        <v>-31.5566078155785</v>
+        <v>-31.7218218195041</v>
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">-(E8*'Unit economics'!$K$11+E9*'Unit economics'!$K$12)</f>
-        <v>-79.1355762754249</v>
+        <v>-79.5518326537548</v>
       </c>
       <c r="F16" s="26" t="n">
         <f aca="false">-(F8*'Unit economics'!$K$11+F9*'Unit economics'!$K$12)</f>
-        <v>-157.783039077893</v>
+        <v>-158.609109097521</v>
       </c>
       <c r="G16" s="26" t="n">
         <f aca="false">-(G8*'Unit economics'!$K$11+G9*'Unit economics'!$K$12)</f>
-        <v>-315.566078155785</v>
+        <v>-317.218218195041</v>
       </c>
       <c r="H16" s="26" t="n">
         <f aca="false">-(H8*'Unit economics'!$K$11+H9*'Unit economics'!$K$12)</f>
-        <v>-788.915195389463</v>
+        <v>-793.045545487603</v>
       </c>
       <c r="I16" s="26" t="n">
         <f aca="false">-(I8*'Unit economics'!$K$11+I9*'Unit economics'!$K$12)</f>
-        <v>-1577.83039077893</v>
+        <v>-1586.09109097521</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B17" s="39" t="n">
+        <v>427</v>
+      </c>
+      <c r="B17" s="41" t="n">
         <f aca="false">B13+B14+B15+B16</f>
-        <v>30.6535386110957</v>
-      </c>
-      <c r="C17" s="39" t="n">
+        <v>30.8464295904656</v>
+      </c>
+      <c r="C17" s="41" t="n">
         <f aca="false">C13+C14+C15+C16</f>
-        <v>144.50161669974</v>
-      </c>
-      <c r="D17" s="39" t="n">
+        <v>145.340177821342</v>
+      </c>
+      <c r="D17" s="41" t="n">
         <f aca="false">D13+D14+D15+D16</f>
-        <v>284.620195221612</v>
-      </c>
-      <c r="E17" s="39" t="n">
+        <v>286.23437057719</v>
+      </c>
+      <c r="E17" s="41" t="n">
         <f aca="false">E13+E14+E15+E16</f>
-        <v>713.742007142964</v>
-      </c>
-      <c r="F17" s="39" t="n">
+        <v>717.808918975722</v>
+      </c>
+      <c r="F17" s="41" t="n">
         <f aca="false">F13+F14+F15+F16</f>
-        <v>1423.10097610806</v>
-      </c>
-      <c r="G17" s="39" t="n">
+        <v>1431.17185288595</v>
+      </c>
+      <c r="G17" s="41" t="n">
         <f aca="false">G13+G14+G15+G16</f>
-        <v>2601.19409746405</v>
-      </c>
-      <c r="H17" s="39" t="n">
+        <v>2615.95698841653</v>
+      </c>
+      <c r="H17" s="41" t="n">
         <f aca="false">H13+H14+H15+H16</f>
-        <v>6502.98524366013</v>
-      </c>
-      <c r="I17" s="39" t="n">
+        <v>6539.89247104132</v>
+      </c>
+      <c r="I17" s="41" t="n">
         <f aca="false">I13+I14+I15+I16</f>
-        <v>13005.9704873203</v>
+        <v>13079.7849420826</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -7398,118 +8332,118 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="B20" s="26" t="n">
         <f aca="false">(B13+B14)*12</f>
-        <v>376.973315082645</v>
+        <v>379.327194214876</v>
       </c>
       <c r="C20" s="26" t="n">
         <f aca="false">(C13+C14)*12</f>
-        <v>1777.01819938017</v>
+        <v>1787.25129338843</v>
       </c>
       <c r="D20" s="26" t="n">
         <f aca="false">(D13+D14)*12</f>
-        <v>3500.1122107438</v>
+        <v>3519.81024793388</v>
       </c>
       <c r="E20" s="26" t="n">
         <f aca="false">(E13+E14)*12</f>
-        <v>8777.24262086777</v>
+        <v>8826.8717892562</v>
       </c>
       <c r="F20" s="26" t="n">
         <f aca="false">(F13+F14)*12</f>
-        <v>17500.561053719</v>
+        <v>17599.0512396694</v>
       </c>
       <c r="G20" s="26" t="n">
         <f aca="false">(G13+G14)*12</f>
-        <v>35001.122107438</v>
+        <v>35198.1024793388</v>
       </c>
       <c r="H20" s="26" t="n">
         <f aca="false">(H13+H14)*12</f>
-        <v>87502.8052685951</v>
+        <v>87995.2561983471</v>
       </c>
       <c r="I20" s="26" t="n">
         <f aca="false">(I13+I14)*12</f>
-        <v>175005.61053719</v>
+        <v>175990.512396694</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B21" s="26" t="n">
         <f aca="false">B13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>145.9640676</v>
+        <v>146.8754896</v>
       </c>
       <c r="C21" s="26" t="n">
         <f aca="false">C13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>688.0614468</v>
+        <v>692.0237008</v>
       </c>
       <c r="D21" s="26" t="n">
         <f aca="false">D13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>1355.243448</v>
+        <v>1362.870528</v>
       </c>
       <c r="E21" s="26" t="n">
         <f aca="false">E13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>3398.5483428</v>
+        <v>3417.7647568</v>
       </c>
       <c r="F21" s="26" t="n">
         <f aca="false">F13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>6776.21724</v>
+        <v>6814.35264</v>
       </c>
       <c r="G21" s="26" t="n">
         <f aca="false">G13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>13552.43448</v>
+        <v>13628.70528</v>
       </c>
       <c r="H21" s="26" t="n">
         <f aca="false">H13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>33881.0862</v>
+        <v>34071.7632</v>
       </c>
       <c r="I21" s="26" t="n">
         <f aca="false">I13*(1-Assumptions!$B$19)*Assumptions!$B$29*12</f>
-        <v>67762.1724</v>
+        <v>68143.5264</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B22" s="41" t="n">
+        <v>431</v>
+      </c>
+      <c r="B22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",B20&lt;=Assumptions!$B$27,B21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",C20&lt;=Assumptions!$B$27,C21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",D20&lt;=Assumptions!$B$27,D21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="E22" s="41" t="n">
+      <c r="E22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",E20&lt;=Assumptions!$B$27,E21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",F20&lt;=Assumptions!$B$27,F21&lt;=Assumptions!$B$28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="41" t="n">
+      <c r="G22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",G20&lt;=Assumptions!$B$27,G21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="41" t="n">
+      <c r="H22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",H20&lt;=Assumptions!$B$27,H21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I22" s="48" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",I20&lt;=Assumptions!$B$27,I21&lt;=Assumptions!$B$28),1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -7522,7 +8456,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="B25" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$M$11+B9*'Unit economics'!$M$12</f>
@@ -7559,7 +8493,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="B26" s="26" t="n">
         <f aca="false">B7*Assumptions!$B$35+B10*Assumptions!$B$36</f>
@@ -7596,7 +8530,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">CHOOSE(B6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
@@ -7633,7 +8567,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B28" s="38" t="n">
         <f aca="false">B25+B26+B27</f>
@@ -7670,7 +8604,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -7683,44 +8617,44 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="B31" s="38" t="n">
         <f aca="false">B17-B28</f>
-        <v>-204.951585388904</v>
+        <v>-204.758694409534</v>
       </c>
       <c r="C31" s="38" t="n">
         <f aca="false">C17-C28</f>
-        <v>-102.21227930026</v>
+        <v>-101.373718178658</v>
       </c>
       <c r="D31" s="38" t="n">
         <f aca="false">D17-D28</f>
-        <v>24.1658152216116</v>
+        <v>25.77999057719</v>
       </c>
       <c r="E31" s="38" t="n">
         <f aca="false">E17-E28</f>
-        <v>288.845251142964</v>
+        <v>292.912162975722</v>
       </c>
       <c r="F31" s="38" t="n">
         <f aca="false">F17-F28</f>
-        <v>928.919876108058</v>
+        <v>936.99075288595</v>
       </c>
       <c r="G31" s="38" t="n">
         <f aca="false">G17-G28</f>
-        <v>1968.15334746405</v>
+        <v>1982.91623841653</v>
       </c>
       <c r="H31" s="38" t="n">
         <f aca="false">H17-H28</f>
-        <v>5072.11029366013</v>
+        <v>5109.01752104132</v>
       </c>
       <c r="I31" s="38" t="n">
         <f aca="false">I17-I28</f>
-        <v>10880.7972873202</v>
+        <v>10954.6117420826</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="B32" s="26" t="n">
         <f aca="false">MAX(0,B31)*12</f>
@@ -7732,32 +8666,32 @@
       </c>
       <c r="D32" s="26" t="n">
         <f aca="false">MAX(0,D31)*12</f>
-        <v>289.989782659339</v>
+        <v>309.35988692628</v>
       </c>
       <c r="E32" s="26" t="n">
         <f aca="false">MAX(0,E31)*12</f>
-        <v>3466.14301371556</v>
+        <v>3514.94595570866</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">MAX(0,F31)*12</f>
-        <v>11147.0385132967</v>
+        <v>11243.8890346314</v>
       </c>
       <c r="G32" s="26" t="n">
         <f aca="false">MAX(0,G31)*12</f>
-        <v>23617.8401695686</v>
+        <v>23794.9948609983</v>
       </c>
       <c r="H32" s="26" t="n">
         <f aca="false">MAX(0,H31)*12</f>
-        <v>60865.3235239215</v>
+        <v>61308.2102524959</v>
       </c>
       <c r="I32" s="26" t="n">
         <f aca="false">MAX(0,I31)*12</f>
-        <v>130569.567447843</v>
+        <v>131455.340904992</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="B33" s="26" t="n">
         <f aca="false">IF(B32&lt;=Assumptions!$B$41,0,IF(B32&lt;Assumptions!$B$42,Assumptions!$B$43*(B32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*B32)))/12</f>
@@ -7777,135 +8711,135 @@
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">IF(F32&lt;=Assumptions!$B$41,0,IF(F32&lt;Assumptions!$B$42,Assumptions!$B$43*(F32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*F32)))/12</f>
-        <v>42.0249746021519</v>
+        <v>43.6795043416197</v>
       </c>
       <c r="G33" s="26" t="n">
         <f aca="false">IF(G32&lt;=Assumptions!$B$41,0,IF(G32&lt;Assumptions!$B$42,Assumptions!$B$43*(G32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*G32)))/12</f>
-        <v>403.47143623013</v>
+        <v>406.497828875388</v>
       </c>
       <c r="H33" s="26" t="n">
         <f aca="false">IF(H32&lt;=Assumptions!$B$41,0,IF(H32&lt;Assumptions!$B$42,Assumptions!$B$43*(H32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*H32)))/12</f>
-        <v>1039.78261020033</v>
+        <v>1047.34859181347</v>
       </c>
       <c r="I33" s="26" t="n">
         <f aca="false">IF(I32&lt;=Assumptions!$B$41,0,IF(I32&lt;Assumptions!$B$42,Assumptions!$B$43*(I32-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*I32)))/12</f>
-        <v>2230.56344390065</v>
+        <v>2245.69540712694</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B34" s="38" t="n">
         <f aca="false">B31-B33</f>
-        <v>-204.951585388904</v>
+        <v>-204.758694409534</v>
       </c>
       <c r="C34" s="38" t="n">
         <f aca="false">C31-C33</f>
-        <v>-102.21227930026</v>
+        <v>-101.373718178658</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">D31-D33</f>
-        <v>24.1658152216116</v>
+        <v>25.77999057719</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">E31-E33</f>
-        <v>288.845251142964</v>
+        <v>292.912162975722</v>
       </c>
       <c r="F34" s="38" t="n">
         <f aca="false">F31-F33</f>
-        <v>886.894901505906</v>
+        <v>893.31124854433</v>
       </c>
       <c r="G34" s="38" t="n">
         <f aca="false">G31-G33</f>
-        <v>1564.68191123392</v>
+        <v>1576.41840954114</v>
       </c>
       <c r="H34" s="38" t="n">
         <f aca="false">H31-H33</f>
-        <v>4032.3276834598</v>
+        <v>4061.66892922785</v>
       </c>
       <c r="I34" s="38" t="n">
         <f aca="false">I31-I33</f>
-        <v>8650.2338434196</v>
+        <v>8708.9163349557</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="B35" s="26" t="n">
         <f aca="false">B34*12</f>
-        <v>-2459.41902466685</v>
+        <v>-2457.10433291441</v>
       </c>
       <c r="C35" s="26" t="n">
         <f aca="false">C34*12</f>
-        <v>-1226.54735160312</v>
+        <v>-1216.4846181439</v>
       </c>
       <c r="D35" s="26" t="n">
         <f aca="false">D34*12</f>
-        <v>289.989782659339</v>
+        <v>309.35988692628</v>
       </c>
       <c r="E35" s="26" t="n">
         <f aca="false">E34*12</f>
-        <v>3466.14301371556</v>
+        <v>3514.94595570866</v>
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">F34*12</f>
-        <v>10642.7388180709</v>
+        <v>10719.734982532</v>
       </c>
       <c r="G35" s="26" t="n">
         <f aca="false">G34*12</f>
-        <v>18776.182934807</v>
+        <v>18917.0209144937</v>
       </c>
       <c r="H35" s="26" t="n">
         <f aca="false">H34*12</f>
-        <v>48387.9322015176</v>
+        <v>48740.0271507342</v>
       </c>
       <c r="I35" s="26" t="n">
         <f aca="false">I34*12</f>
-        <v>103802.806121035</v>
+        <v>104506.996019468</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B36" s="43" t="str">
+        <v>443</v>
+      </c>
+      <c r="B36" s="50" t="str">
         <f aca="false">IF(B32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="C36" s="43" t="str">
+      <c r="C36" s="50" t="str">
         <f aca="false">IF(C32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="D36" s="43" t="str">
+      <c r="D36" s="50" t="str">
         <f aca="false">IF(D32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="E36" s="43" t="str">
+      <c r="E36" s="50" t="str">
         <f aca="false">IF(E32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="F36" s="43" t="str">
+      <c r="F36" s="50" t="str">
         <f aca="false">IF(F32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>yes</v>
       </c>
-      <c r="G36" s="43" t="str">
+      <c r="G36" s="50" t="str">
         <f aca="false">IF(G32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
-      <c r="H36" s="43" t="str">
+      <c r="H36" s="50" t="str">
         <f aca="false">IF(H32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
-      <c r="I36" s="43" t="str">
+      <c r="I36" s="50" t="str">
         <f aca="false">IF(I32&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
         <v>no: full-time rates</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -7918,7 +8852,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B39" s="26" t="n">
         <f aca="false">IF(B5=0,0,B28/B5)</f>
@@ -7955,7 +8889,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="B40" s="26" t="n">
         <f aca="false">IF(B10=0,0,B28/B10)</f>
@@ -7992,44 +8926,44 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="B41" s="26" t="n">
         <f aca="false">IF(B10=0,0,B17/B10)</f>
-        <v>5.10892310184929</v>
+        <v>5.14107159841093</v>
       </c>
       <c r="C41" s="26" t="n">
         <f aca="false">IF(C10=0,0,C17/C10)</f>
-        <v>5.16077202499073</v>
+        <v>5.19072063647649</v>
       </c>
       <c r="D41" s="26" t="n">
         <f aca="false">IF(D10=0,0,D17/D10)</f>
-        <v>5.17491264039294</v>
+        <v>5.20426128322164</v>
       </c>
       <c r="E41" s="26" t="n">
         <f aca="false">IF(E10=0,0,E17/E10)</f>
-        <v>5.17204353002148</v>
+        <v>5.20151390562117</v>
       </c>
       <c r="F41" s="26" t="n">
         <f aca="false">IF(F10=0,0,F17/F10)</f>
-        <v>5.17491264039294</v>
+        <v>5.20426128322164</v>
       </c>
       <c r="G41" s="26" t="n">
         <f aca="false">IF(G10=0,0,G17/G10)</f>
-        <v>4.729443813571</v>
+        <v>4.7562854334846</v>
       </c>
       <c r="H41" s="26" t="n">
         <f aca="false">IF(H10=0,0,H17/H10)</f>
-        <v>4.729443813571</v>
+        <v>4.7562854334846</v>
       </c>
       <c r="I41" s="26" t="n">
         <f aca="false">IF(I10=0,0,I17/I10)</f>
-        <v>4.729443813571</v>
+        <v>4.7562854334846</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -8066,44 +9000,44 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="B43" s="27" t="n">
         <f aca="false">IF(B17=0,0,B31/B17)</f>
-        <v>-6.68606610118146</v>
+        <v>-6.63800307290099</v>
       </c>
       <c r="C43" s="27" t="n">
         <f aca="false">IF(C17=0,0,C31/C17)</f>
-        <v>-0.707343499918387</v>
+        <v>-0.69749273530731</v>
       </c>
       <c r="D43" s="27" t="n">
         <f aca="false">IF(D17=0,0,D31/D17)</f>
-        <v>0.0849054832626882</v>
+        <v>0.0900660201121368</v>
       </c>
       <c r="E43" s="27" t="n">
         <f aca="false">IF(E17=0,0,E31/E17)</f>
-        <v>0.404691398645824</v>
+        <v>0.40806425670176</v>
       </c>
       <c r="F43" s="27" t="n">
         <f aca="false">IF(F17=0,0,F31/F17)</f>
-        <v>0.652743474780333</v>
+        <v>0.654701775329436</v>
       </c>
       <c r="G43" s="27" t="n">
         <f aca="false">IF(G17=0,0,G31/G17)</f>
-        <v>0.756634558483289</v>
+        <v>0.758007966949339</v>
       </c>
       <c r="H43" s="27" t="n">
         <f aca="false">IF(H17=0,0,H31/H17)</f>
-        <v>0.779966446733831</v>
+        <v>0.781208184028113</v>
       </c>
       <c r="I43" s="27" t="n">
         <f aca="false">IF(I17=0,0,I31/I17)</f>
-        <v>0.836600182810512</v>
+        <v>0.837522313294119</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -8116,91 +9050,91 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="B46" s="26" t="n">
         <f aca="false">B8*'Unit economics'!$Q$11+B9*'Unit economics'!$Q$12</f>
-        <v>10.24991</v>
+        <v>17.9914537</v>
       </c>
       <c r="C46" s="26" t="n">
         <f aca="false">C8*'Unit economics'!$Q$11+C9*'Unit economics'!$Q$12</f>
-        <v>48.481554</v>
+        <v>84.7744800738</v>
       </c>
       <c r="D46" s="26" t="n">
         <f aca="false">D8*'Unit economics'!$Q$11+D9*'Unit economics'!$Q$12</f>
-        <v>95.57911</v>
+        <v>166.9575659345</v>
       </c>
       <c r="E46" s="26" t="n">
         <f aca="false">E8*'Unit economics'!$Q$11+E9*'Unit economics'!$Q$12</f>
-        <v>239.639774</v>
+        <v>418.6896119428</v>
       </c>
       <c r="F46" s="26" t="n">
         <f aca="false">F8*'Unit economics'!$Q$11+F9*'Unit economics'!$Q$12</f>
-        <v>477.89555</v>
+        <v>834.7878296725</v>
       </c>
       <c r="G46" s="26" t="n">
         <f aca="false">G8*'Unit economics'!$Q$11+G9*'Unit economics'!$Q$12</f>
-        <v>955.7911</v>
+        <v>1669.575659345</v>
       </c>
       <c r="H46" s="26" t="n">
         <f aca="false">H8*'Unit economics'!$Q$11+H9*'Unit economics'!$Q$12</f>
-        <v>2389.47775</v>
+        <v>4173.9391483625</v>
       </c>
       <c r="I46" s="26" t="n">
         <f aca="false">I8*'Unit economics'!$Q$11+I9*'Unit economics'!$Q$12</f>
-        <v>4778.9555</v>
+        <v>8347.878296725</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B47" s="39" t="n">
+        <v>452</v>
+      </c>
+      <c r="B47" s="41" t="n">
         <f aca="false">B17-(B46+B26+B27)</f>
-        <v>-213.338821388904</v>
-      </c>
-      <c r="C47" s="39" t="n">
+        <v>-220.887474109534</v>
+      </c>
+      <c r="C47" s="41" t="n">
         <f aca="false">C17-(C46+C26+C27)</f>
-        <v>-141.94238730026</v>
-      </c>
-      <c r="D47" s="39" t="n">
+        <v>-177.396752252458</v>
+      </c>
+      <c r="D47" s="41" t="n">
         <f aca="false">D17-(D46+D26+D27)</f>
-        <v>-54.1913647783884</v>
-      </c>
-      <c r="E47" s="39" t="n">
+        <v>-123.95564535731</v>
+      </c>
+      <c r="E47" s="41" t="n">
         <f aca="false">E17-(E46+E26+E27)</f>
-        <v>92.4007831429636</v>
-      </c>
-      <c r="F47" s="39" t="n">
+        <v>-82.5821429670781</v>
+      </c>
+      <c r="F47" s="41" t="n">
         <f aca="false">F17-(F46+F26+F27)</f>
-        <v>537.133976108058</v>
-      </c>
-      <c r="G47" s="39" t="n">
+        <v>188.31257321345</v>
+      </c>
+      <c r="G47" s="41" t="n">
         <f aca="false">G17-(G46+G26+G27)</f>
-        <v>1184.58154746405</v>
-      </c>
-      <c r="H47" s="39" t="n">
+        <v>485.559879071529</v>
+      </c>
+      <c r="H47" s="41" t="n">
         <f aca="false">H17-(H46+H26+H27)</f>
-        <v>3113.18079366013</v>
-      </c>
-      <c r="I47" s="39" t="n">
+        <v>1365.62662267882</v>
+      </c>
+      <c r="I47" s="41" t="n">
         <f aca="false">I17-(I46+I26+I27)</f>
-        <v>6962.93828732025</v>
+        <v>3467.82994535765</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -8215,12 +9149,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -8233,377 +9167,377 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>401</v>
+        <v>458</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>405</v>
+      <c r="A5" s="51" t="s">
+        <v>462</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>406</v>
+        <v>463</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>409</v>
+        <v>466</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
-        <v>411</v>
+      <c r="A6" s="51" t="s">
+        <v>468</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>413</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
-        <v>414</v>
+      <c r="A7" s="51" t="s">
+        <v>471</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>417</v>
+        <v>474</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
-        <v>419</v>
+      <c r="A8" s="51" t="s">
+        <v>476</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>422</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
-        <v>423</v>
+      <c r="A9" s="51" t="s">
+        <v>480</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
-        <v>428</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="51" t="s">
+        <v>485</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>430</v>
+        <v>487</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>431</v>
+        <v>488</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44" t="s">
-        <v>433</v>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="51" t="s">
+        <v>490</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>437</v>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="51" t="s">
+        <v>495</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>402</v>
+        <v>496</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>402</v>
+        <v>497</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>435</v>
+        <v>498</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>438</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
-        <v>439</v>
+      <c r="A13" s="51" t="s">
+        <v>500</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>441</v>
+        <v>502</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>442</v>
+        <v>503</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
-        <v>444</v>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="51" t="s">
+        <v>505</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>447</v>
+        <v>508</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>448</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>449</v>
+      <c r="A15" s="51" t="s">
+        <v>510</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>450</v>
+        <v>511</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>451</v>
+        <v>512</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>452</v>
+        <v>513</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>454</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
-        <v>455</v>
+      <c r="A16" s="51" t="s">
+        <v>516</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>456</v>
+        <v>517</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>457</v>
+        <v>518</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>458</v>
+        <v>519</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>459</v>
+        <v>520</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>460</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
-        <v>461</v>
+      <c r="A17" s="51" t="s">
+        <v>522</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>462</v>
+        <v>233</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>462</v>
+        <v>233</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>462</v>
+        <v>233</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>463</v>
+        <v>523</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>464</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
-        <v>465</v>
+      <c r="A18" s="51" t="s">
+        <v>525</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>467</v>
+        <v>527</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>468</v>
+        <v>528</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>469</v>
+        <v>529</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="44" t="s">
-        <v>470</v>
+      <c r="A19" s="51" t="s">
+        <v>530</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>471</v>
+        <v>531</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>471</v>
+        <v>531</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>472</v>
+        <v>532</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>473</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="s">
-        <v>474</v>
+      <c r="A20" s="51" t="s">
+        <v>534</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>475</v>
+        <v>535</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>476</v>
+        <v>535</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>472</v>
+        <v>532</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="s">
-        <v>478</v>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="51" t="s">
+        <v>537</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>479</v>
+        <v>538</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>480</v>
+        <v>539</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>482</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>483</v>
+        <v>542</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8615,82 +9549,95 @@
       <c r="A24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="29" t="s">
-        <v>484</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
+      <c r="B24" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="29" t="s">
-        <v>485</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
+      <c r="B25" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="29" t="s">
-        <v>486</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
+      <c r="B26" s="30" t="s">
+        <v>545</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
+      <c r="B27" s="30" t="s">
+        <v>546</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
+      <c r="B28" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+      <c r="B29" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -1522,7 +1522,7 @@
     <t xml:space="preserve">Pass only; practice never spends credits.</t>
   </si>
   <si>
-    <t xml:space="preserve">To build: 1 credit per play for Pro. Assumed: a play is one exercise the model marks or writes (one sentence reviewed, one text, one paper). If a play were a whole run, Pro's worst case would be several times higher.</t>
+    <t xml:space="preserve">Decided: a play is one exercise (one sentence reviewed, one text, one paper), so one credit never buys more than one exercise's AI cost. To build: 1 credit per play for Pro.</t>
   </si>
   <si>
     <t xml:space="preserve">Mock exam</t>
@@ -2540,11 +2540,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="5244941"/>
-        <c:axId val="35062061"/>
+        <c:axId val="3403515"/>
+        <c:axId val="2935780"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="5244941"/>
+        <c:axId val="3403515"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2610,7 +2610,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35062061"/>
+        <c:crossAx val="2935780"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2618,7 +2618,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35062061"/>
+        <c:axId val="2935780"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2694,7 +2694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5244941"/>
+        <c:crossAx val="3403515"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9295,7 +9295,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
         <v>485</v>
       </c>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="729">
   <si>
     <t xml:space="preserve">Tsuji — cost overview</t>
   </si>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">$ / month</t>
   </si>
   <si>
-    <t xml:space="preserve">scripts/llm_cost_model.py --fleet: Gemini 3.1 Flash-Lite, 70% light / 25% typical / 5% heavy, with caching. The free Explain button is included (phrase analysis, mostly cached).</t>
+    <t xml:space="preserve">Owner, 27 Oct 2026: early-access learners use little AI, so lowered from $0.27 (llm_cost_model.py, light-heavy blend). Replace with scripts/llm_usage_report.py.</t>
   </si>
   <si>
     <t xml:space="preserve">LLM cost – Pro user, worst case</t>
@@ -367,7 +367,7 @@
     <t xml:space="preserve">LLM cost – Max user, expected</t>
   </si>
   <si>
-    <t xml:space="preserve">llm_cost_model.py 'typical' user: Max buyers use the app more.</t>
+    <t xml:space="preserve">Lowered from $0.44 for the same reason (owner, 27 Oct 2026). Replace with the usage report.</t>
   </si>
   <si>
     <t xml:space="preserve">LLM cost – Max user, worst case</t>
@@ -460,19 +460,16 @@
     <t xml:space="preserve">Store trials that ask for a payment method commonly convert 30–60%. Replace with real data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Founder offer: discount on the first year of an annual plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner's decision, 26 Oct 2026: −25% and one month free, on every platform, for every account created before sales open. 'Pricing' shows what it does to the worst case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founder offer: share of annual payers in their founder year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of annual payers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cohort is closed (~100 accounts): at break-even (~70 annual payers) about 10 are founders. Set to 0 once their founder year has run out.</t>
+    <t xml:space="preserve">Founder offer: discount on the first year (monthly or annual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner's decision, 26-27 Oct 2026: −25% on the first year of any plan, monthly or annual, and one month of Max free, on every platform, for every account created before sales open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder offer: share of payers in their founder year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cohort is closed (~100 accounts): at break-even about 10 of the ~70 payers are founders. Set to 0 once their founder year has run out.</t>
   </si>
   <si>
     <t xml:space="preserve">Credit packs: share of free active users buying a pack in a month</t>
@@ -541,7 +538,7 @@
     <t xml:space="preserve">Target date for break-even (fixed costs covered)</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposal: the end-2026 goal could not be met (owner asked to adjust it). See 'Summary'.</t>
+    <t xml:space="preserve">Owner, 27 Oct 2026: more ambitious than the 30 June 2027 first proposed. See 'Summary'.</t>
   </si>
   <si>
     <t xml:space="preserve">Founder accounts (created before sales open)</t>
@@ -565,7 +562,7 @@
     <t xml:space="preserve">Founder month: share of founder accounts who use it</t>
   </si>
   <si>
-    <t xml:space="preserve">Every founder account gets the month; it only costs what an active account uses. Costed as Max, the dearer case.</t>
+    <t xml:space="preserve">Every founder account gets a month of Max (owner, 27 Oct 2026); it only costs what an active account uses.</t>
   </si>
   <si>
     <t xml:space="preserve">Pricing: pushing the annual Pro plan, with Max as the upgrade</t>
@@ -802,13 +799,13 @@
     <t xml:space="preserve">'Unit economics' and 'Projection' use the average indexes, so revenue already reflects regional prices. The shares of payers must add up to 100%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Founder offer: −25% on the first year of an annual plan and one free month, every platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full price (€/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founder price (€/yr)</t>
+    <t xml:space="preserve">Founder offer: −25% on the first year of any plan, and one month of Max free, every platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full price (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder price (€)</t>
   </si>
   <si>
     <t xml:space="preserve">Worst-case margin in-app (€/mo)</t>
@@ -823,16 +820,28 @@
     <t xml:space="preserve">Holds on the web?</t>
   </si>
   <si>
-    <t xml:space="preserve">In-app, a founder year loses money on a learner who maxes every AI allowance; on the web it holds. The cohort is closed (accounts created before sales open), so the loss is bounded: below.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founder rules to write: who qualifies (an account created before sales open), the free month (which plan, from when), the discount on the first year only, then the regular price with a reminder 30 days before renewal.</t>
+    <t xml:space="preserve">Pro annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder prices are rounded UP to a .99 store price point, so a monthly discount can land under 25% (Pro €3.99 is −20%). In-app a founder year can lose on a learner who maxes every AI allowance; the cohort is closed (accounts created before sales open), so the loss is bounded: below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder rules to write: who qualifies (an account created before sales open), the month of Max (from when), the discount on the first year only, then the regular price with a reminder 30 days before renewal.</t>
   </si>
   <si>
     <t xml:space="preserve">Founder cohort, worst case a month (every founder payer maxes the AI in-app)</t>
   </si>
   <si>
-    <t xml:space="preserve">The free month for the cohort, expected (one-off)</t>
+    <t xml:space="preserve">The month of Max for the cohort, expected (one-off)</t>
   </si>
   <si>
     <t xml:space="preserve">… if everyone who uses it maxes the AI (one-off)</t>
@@ -865,7 +874,7 @@
     <t xml:space="preserve">Due review on Pro and Max (credits)</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice exercise (2 to 5 by mode; average)</t>
+    <t xml:space="preserve">Practice exercise (average of the prices below)</t>
   </si>
   <si>
     <t xml:space="preserve">Due reviews a day of a steady Pro learner (for the comparison below)</t>
@@ -967,6 +976,75 @@
     <t xml:space="preserve">Proposal for the missions' 65 a day: three daily missions of 15 and a bonus of 10 for all three (55), and weekly missions worth about 70 (10 a day). A practice exercise asked by a mission costs nothing.</t>
   </si>
   <si>
+    <t xml:space="preserve">What a credit buys (owner's decisions, 27 Oct 2026). Max: everything included; inside a mission: free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New card (kana, vocab, kanji, grammar), Free and Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A due review: 1 on Free, free on Pro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading (one exercise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprehension (one text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the hand-written texts; no new text is generated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dictation (one exercise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translation (one exercise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past the AI cap, graded by the learner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition (one exercise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past the AI cap, without the tutor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversation (one scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past the AI cap, Choose and Translate go on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mock exam (one paper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the seeded papers; no new paper is generated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duel with a friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free, to build ties between learners.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duel with anyone else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score free; details and corrections in credits (price to set).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price to set (end of November 2026).</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI worst case: a user who uses every AI allowance to the full, every day</t>
   </si>
   <si>
@@ -1060,7 +1138,7 @@
     <t xml:space="preserve">month</t>
   </si>
   <si>
-    <t xml:space="preserve">Papers already in the pool stay open to all (credits). TODAY: 5 new papers a day (EXAM_PAPERS_DAILY_LIMIT).</t>
+    <t xml:space="preserve">Removed (owner, 27 Oct 2026): the seeded papers stay, 2 credits an exam. TODAY: 5 new papers a day.</t>
   </si>
   <si>
     <t xml:space="preserve">New comprehension text generated</t>
@@ -1069,7 +1147,7 @@
     <t xml:space="preserve">day</t>
   </si>
   <si>
-    <t xml:space="preserve">Texts from the pool are free to serve (30–60 hand-written seeds a level). TODAY: 10 a day (COMPREHENSION_DAILY_LIMIT).</t>
+    <t xml:space="preserve">Removed (owner, 27 Oct 2026): the 30–60 hand-written texts a level stay. TODAY: 10 a day.</t>
   </si>
   <si>
     <t xml:space="preserve">Composition review (one sentence)</t>
@@ -1473,7 +1551,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Not tied to any one user. §5.4: a full prewarm ≈ $4. Per-user LLM spend is in 'Unit economics'.</t>
+    <t xml:space="preserve">Generation of new exam papers and comprehension texts removed (owner, 27 Oct 2026): the pools are the hand-written seeds.</t>
   </si>
   <si>
     <t xml:space="preserve">Rotating residential proxy (fetching YouTube subtitles)</t>
@@ -1533,7 +1611,7 @@
     <t xml:space="preserve">Development tools (AI coding subscription, etc.)</t>
   </si>
   <si>
-    <t xml:space="preserve">PLACEHOLDER: enter what you actually pay.</t>
+    <t xml:space="preserve">Owner, 27 Oct 2026: a cost of the business, expected to drop at the end of 2026 once the app is well advanced. Enter the new figure then.</t>
   </si>
   <si>
     <t xml:space="preserve">Paid acquisition / ads</t>
@@ -1557,7 +1635,7 @@
     <t xml:space="preserve">Unit economics: what one subscriber brings in and costs, per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Prices are averaged over the regional tiers (Pricing) · annual plans are spread over 12 months · in-app and web sales are blended by the channel mix · VAT shown as if charged on the web too (the exemption is added back in 'Projection'). · annual plans carry the founder discount for the share of payers in their founder year (Assumptions) · the 7-day trial's cost is spread over the year it buys.</t>
+    <t xml:space="preserve">Prices are averaged over the regional tiers (Pricing) · annual plans are spread over 12 months · in-app and web sales are blended by the channel mix · VAT shown as if charged on the web too (the exemption is added back in 'Projection'). · every plan carries the founder discount for the share of payers in their founder year (Assumptions) · the 7-day trial's cost is spread over the year it buys.</t>
   </si>
   <si>
     <t xml:space="preserve">Average price paid incl. VAT (€)</t>
@@ -2068,13 +2146,13 @@
     <t xml:space="preserve">Practice modes</t>
   </si>
   <si>
-    <t xml:space="preserve">2 to 5 credits by mode; free inside a mission</t>
+    <t xml:space="preserve">Reading 1, comprehension 2, dictation 1, translation 1, composition 1, conversation 2; free inside a mission</t>
   </si>
   <si>
     <t xml:space="preserve">Pass only; practice never spends credits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decided. The price per mode to set.</t>
+    <t xml:space="preserve">Decided ('Credit shop').</t>
   </si>
   <si>
     <t xml:space="preserve">Solo games (end Nov 2026)</t>
@@ -2089,13 +2167,13 @@
     <t xml:space="preserve">PvP: async duels, real time between friends, friends list</t>
   </si>
   <si>
-    <t xml:space="preserve">Duels with friends free, others in credits; score free, corrections in credits</t>
+    <t xml:space="preserve">With a friend free, others 2 credits; score free, corrections in credits</t>
   </si>
   <si>
     <t xml:space="preserve">Beta this week.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decided. Friends found by unique username, report button, no chat. Questions at the lower of the two levels; speed adds points.</t>
+    <t xml:space="preserve">Decided. Friends found by unique username (only the username shows before a request is accepted, board_hidden included), report button, no chat. Questions at the lower of the two levels; speed adds points.</t>
   </si>
   <si>
     <t xml:space="preserve">Missions (daily, weekly), achievements</t>
@@ -2155,18 +2233,15 @@
     <t xml:space="preserve">Mock exams</t>
   </si>
   <si>
-    <t xml:space="preserve">Pool papers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pool + 2 new a month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pool + 4 new a month</t>
+    <t xml:space="preserve">Seeded papers, 2 credits an exam</t>
   </si>
   <si>
     <t xml:space="preserve">Pass only; 5 new papers a day.</t>
   </si>
   <si>
+    <t xml:space="preserve">Decided. Generating new papers and comprehension texts is removed (owner).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Decks</t>
   </si>
   <si>
@@ -2182,7 +2257,7 @@
     <t xml:space="preserve">Free 7 / 200; pass 100 / 10,000.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decided: a published deck with a minimum of followers (e.g. 3) counts in no limit.</t>
+    <t xml:space="preserve">Decided: a published deck with 5 followers or more counts in no limit.</t>
   </si>
   <si>
     <t xml:space="preserve">Analyser history</t>
@@ -2224,7 +2299,7 @@
     <t xml:space="preserve">Founder offer</t>
   </si>
   <si>
-    <t xml:space="preserve">−25% first year + 1 free month</t>
+    <t xml:space="preserve">−25% first year (monthly or annual) + 1 month of Max</t>
   </si>
   <si>
     <t xml:space="preserve">Decided: every platform, every account created before sales open (~9 Nov 2026). Bounded worst case ('Pricing').</t>
@@ -3157,28 +3232,28 @@
                 <c:formatCode>\€#,##0.00;"(€"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>232.68245</c:v>
+                  <c:v>230.60125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>232.68245</c:v>
+                  <c:v>230.60125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232.68245</c:v>
+                  <c:v>230.60125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>355.32145</c:v>
+                  <c:v>350.11845</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>355.32145</c:v>
+                  <c:v>350.11845</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>355.32145</c:v>
+                  <c:v>350.11845</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>736.5767</c:v>
+                  <c:v>726.1707</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>736.5767</c:v>
+                  <c:v>726.1707</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3193,11 +3268,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2450262"/>
-        <c:axId val="84261895"/>
+        <c:axId val="97545314"/>
+        <c:axId val="63858619"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2450262"/>
+        <c:axId val="97545314"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3263,7 +3338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84261895"/>
+        <c:crossAx val="63858619"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3271,7 +3346,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84261895"/>
+        <c:axId val="63858619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3347,7 +3422,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2450262"/>
+        <c:crossAx val="97545314"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3699,7 +3774,7 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">'Fixed costs'!$I$24</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3708,7 +3783,7 @@
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">'Fixed costs'!$J$24</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3717,7 +3792,7 @@
       </c>
       <c r="B15" s="7" t="n">
         <f aca="false">'Fixed costs'!$K$24</f>
-        <v>736.5767</v>
+        <v>726.1707</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3726,7 +3801,7 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">'Start-up costs'!$I$23+12*'Fixed costs'!$I$24</f>
-        <v>3771.5164</v>
+        <v>3746.542</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3741,7 +3816,7 @@
       </c>
       <c r="B19" s="7" t="n">
         <f aca="false">'Unit economics'!$O$11</f>
-        <v>2.50400700896495</v>
+        <v>2.59429313856742</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3750,7 +3825,7 @@
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">'Unit economics'!$O$12</f>
-        <v>4.03520547678296</v>
+        <v>4.12650227972841</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3759,7 +3834,7 @@
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">'Unit economics'!$O$13</f>
-        <v>2.7824067303864</v>
+        <v>2.87287661877851</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3768,7 +3843,7 @@
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">'Unit economics'!$R$13</f>
-        <v>0.484572730386401</v>
+        <v>0.516528261778512</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3777,7 +3852,7 @@
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3792,7 +3867,7 @@
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">'Unit economics'!$D$23</f>
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3801,7 +3876,7 @@
       </c>
       <c r="B27" s="10" t="n">
         <f aca="false">'Unit economics'!$E$23</f>
-        <v>1470</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3853,35 +3928,35 @@
       </c>
       <c r="B31" s="11" t="n">
         <f aca="false">Projection!B18</f>
-        <v>23.2718063723343</v>
+        <v>22.9495933627859</v>
       </c>
       <c r="C31" s="11" t="n">
         <f aca="false">Projection!C18</f>
-        <v>113.144759308562</v>
+        <v>111.614901866409</v>
       </c>
       <c r="D31" s="11" t="n">
         <f aca="false">Projection!D18</f>
-        <v>223.212498462884</v>
+        <v>220.193387381372</v>
       </c>
       <c r="E31" s="11" t="n">
         <f aca="false">Projection!E18</f>
-        <v>556.629988478959</v>
+        <v>549.061908873781</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">Projection!F18</f>
-        <v>1113.12272455905</v>
+        <v>1098.02716915149</v>
       </c>
       <c r="G31" s="11" t="n">
         <f aca="false">Projection!G18</f>
-        <v>2060.88811396603</v>
+        <v>2033.27599145669</v>
       </c>
       <c r="H31" s="11" t="n">
         <f aca="false">Projection!H18</f>
-        <v>5153.69016879277</v>
+        <v>5084.65986251942</v>
       </c>
       <c r="I31" s="11" t="n">
         <f aca="false">Projection!I18</f>
-        <v>10304.4405698302</v>
+        <v>10166.3799572835</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3890,35 +3965,35 @@
       </c>
       <c r="B32" s="11" t="n">
         <f aca="false">Projection!B29</f>
-        <v>237.561452</v>
+        <v>233.680014</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">Projection!C29</f>
-        <v>256.53716</v>
+        <v>245.683702</v>
       </c>
       <c r="D32" s="11" t="n">
         <f aca="false">Projection!D29</f>
-        <v>280.12172</v>
+        <v>260.61047</v>
       </c>
       <c r="E32" s="11" t="n">
         <f aca="false">Projection!E29</f>
-        <v>474.0547</v>
+        <v>425.219342</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">Projection!F29</f>
-        <v>592.5178</v>
+        <v>500.16455</v>
       </c>
       <c r="G32" s="11" t="n">
         <f aca="false">Projection!G29</f>
-        <v>829.71415</v>
+        <v>650.21065</v>
       </c>
       <c r="H32" s="11" t="n">
         <f aca="false">Projection!H29</f>
-        <v>1922.55845</v>
+        <v>1476.4012</v>
       </c>
       <c r="I32" s="11" t="n">
         <f aca="false">Projection!I29</f>
-        <v>3108.5402</v>
+        <v>2226.6317</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3947,15 +4022,15 @@
       </c>
       <c r="G33" s="11" t="n">
         <f aca="false">Projection!G34</f>
-        <v>103.987062613037</v>
+        <v>135.124794998622</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">Projection!H34</f>
-        <v>662.382002352517</v>
+        <v>739.693025816482</v>
       </c>
       <c r="I33" s="11" t="n">
         <f aca="false">Projection!I34</f>
-        <v>1475.15957581518</v>
+        <v>1627.64839274311</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3964,35 +4039,35 @@
       </c>
       <c r="B34" s="11" t="n">
         <f aca="false">Projection!B35</f>
-        <v>-214.289645627666</v>
+        <v>-210.730420637214</v>
       </c>
       <c r="C34" s="11" t="n">
         <f aca="false">Projection!C35</f>
-        <v>-143.392400691438</v>
+        <v>-134.068800133591</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">Projection!D35</f>
-        <v>-56.9092215371157</v>
+        <v>-40.4170826186281</v>
       </c>
       <c r="E34" s="11" t="n">
         <f aca="false">Projection!E35</f>
-        <v>82.5752884789591</v>
+        <v>123.842566873781</v>
       </c>
       <c r="F34" s="11" t="n">
         <f aca="false">Projection!F35</f>
-        <v>520.60492455905</v>
+        <v>597.862619151488</v>
       </c>
       <c r="G34" s="11" t="n">
         <f aca="false">Projection!G35</f>
-        <v>1127.186901353</v>
+        <v>1247.94054645807</v>
       </c>
       <c r="H34" s="11" t="n">
         <f aca="false">Projection!H35</f>
-        <v>2568.74971644025</v>
+        <v>2868.56563670294</v>
       </c>
       <c r="I34" s="11" t="n">
         <f aca="false">Projection!I35</f>
-        <v>5720.74079401498</v>
+        <v>6312.09986454036</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4075,35 +4150,35 @@
       </c>
       <c r="B37" s="7" t="n">
         <f aca="false">Projection!B40</f>
-        <v>2.37561452</v>
+        <v>2.33680014</v>
       </c>
       <c r="C37" s="7" t="n">
         <f aca="false">Projection!C40</f>
-        <v>0.51307432</v>
+        <v>0.491367404</v>
       </c>
       <c r="D37" s="7" t="n">
         <f aca="false">Projection!D40</f>
-        <v>0.28012172</v>
+        <v>0.26061047</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">Projection!E40</f>
-        <v>0.18962188</v>
+        <v>0.1700877368</v>
       </c>
       <c r="F37" s="7" t="n">
         <f aca="false">Projection!F40</f>
-        <v>0.11850356</v>
+        <v>0.10003291</v>
       </c>
       <c r="G37" s="7" t="n">
         <f aca="false">Projection!G40</f>
-        <v>0.082971415</v>
+        <v>0.065021065</v>
       </c>
       <c r="H37" s="7" t="n">
         <f aca="false">Projection!H40</f>
-        <v>0.076902338</v>
+        <v>0.059056048</v>
       </c>
       <c r="I37" s="7" t="n">
         <f aca="false">Projection!I40</f>
-        <v>0.062170804</v>
+        <v>0.044532634</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4112,35 +4187,35 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">Projection!B41</f>
-        <v>39.5935753333333</v>
+        <v>38.946669</v>
       </c>
       <c r="C38" s="7" t="n">
         <f aca="false">Projection!C41</f>
-        <v>9.16204142857143</v>
+        <v>8.77441792857143</v>
       </c>
       <c r="D38" s="7" t="n">
         <f aca="false">Projection!D41</f>
-        <v>5.09312218181818</v>
+        <v>4.73837218181818</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">Projection!E41</f>
-        <v>3.43517898550725</v>
+        <v>3.08129957971015</v>
       </c>
       <c r="F38" s="7" t="n">
         <f aca="false">Projection!F41</f>
-        <v>2.15461018181818</v>
+        <v>1.81878018181818</v>
       </c>
       <c r="G38" s="7" t="n">
         <f aca="false">Projection!G41</f>
-        <v>1.50857118181818</v>
+        <v>1.18220118181818</v>
       </c>
       <c r="H38" s="7" t="n">
         <f aca="false">Projection!H41</f>
-        <v>1.39822432727273</v>
+        <v>1.07374632727273</v>
       </c>
       <c r="I38" s="7" t="n">
         <f aca="false">Projection!I41</f>
-        <v>1.13037825454545</v>
+        <v>0.809684254545455</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4164,7 +4239,7 @@
       </c>
       <c r="B42" s="15" t="n">
         <f aca="false">'Unit economics'!$E$23</f>
-        <v>1470</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,7 +4248,7 @@
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">IF(OR(B41=0,NOT(ISNUMBER(B42))),0,B42/B41)</f>
-        <v>58.8</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4182,7 +4257,7 @@
       </c>
       <c r="B44" s="17" t="n">
         <f aca="true">MAX(0,(Assumptions!$B$61-TODAY())/30.44)</f>
-        <v>8.11432325886991</v>
+        <v>5.09198423127464</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4191,7 +4266,7 @@
       </c>
       <c r="B45" s="18" t="n">
         <f aca="false">IF(OR(B41=0,B44=0,NOT(ISNUMBER(B42))),0,(B42/B41)^(1/B44)-1)</f>
-        <v>0.652175036424316</v>
+        <v>1.18342833104302</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,7 +4275,7 @@
       </c>
       <c r="B46" s="19" t="n">
         <f aca="true">IF(B45=0,0,B41*(1+B45)^(MAX(0,DATE(2026,12,31)-TODAY())/30.44))</f>
-        <v>74.255579504476</v>
+        <v>132.470673737166</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,7 +4284,7 @@
       </c>
       <c r="B47" s="19" t="n">
         <f aca="true">IF(B45=0,0,B41*(1+B45)^(MAX(0,Assumptions!$B$60-TODAY())/30.44))</f>
-        <v>31.4940564840997</v>
+        <v>34.8960247260582</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4316,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
@@ -4251,7 +4326,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
@@ -4269,500 +4344,502 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="71" t="s">
-        <v>595</v>
+        <v>621</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="71" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>604</v>
+        <v>630</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>606</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="71" t="s">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>610</v>
+        <v>636</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>612</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="71" t="s">
-        <v>613</v>
+        <v>639</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>614</v>
+        <v>640</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>616</v>
+        <v>642</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="71" t="s">
+        <v>644</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>645</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>619</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>592</v>
-      </c>
       <c r="D9" s="22" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="71" t="s">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>622</v>
+        <v>648</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>624</v>
+        <v>650</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="71" t="s">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>626</v>
+        <v>652</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>627</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="71" t="s">
-        <v>628</v>
+        <v>654</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="71" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="71" t="s">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>636</v>
+        <v>662</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>637</v>
+        <v>663</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>638</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="71" t="s">
-        <v>639</v>
+        <v>665</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>640</v>
+        <v>666</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>640</v>
+        <v>666</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>641</v>
+        <v>667</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>642</v>
+        <v>668</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>643</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="71" t="s">
-        <v>644</v>
+        <v>670</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>647</v>
+        <v>673</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="71" t="s">
-        <v>648</v>
+        <v>674</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>650</v>
+        <v>676</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="71" t="s">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>652</v>
+        <v>678</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>653</v>
+        <v>679</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>654</v>
+        <v>680</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>655</v>
+        <v>681</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>656</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="71" t="s">
-        <v>657</v>
+        <v>683</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>661</v>
-      </c>
-      <c r="F19" s="22"/>
+        <v>685</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="71" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="71" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="71" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="71" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="71" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="71" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="71" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="71" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="71" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4775,7 +4852,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -4788,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -4800,7 +4877,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="C32" s="40"/>
       <c r="D32" s="40"/>
@@ -4812,7 +4889,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="C33" s="40"/>
       <c r="D33" s="40"/>
@@ -4824,7 +4901,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
@@ -4836,7 +4913,7 @@
         <v>5</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="C35" s="40"/>
       <c r="D35" s="40"/>
@@ -4848,7 +4925,7 @@
         <v>6</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -4860,7 +4937,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="40"/>
@@ -5282,7 +5359,7 @@
         <v>106</v>
       </c>
       <c r="B31" s="29" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>107</v>
@@ -5297,7 +5374,7 @@
       </c>
       <c r="B32" s="30" t="n">
         <f aca="false">'AI worst case'!$L$26</f>
-        <v>2.4</v>
+        <v>2.306505</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>107</v>
@@ -5311,7 +5388,7 @@
         <v>111</v>
       </c>
       <c r="B33" s="29" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>107</v>
@@ -5479,7 +5556,7 @@
         <v>136</v>
       </c>
       <c r="B49" s="29" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>107</v>
@@ -5539,165 +5616,165 @@
         <v>0.15</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B54" s="23" t="n">
         <v>0.01</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B55" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B56" s="33" t="n">
         <v>1.2</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B57" s="7" t="n">
         <f aca="false">'Credit shop'!$C$21</f>
         <v>3.39</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B58" s="25" t="n">
         <v>0.9</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B59" s="31" t="n">
         <v>25</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B60" s="34" t="n">
         <v>46335</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B61" s="35" t="n">
+        <v>46477</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="B61" s="35" t="n">
-        <v>46568</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B62" s="36" t="n">
         <v>100</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B63" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B64" s="23" t="n">
         <v>0.5</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5716,7 +5793,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
@@ -5730,46 +5807,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="20" t="s">
         <v>187</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>8.99</v>
@@ -5793,10 +5870,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>59.99</v>
@@ -5824,10 +5901,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>14.99</v>
@@ -5851,10 +5928,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>99.99</v>
@@ -5882,7 +5959,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -5894,7 +5971,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D11" s="37" t="n">
         <f aca="false">D8-D6</f>
@@ -5907,7 +5984,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">(D8-D6)/12</f>
@@ -5916,7 +5993,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D13" s="37" t="n">
         <f aca="false">D7-D5</f>
@@ -5925,12 +6002,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5942,32 +6019,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="C17" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="D17" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="E17" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
       <c r="H17" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="C18" s="39" t="n">
         <v>9</v>
@@ -5979,35 +6056,35 @@
         <v>299</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="C19" s="39" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E19" s="39" t="n">
         <v>150</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="C20" s="39" t="n">
         <v>6.99</v>
@@ -6019,32 +6096,32 @@
         <v>109.99</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="C21" s="39" t="n">
         <v>14</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -6059,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="40"/>
@@ -6073,7 +6150,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40"/>
@@ -6087,7 +6164,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -6101,7 +6178,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
@@ -6115,7 +6192,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -6129,7 +6206,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="40"/>
@@ -6143,7 +6220,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
@@ -6157,7 +6234,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -6168,7 +6245,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -6186,54 +6263,54 @@
     </row>
     <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="C34" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="D34" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="E34" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="F34" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="G34" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="H34" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="I34" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="I34" s="20" t="s">
+      <c r="J34" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="J34" s="20" t="s">
+      <c r="K34" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="L34" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="L34" s="20" t="s">
+      <c r="M34" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="M34" s="20" t="s">
+      <c r="N34" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="N34" s="20" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>242</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>243</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>0.7</v>
@@ -6262,11 +6339,11 @@
       </c>
       <c r="J35" s="37" t="n">
         <f aca="false">MIN(F35/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F35/(1+Assumptions!$B$7)-(F35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$33-Assumptions!$B$36</f>
-        <v>0.987931900826446</v>
+        <v>1.08522279782645</v>
       </c>
       <c r="K35" s="37" t="n">
         <f aca="false">MIN(G35/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G35/(1+Assumptions!$B$7)-(G35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$33-Assumptions!$B$36</f>
-        <v>0.408971845730028</v>
+        <v>0.506262742730028</v>
       </c>
       <c r="L35" s="37" t="n">
         <f aca="false">MIN(H35/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H35/(1+Assumptions!$B$7)-(H35*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$33-Assumptions!$B$36</f>
@@ -6283,10 +6360,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>244</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>245</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>0.15</v>
@@ -6315,11 +6392,11 @@
       </c>
       <c r="J36" s="37" t="n">
         <f aca="false">MIN(F36/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F36/(1+Assumptions!$B$7)-(F36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$34-Assumptions!$B$36</f>
-        <v>0.939987360483471</v>
+        <v>1.05469529998347</v>
       </c>
       <c r="K36" s="37" t="n">
         <f aca="false">MIN(G36/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G36/(1+Assumptions!$B$7)-(G36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$34-Assumptions!$B$36</f>
-        <v>0.361027305387052</v>
+        <v>0.475735244887052</v>
       </c>
       <c r="L36" s="37" t="n">
         <f aca="false">MIN(H36/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H36/(1+Assumptions!$B$7)-(H36*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$34-Assumptions!$B$36</f>
@@ -6336,10 +6413,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B37" s="22" t="s">
         <v>246</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>247</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0.1</v>
@@ -6368,11 +6445,11 @@
       </c>
       <c r="J37" s="37" t="n">
         <f aca="false">MIN(F37/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(F37/(1+Assumptions!$B$7)-(F37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$F$35-Assumptions!$B$36</f>
-        <v>0.733015726640496</v>
+        <v>0.847723666140496</v>
       </c>
       <c r="K37" s="37" t="n">
         <f aca="false">MIN(G37/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(G37/(1+Assumptions!$B$7)-(G37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12)-'AI worst case'!$F$35-Assumptions!$B$36</f>
-        <v>0.27113556135124</v>
+        <v>0.38584350085124</v>
       </c>
       <c r="L37" s="37" t="n">
         <f aca="false">MIN(H37/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21),(H37/(1+Assumptions!$B$7)-(H37*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1)-'AI worst case'!$G$35-Assumptions!$B$36</f>
@@ -6389,10 +6466,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>248</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>249</v>
       </c>
       <c r="C38" s="23" t="n">
         <v>0.05</v>
@@ -6442,7 +6519,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C39" s="41" t="n">
         <f aca="false">SUM(C35:C38)</f>
@@ -6459,37 +6536,37 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -6501,30 +6578,30 @@
     </row>
     <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="D49" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="E49" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="F49" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="G49" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="B50" s="37" t="n">
         <f aca="false">$D$6</f>
@@ -6536,11 +6613,11 @@
       </c>
       <c r="D50" s="37" t="n">
         <f aca="false">C50/12/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-'AI worst case'!$F$33-Assumptions!$B$36</f>
-        <v>-0.293507493112948</v>
+        <v>-0.196216596112948</v>
       </c>
       <c r="E50" s="37" t="n">
         <f aca="false">(C50-(C50*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/12-'AI worst case'!$F$33-Assumptions!$B$36</f>
-        <v>0.557911666666667</v>
+        <v>0.655202563666667</v>
       </c>
       <c r="F50" s="6" t="str">
         <f aca="false">IF(D50&gt;='AI worst case'!$B$10,"yes","NO")</f>
@@ -6553,7 +6630,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>192</v>
+        <v>264</v>
       </c>
       <c r="B51" s="37" t="n">
         <f aca="false">$D$8</f>
@@ -6580,53 +6657,111 @@
         <v>yes</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="B52" s="40"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-    </row>
-    <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="40" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="B52" s="37" t="n">
+        <f aca="false">$D$5</f>
+        <v>4.99</v>
+      </c>
+      <c r="C52" s="37" t="n">
+        <f aca="false">MAX(0.99,CEILING($D$5*(1-Assumptions!$B$52),1)-0.01)</f>
+        <v>3.99</v>
+      </c>
+      <c r="D52" s="37" t="n">
+        <f aca="false">C52/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-'AI worst case'!$F$33-Assumptions!$B$36</f>
+        <v>0.382743458983471</v>
+      </c>
+      <c r="E52" s="37" t="n">
+        <f aca="false">(C52-(C52*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1-'AI worst case'!$F$33-Assumptions!$B$36</f>
+        <v>1.232070897</v>
+      </c>
+      <c r="F52" s="6" t="str">
+        <f aca="false">IF(D52&gt;='AI worst case'!$B$10,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="G52" s="6" t="str">
+        <f aca="false">IF(E52&gt;='AI worst case'!$B$10,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D54" s="43" t="n">
-        <f aca="false">Assumptions!$B$62*Assumptions!$B$63*MAX(0,-MIN(D50,D51))</f>
-        <v>2.93507493112948</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="B53" s="37" t="n">
+        <f aca="false">$D$7</f>
+        <v>7.99</v>
+      </c>
+      <c r="C53" s="37" t="n">
+        <f aca="false">MAX(0.99,CEILING($D$7*(1-Assumptions!$B$52),1)-0.01)</f>
+        <v>5.99</v>
+      </c>
+      <c r="D53" s="37" t="n">
+        <f aca="false">C53/1/(1+Assumptions!$B$7)*(1-Assumptions!$B$21)-'AI worst case'!$G$33-Assumptions!$B$36</f>
+        <v>1.06605123966942</v>
+      </c>
+      <c r="E53" s="37" t="n">
+        <f aca="false">(C53-(C53*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23))/1-'AI worst case'!$G$33-Assumptions!$B$36</f>
+        <v>2.46642</v>
+      </c>
+      <c r="F53" s="6" t="str">
+        <f aca="false">IF(D53&gt;='AI worst case'!$B$10,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+      <c r="G53" s="6" t="str">
+        <f aca="false">IF(E53&gt;='AI worst case'!$B$10,"yes","NO")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="D55" s="43" t="n">
-        <f aca="false">Assumptions!$B$62*Assumptions!$B$64*('Unit economics'!$M$8+'Unit economics'!$N$8)</f>
-        <v>23.8932</v>
-      </c>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+    </row>
+    <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D56" s="43" t="n">
+        <f aca="false">Assumptions!$B$62*Assumptions!$B$63*MAX(0,-MIN(D50:D53))</f>
+        <v>1.96216596112948</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D57" s="43" t="n">
+        <f aca="false">Assumptions!$B$62*Assumptions!$B$64*('Unit economics'!$M$8+'Unit economics'!$N$8)</f>
+        <v>14.0075</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D58" s="43" t="n">
         <f aca="false">Assumptions!$B$62*Assumptions!$B$64*('AI worst case'!$M$27+Assumptions!$B$36)</f>
         <v>157.09</v>
       </c>
@@ -6641,8 +6776,8 @@
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B31:H31"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="J35:M38">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6667,7 +6802,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="72"/>
@@ -6681,17 +6816,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -6703,7 +6838,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>60</v>
@@ -6711,7 +6846,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>90</v>
@@ -6719,7 +6854,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>120</v>
@@ -6727,7 +6862,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B8" s="31" t="n">
         <v>200</v>
@@ -6735,7 +6870,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B9" s="31" t="n">
         <v>1</v>
@@ -6743,7 +6878,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B10" s="31" t="n">
         <v>0</v>
@@ -6751,15 +6886,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" s="33" t="n">
-        <v>3</v>
+        <v>281</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <f aca="false">AVERAGE(B44:B49)</f>
+        <v>1.33333333333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B12" s="31" t="n">
         <v>60</v>
@@ -6767,7 +6903,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B13" s="31" t="n">
         <v>125</v>
@@ -6775,7 +6911,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -6787,33 +6923,33 @@
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B16" s="36" t="n">
         <v>100</v>
@@ -6843,7 +6979,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B17" s="36" t="n">
         <v>330</v>
@@ -6873,7 +7009,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B18" s="36" t="n">
         <v>600</v>
@@ -6903,7 +7039,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B19" s="36" t="n">
         <v>1300</v>
@@ -6933,7 +7069,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F20" s="18" t="n">
         <f aca="false">SUM(F16:F19)</f>
@@ -6942,7 +7078,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C21" s="43" t="n">
         <f aca="false">SUMPRODUCT(C16:C19,F16:F19)</f>
@@ -6959,7 +7095,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G22" s="45" t="n">
         <f aca="false">Assumptions!$B$58*G21+(1-Assumptions!$B$58)*H21</f>
@@ -6968,7 +7104,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -6980,7 +7116,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">(B7-B5)*30</f>
@@ -6989,7 +7125,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">B12*30*(B9-B10)</f>
@@ -6998,7 +7134,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">B25+B26</f>
@@ -7007,7 +7143,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B28" s="37" t="n">
         <f aca="false">B27*MIN(D16:D19)/100</f>
@@ -7016,7 +7152,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$10=0,0,B28/Assumptions!$B$10)</f>
@@ -7025,7 +7161,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B30" s="23" t="n">
         <v>0.5</v>
@@ -7033,7 +7169,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B31" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$10=0,0,B28/(1+B30)/Assumptions!$B$10)</f>
@@ -7042,7 +7178,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B32" s="46" t="n">
         <v>1.5</v>
@@ -7050,7 +7186,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B33" s="8" t="str">
         <f aca="false">IF(MIN(B29,B31)&gt;=B32,"yes","NO: raise the pack prices or shrink the bonus")</f>
@@ -7059,7 +7195,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">B13-B5</f>
@@ -7068,7 +7204,7 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -7080,7 +7216,7 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B37" s="40"/>
       <c r="C37" s="40"/>
@@ -7092,7 +7228,7 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -7104,7 +7240,7 @@
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -7113,6 +7249,146 @@
       <c r="F39" s="40"/>
       <c r="G39" s="40"/>
       <c r="H39" s="40"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B49" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B50" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B52" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>337</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7151,17 +7427,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -7169,32 +7445,32 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="B5" s="39" t="n">
         <v>0.25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B6" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>0.6</v>
@@ -7205,87 +7481,87 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="B8" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="B9" s="31" t="n">
         <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>0.1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="M12" s="20" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="N12" s="20" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="47" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="B13" s="48" t="n">
         <v>35</v>
@@ -7301,16 +7577,16 @@
         <v>0.1102325</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G13" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" s="53" t="n">
         <f aca="false">IF(F13="day",$B$9,1)</f>
@@ -7322,19 +7598,19 @@
       </c>
       <c r="L13" s="54" t="n">
         <f aca="false">H13*$E13*$J13</f>
-        <v>0.220465</v>
+        <v>0</v>
       </c>
       <c r="M13" s="54" t="n">
         <f aca="false">I13*$E13*$J13</f>
-        <v>0.44093</v>
+        <v>0</v>
       </c>
       <c r="N13" s="55" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="47" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="B14" s="48" t="n">
         <v>1.3</v>
@@ -7350,16 +7626,16 @@
         <v>0.00625365</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G14" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="53" t="n">
         <f aca="false">IF(F14="day",$B$9,1)</f>
@@ -7371,19 +7647,19 @@
       </c>
       <c r="L14" s="54" t="n">
         <f aca="false">H14*$E14*$J14</f>
-        <v>0.1876095</v>
+        <v>0</v>
       </c>
       <c r="M14" s="54" t="n">
         <f aca="false">I14*$E14*$J14</f>
-        <v>0.375219</v>
+        <v>0</v>
       </c>
       <c r="N14" s="55" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="47" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B15" s="48" t="n">
         <v>1</v>
@@ -7399,7 +7675,7 @@
         <v>0.0007035</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G15" s="52" t="n">
         <v>3</v>
@@ -7427,12 +7703,12 @@
         <v>0.527625</v>
       </c>
       <c r="N15" s="55" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="47" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="B16" s="48" t="n">
         <v>1</v>
@@ -7448,7 +7724,7 @@
         <v>0.000669</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G16" s="52" t="n">
         <v>3</v>
@@ -7476,12 +7752,12 @@
         <v>0.50175</v>
       </c>
       <c r="N16" s="55" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="47" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="B17" s="48" t="n">
         <v>1</v>
@@ -7497,7 +7773,7 @@
         <v>0.0008705</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G17" s="52" t="n">
         <v>6</v>
@@ -7525,12 +7801,12 @@
         <v>0.78345</v>
       </c>
       <c r="N17" s="55" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="47" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="B18" s="48" t="n">
         <v>1</v>
@@ -7546,7 +7822,7 @@
         <v>0.0007265</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G18" s="52" t="n">
         <v>2</v>
@@ -7574,12 +7850,12 @@
         <v>0.326925</v>
       </c>
       <c r="N18" s="55" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="47" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="B19" s="48" t="n">
         <v>1</v>
@@ -7595,7 +7871,7 @@
         <v>0.000341</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G19" s="52" t="n">
         <v>5</v>
@@ -7623,12 +7899,12 @@
         <v>0.4092</v>
       </c>
       <c r="N19" s="55" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="47" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B20" s="48" t="n">
         <v>1</v>
@@ -7644,7 +7920,7 @@
         <v>0.000796</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G20" s="52" t="n">
         <v>5</v>
@@ -7672,12 +7948,12 @@
         <v>0.7164</v>
       </c>
       <c r="N20" s="55" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="47" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="B21" s="48" t="n">
         <v>1</v>
@@ -7693,7 +7969,7 @@
         <v>0.000761</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G21" s="52" t="n">
         <v>1</v>
@@ -7721,12 +7997,12 @@
         <v>0.34245</v>
       </c>
       <c r="N21" s="55" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="47" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B22" s="48" t="n">
         <v>1</v>
@@ -7742,7 +8018,7 @@
         <v>0.0011535</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G22" s="52" t="n">
         <v>2</v>
@@ -7770,12 +8046,12 @@
         <v>0.6921</v>
       </c>
       <c r="N22" s="55" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="47" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B23" s="48" t="n">
         <v>1</v>
@@ -7791,7 +8067,7 @@
         <v>0.001511</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G23" s="52" t="n">
         <v>0</v>
@@ -7819,12 +8095,12 @@
         <v>0.22665</v>
       </c>
       <c r="N23" s="55" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="K24" s="56" t="n">
         <f aca="false">SUM(K13:K23)</f>
@@ -7832,16 +8108,16 @@
       </c>
       <c r="L24" s="56" t="n">
         <f aca="false">SUM(L13:L23)</f>
-        <v>2.7145795</v>
+        <v>2.306505</v>
       </c>
       <c r="M24" s="56" t="n">
         <f aca="false">SUM(M13:M23)</f>
-        <v>5.342699</v>
+        <v>4.52655</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="G25" s="57" t="n">
         <v>0.01</v>
@@ -7865,12 +8141,12 @@
         <v>3</v>
       </c>
       <c r="N25" s="22" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="K26" s="59" t="n">
         <f aca="false">MIN(K24,K25)</f>
@@ -7878,7 +8154,7 @@
       </c>
       <c r="L26" s="59" t="n">
         <f aca="false">MIN(L24,L25)</f>
-        <v>2.4</v>
+        <v>2.306505</v>
       </c>
       <c r="M26" s="59" t="n">
         <f aca="false">MIN(M24,M25)</f>
@@ -7887,7 +8163,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="K27" s="37" t="n">
         <f aca="false">K26*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -7895,7 +8171,7 @@
       </c>
       <c r="L27" s="37" t="n">
         <f aca="false">L26*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>2.49744</v>
+        <v>2.400149103</v>
       </c>
       <c r="M27" s="37" t="n">
         <f aca="false">M26*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -7904,7 +8180,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="G28" s="19" t="n">
         <f aca="false">IF($E$15=0,0,G25/$E$15)</f>
@@ -7921,7 +8197,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="G29" s="19" t="n">
         <f aca="false">IF($E$19=0,0,G25/$E$19)</f>
@@ -7938,7 +8214,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -7949,25 +8225,25 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7985,7 +8261,7 @@
       </c>
       <c r="D33" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($H$13:$H$23*B33,0),$E$13:$E$23,$J$13:$J$23),$H$25*B33*$B$9)</f>
-        <v>2.4</v>
+        <v>2.306505</v>
       </c>
       <c r="E33" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($I$13:$I$23*C33,0),$E$13:$E$23,$J$13:$J$23),$I$25*C33*$B$9)</f>
@@ -7993,7 +8269,7 @@
       </c>
       <c r="F33" s="37" t="n">
         <f aca="false">D33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>2.49744</v>
+        <v>2.400149103</v>
       </c>
       <c r="G33" s="37" t="n">
         <f aca="false">E33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -8015,7 +8291,7 @@
       </c>
       <c r="D34" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($H$13:$H$23*B34,0),$E$13:$E$23,$J$13:$J$23),$H$25*B34*$B$9)</f>
-        <v>1.7710025</v>
+        <v>1.66077</v>
       </c>
       <c r="E34" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($I$13:$I$23*C34,0),$E$13:$E$23,$J$13:$J$23),$I$25*C34*$B$9)</f>
@@ -8023,7 +8299,7 @@
       </c>
       <c r="F34" s="37" t="n">
         <f aca="false">D34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>1.8429052015</v>
+        <v>1.728197262</v>
       </c>
       <c r="G34" s="37" t="n">
         <f aca="false">E34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -8045,7 +8321,7 @@
       </c>
       <c r="D35" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($H$13:$H$23*B35,0),$E$13:$E$23,$J$13:$J$23),$H$25*B35*$B$9)</f>
-        <v>1.2948275</v>
+        <v>1.184595</v>
       </c>
       <c r="E35" s="58" t="n">
         <f aca="false">MIN(SUMPRODUCT(ROUNDDOWN($I$13:$I$23*C35,0),$E$13:$E$23,$J$13:$J$23),$I$25*C35*$B$9)</f>
@@ -8053,7 +8329,7 @@
       </c>
       <c r="F35" s="37" t="n">
         <f aca="false">D35*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>1.3473974965</v>
+        <v>1.232689557</v>
       </c>
       <c r="G35" s="37" t="n">
         <f aca="false">E35*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -8092,7 +8368,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -8110,7 +8386,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="40" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -8128,7 +8404,7 @@
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="40" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
@@ -8181,61 +8457,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E5" s="64" t="n">
         <v>111.5</v>
@@ -8259,21 +8535,21 @@
         <v>111.5</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C6" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E6" s="64" t="n">
         <v>0</v>
@@ -8297,21 +8573,21 @@
         <v>0</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E7" s="64" t="n">
         <v>0</v>
@@ -8335,21 +8611,21 @@
         <v>0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C8" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E8" s="64" t="n">
         <v>0</v>
@@ -8373,21 +8649,21 @@
         <v>0</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E9" s="64" t="n">
         <v>1000</v>
@@ -8411,21 +8687,21 @@
         <v>2000</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C10" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E10" s="64" t="n">
         <v>271</v>
@@ -8449,21 +8725,21 @@
         <v>271</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E11" s="64" t="n">
         <v>900</v>
@@ -8487,21 +8763,21 @@
         <v>900</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E12" s="64" t="n">
         <v>0</v>
@@ -8525,21 +8801,21 @@
         <v>500</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C13" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E13" s="64" t="n">
         <v>0</v>
@@ -8563,21 +8839,21 @@
         <v>1500</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C14" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E14" s="64" t="n">
         <v>0</v>
@@ -8601,21 +8877,21 @@
         <v>300</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C15" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E15" s="64" t="n">
         <v>25</v>
@@ -8639,21 +8915,21 @@
         <v>26.015</v>
       </c>
       <c r="K15" s="22" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E16" s="64" t="n">
         <v>0</v>
@@ -8677,21 +8953,21 @@
         <v>700</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E17" s="64" t="n">
         <v>0</v>
@@ -8718,16 +8994,16 @@
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C18" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E18" s="64" t="n">
         <v>10</v>
@@ -8751,21 +9027,21 @@
         <v>41.624</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C19" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E19" s="64" t="n">
         <v>0</v>
@@ -8789,21 +9065,21 @@
         <v>0</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C20" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E20" s="64" t="n">
         <v>0</v>
@@ -8827,21 +9103,21 @@
         <v>0</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C21" s="62" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="62" t="s">
-        <v>406</v>
-      </c>
       <c r="D21" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E21" s="64" t="n">
         <v>0</v>
@@ -8865,12 +9141,12 @@
         <v>1500</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="H23" s="65" t="n">
         <f aca="false">SUMIFS(H5:H21,$C$5:$C$21,"Y")</f>
@@ -8887,7 +9163,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="H24" s="65" t="n">
         <f aca="false">SUM(H5:H21)</f>
@@ -8930,67 +9206,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E5" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F5" s="64" t="n">
         <v>7</v>
@@ -9014,24 +9290,24 @@
         <v>88.451</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C6" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E6" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F6" s="64" t="n">
         <v>0.25</v>
@@ -9055,24 +9331,24 @@
         <v>5.203</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E7" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F7" s="64" t="n">
         <v>7</v>
@@ -9096,24 +9372,24 @@
         <v>26.015</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C8" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E8" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F8" s="64" t="n">
         <v>0</v>
@@ -9137,24 +9413,24 @@
         <v>19.7714</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C9" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F9" s="64" t="n">
         <v>20</v>
@@ -9178,24 +9454,24 @@
         <v>20.812</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C10" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E10" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F10" s="64" t="n">
         <v>25</v>
@@ -9219,24 +9495,24 @@
         <v>78.045</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C11" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F11" s="64" t="n">
         <v>0</v>
@@ -9260,24 +9536,24 @@
         <v>20.812</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C12" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E12" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F12" s="64" t="n">
         <v>0</v>
@@ -9301,65 +9577,65 @@
         <v>27.0556</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="C13" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E13" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F13" s="64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" s="64" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I13" s="37" t="n">
         <f aca="false">F13*IF($D13="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)/IF($E13="year",12,1)</f>
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="J13" s="37" t="n">
         <f aca="false">G13*IF($D13="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)/IF($E13="year",12,1)</f>
-        <v>5.203</v>
+        <v>0</v>
       </c>
       <c r="K13" s="37" t="n">
         <f aca="false">H13*IF($D13="USD",Assumptions!$B$6*(1+Assumptions!$B$8),1)/IF($E13="year",12,1)</f>
-        <v>10.406</v>
+        <v>0</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E14" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F14" s="64" t="n">
         <v>3.5</v>
@@ -9383,24 +9659,24 @@
         <v>14.5684</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C15" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="F15" s="64" t="n">
         <v>15</v>
@@ -9424,24 +9700,24 @@
         <v>1.30075</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C16" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E16" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F16" s="64" t="n">
         <v>0</v>
@@ -9465,24 +9741,24 @@
         <v>7</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="C17" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="F17" s="64" t="n">
         <v>99</v>
@@ -9506,24 +9782,24 @@
         <v>8.58495</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C18" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E18" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F18" s="64" t="n">
         <v>50</v>
@@ -9547,24 +9823,24 @@
         <v>200</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C19" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F19" s="64" t="n">
         <v>5</v>
@@ -9588,24 +9864,24 @@
         <v>15</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C20" s="62" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F20" s="64" t="n">
         <v>0</v>
@@ -9629,24 +9905,24 @@
         <v>40</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C21" s="62" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="E21" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F21" s="66" t="n">
         <v>100</v>
@@ -9670,24 +9946,24 @@
         <v>208.12</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C22" s="62" t="s">
         <v>432</v>
       </c>
-      <c r="C22" s="62" t="s">
-        <v>406</v>
-      </c>
       <c r="D22" s="63" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="E22" s="63" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="F22" s="64" t="n">
         <v>0</v>
@@ -9711,63 +9987,63 @@
         <v>1000</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="I24" s="65" t="n">
         <f aca="false">SUMIFS(I5:I22,$C$5:$C$22,"Y")</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
       <c r="J24" s="65" t="n">
         <f aca="false">SUMIFS(J5:J22,$C$5:$C$22,"Y")</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
       <c r="K24" s="65" t="n">
         <f aca="false">SUMIFS(K5:K22,$C$5:$C$22,"Y")</f>
-        <v>736.5767</v>
+        <v>726.1707</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="I25" s="65" t="n">
         <f aca="false">I24*12</f>
-        <v>2792.1894</v>
+        <v>2767.215</v>
       </c>
       <c r="J25" s="65" t="n">
         <f aca="false">J24*12</f>
-        <v>4263.8574</v>
+        <v>4201.4214</v>
       </c>
       <c r="K25" s="65" t="n">
         <f aca="false">K24*12</f>
-        <v>8838.9204</v>
+        <v>8714.0484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="I26" s="65" t="n">
         <f aca="false">SUM(I5:I22)</f>
-        <v>236.32455</v>
+        <v>234.24335</v>
       </c>
       <c r="J26" s="65" t="n">
         <f aca="false">SUM(J5:J22)</f>
-        <v>587.60565</v>
+        <v>582.40265</v>
       </c>
       <c r="K26" s="65" t="n">
         <f aca="false">SUM(K5:K22)</f>
-        <v>1791.1451</v>
+        <v>1780.7391</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -9796,83 +10072,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>182</v>
-      </c>
       <c r="C4" s="20" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="M4" s="20" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="N4" s="20" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="R4" s="20" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">Assumptions!$B$10*Pricing!$D$39</f>
-        <v>4.4411</v>
+        <f aca="false">Assumptions!$B$10*Pricing!$D$39*(1-Assumptions!$B$53*Assumptions!$B$52)</f>
+        <v>4.27455875</v>
       </c>
       <c r="D5" s="63" t="n">
         <v>1</v>
@@ -9883,35 +10159,35 @@
       </c>
       <c r="F5" s="37" t="n">
         <f aca="false">C5/D5</f>
-        <v>4.4411</v>
+        <v>4.27455875</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">F5-H5</f>
-        <v>0.770769421487603</v>
+        <v>0.741865568181818</v>
       </c>
       <c r="H5" s="37" t="n">
         <f aca="false">F5/(1+Assumptions!$B$7)</f>
-        <v>3.6703305785124</v>
+        <v>3.53269318181818</v>
       </c>
       <c r="I5" s="37" t="n">
         <f aca="false">H5*Assumptions!$B$21</f>
-        <v>0.55054958677686</v>
+        <v>0.529903977272727</v>
       </c>
       <c r="J5" s="37" t="n">
         <f aca="false">F5*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E5</f>
-        <v>0.3477042</v>
+        <v>0.3440402925</v>
       </c>
       <c r="K5" s="37" t="n">
         <f aca="false">Assumptions!$B$19*I5+(1-Assumptions!$B$19)*J5</f>
-        <v>0.469411432066116</v>
+        <v>0.455558503363636</v>
       </c>
       <c r="L5" s="37" t="n">
         <f aca="false">H5-K5</f>
-        <v>3.20091914644628</v>
+        <v>3.07713467845455</v>
       </c>
       <c r="M5" s="37" t="n">
         <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.280962</v>
+        <v>0.15609</v>
       </c>
       <c r="N5" s="37" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -9919,27 +10195,27 @@
       </c>
       <c r="O5" s="37" t="n">
         <f aca="false">L5-M5-N5</f>
-        <v>2.89995714644628</v>
+        <v>2.90104467845455</v>
       </c>
       <c r="P5" s="18" t="n">
         <f aca="false">IF(F5=0,0,O5/F5)</f>
-        <v>0.652981726699755</v>
+        <v>0.678676992907056</v>
       </c>
       <c r="Q5" s="37" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>2.49744</v>
+        <v>2.400149103</v>
       </c>
       <c r="R5" s="37" t="n">
         <f aca="false">L5-Q5-N5</f>
-        <v>0.683479146446281</v>
+        <v>0.656985575454545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">Assumptions!$B$11*Pricing!$D$39*(1-Assumptions!$B$53*Assumptions!$B$52)</f>
@@ -9982,7 +10258,7 @@
       </c>
       <c r="M6" s="37" t="n">
         <f aca="false">Assumptions!$B$31*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.280962</v>
+        <v>0.15609</v>
       </c>
       <c r="N6" s="37" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -9990,35 +10266,35 @@
       </c>
       <c r="O6" s="37" t="n">
         <f aca="false">L6-M6-N6-$C$35</f>
-        <v>2.33431409290152</v>
+        <v>2.46282819290152</v>
       </c>
       <c r="P6" s="18" t="n">
         <f aca="false">IF(F6=0,0,O6/F6)</f>
-        <v>0.654133899648879</v>
+        <v>0.690146803674307</v>
       </c>
       <c r="Q6" s="37" t="n">
         <f aca="false">Assumptions!$B$32*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>2.49744</v>
+        <v>2.400149103</v>
       </c>
       <c r="R6" s="37" t="n">
         <f aca="false">L6-Q6-N6-$C$35</f>
-        <v>0.117836092901515</v>
+        <v>0.218769089901515</v>
       </c>
       <c r="S6" s="18" t="n">
         <f aca="false">1-C6/(12*C5)</f>
-        <v>0.196470023380094</v>
+        <v>0.165163660654643</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">Assumptions!$B$12*Pricing!$E$39</f>
-        <v>7.1111</v>
+        <f aca="false">Assumptions!$B$12*Pricing!$E$39*(1-Assumptions!$B$53*Assumptions!$B$52)</f>
+        <v>6.84443375</v>
       </c>
       <c r="D7" s="63" t="n">
         <v>1</v>
@@ -10029,35 +10305,35 @@
       </c>
       <c r="F7" s="37" t="n">
         <f aca="false">C7/D7</f>
-        <v>7.1111</v>
+        <v>6.84443375</v>
       </c>
       <c r="G7" s="37" t="n">
         <f aca="false">F7-H7</f>
-        <v>1.23415785123967</v>
+        <v>1.18787693181818</v>
       </c>
       <c r="H7" s="37" t="n">
         <f aca="false">F7/(1+Assumptions!$B$7)</f>
-        <v>5.87694214876033</v>
+        <v>5.65655681818182</v>
       </c>
       <c r="I7" s="37" t="n">
         <f aca="false">H7*Assumptions!$B$21</f>
-        <v>0.88154132231405</v>
+        <v>0.848483522727273</v>
       </c>
       <c r="J7" s="37" t="n">
         <f aca="false">F7*(Assumptions!$B$22+Assumptions!$B$24)+Assumptions!$B$23*E7</f>
-        <v>0.4064442</v>
+        <v>0.4005775425</v>
       </c>
       <c r="K7" s="37" t="n">
         <f aca="false">Assumptions!$B$19*I7+(1-Assumptions!$B$19)*J7</f>
-        <v>0.69150247338843</v>
+        <v>0.669321130636363</v>
       </c>
       <c r="L7" s="37" t="n">
         <f aca="false">H7-K7</f>
-        <v>5.1854396753719</v>
+        <v>4.98723568754545</v>
       </c>
       <c r="M7" s="37" t="n">
         <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.457864</v>
+        <v>0.26015</v>
       </c>
       <c r="N7" s="37" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -10065,11 +10341,11 @@
       </c>
       <c r="O7" s="37" t="n">
         <f aca="false">L7-M7-N7</f>
-        <v>4.7075756753719</v>
+        <v>4.70708568754545</v>
       </c>
       <c r="P7" s="18" t="n">
         <f aca="false">IF(F7=0,0,O7/F7)</f>
-        <v>0.662003863730211</v>
+        <v>0.687724632815016</v>
       </c>
       <c r="Q7" s="37" t="n">
         <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -10077,15 +10353,15 @@
       </c>
       <c r="R7" s="37" t="n">
         <f aca="false">L7-Q7-N7</f>
-        <v>2.0436396753719</v>
+        <v>1.84543568754545</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">Assumptions!$B$13*Pricing!$E$39*(1-Assumptions!$B$53*Assumptions!$B$52)</f>
@@ -10128,7 +10404,7 @@
       </c>
       <c r="M8" s="37" t="n">
         <f aca="false">Assumptions!$B$33*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.457864</v>
+        <v>0.26015</v>
       </c>
       <c r="N8" s="37" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -10136,11 +10412,11 @@
       </c>
       <c r="O8" s="37" t="n">
         <f aca="false">L8-M8-N8-$C$36</f>
-        <v>3.21341967850758</v>
+        <v>3.41690033684091</v>
       </c>
       <c r="P8" s="18" t="n">
         <f aca="false">IF(F8=0,0,O8/F8)</f>
-        <v>0.643164339265175</v>
+        <v>0.683890891120668</v>
       </c>
       <c r="Q8" s="37" t="n">
         <f aca="false">Assumptions!$B$34*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -10148,48 +10424,48 @@
       </c>
       <c r="R8" s="37" t="n">
         <f aca="false">L8-Q8-N8-$C$36</f>
-        <v>0.549483678507575</v>
+        <v>0.555250336840909</v>
       </c>
       <c r="S8" s="18" t="n">
         <f aca="false">1-C8/(12*C7)</f>
-        <v>0.29739909261577</v>
+        <v>0.270025031289112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="F11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*F5+Assumptions!$B$17*F6</f>
-        <v>3.83031988541667</v>
+        <v>3.78035751041667</v>
       </c>
       <c r="G11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*G5+Assumptions!$B$17*G6</f>
-        <v>0.664766261105372</v>
+        <v>0.656095105113636</v>
       </c>
       <c r="H11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*H5+Assumptions!$B$17*H6</f>
-        <v>3.1655536243113</v>
+        <v>3.12426240530303</v>
       </c>
       <c r="K11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*K5+Assumptions!$B$17*K6</f>
-        <v>0.354439974513017</v>
+        <v>0.350284095902273</v>
       </c>
       <c r="L11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*L5+Assumptions!$B$17*L6</f>
-        <v>2.81111364979828</v>
+        <v>2.77397830940076</v>
       </c>
       <c r="M11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*M5+Assumptions!$B$17*M6</f>
-        <v>0.280962</v>
+        <v>0.15609</v>
       </c>
       <c r="N11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*N5+Assumptions!$B$17*N6</f>
@@ -10197,51 +10473,51 @@
       </c>
       <c r="O11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*O5+Assumptions!$B$17*O6</f>
-        <v>2.50400700896495</v>
+        <v>2.59429313856742</v>
       </c>
       <c r="P11" s="42" t="n">
         <f aca="false">IF(F11=0,0,O11/F11)</f>
-        <v>0.653733130357742</v>
+        <v>0.686256030393666</v>
       </c>
       <c r="Q11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*Q5+Assumptions!$B$17*Q6</f>
-        <v>2.49744</v>
+        <v>2.400149103</v>
       </c>
       <c r="R11" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$17)*R5+Assumptions!$B$17*R6</f>
-        <v>0.287529008964945</v>
+        <v>0.350234035567424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="F12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*F7+Assumptions!$B$18*F8</f>
-        <v>6.159424390625</v>
+        <v>6.012757953125</v>
       </c>
       <c r="G12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*G7+Assumptions!$B$18*G8</f>
-        <v>1.06899100994318</v>
+        <v>1.04353650426136</v>
       </c>
       <c r="H12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*H7+Assumptions!$B$18*H8</f>
-        <v>5.09043338068182</v>
+        <v>4.96922144886364</v>
       </c>
       <c r="K12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*K7+Assumptions!$B$18*K8</f>
-        <v>0.571091938898864</v>
+        <v>0.558892200385227</v>
       </c>
       <c r="L12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*L7+Assumptions!$B$18*L8</f>
-        <v>4.51934144178295</v>
+        <v>4.41032924847841</v>
       </c>
       <c r="M12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*M7+Assumptions!$B$18*M8</f>
-        <v>0.457864</v>
+        <v>0.26015</v>
       </c>
       <c r="N12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*N7+Assumptions!$B$18*N8</f>
@@ -10249,11 +10525,11 @@
       </c>
       <c r="O12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*O7+Assumptions!$B$18*O8</f>
-        <v>4.03520547678296</v>
+        <v>4.12650227972841</v>
       </c>
       <c r="P12" s="42" t="n">
         <f aca="false">IF(F12=0,0,O12/F12)</f>
-        <v>0.655127041241836</v>
+        <v>0.686291101670532</v>
       </c>
       <c r="Q12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*Q7+Assumptions!$B$18*Q8</f>
@@ -10261,39 +10537,39 @@
       </c>
       <c r="R12" s="45" t="n">
         <f aca="false">(1-Assumptions!$B$18)*R7+Assumptions!$B$18*R8</f>
-        <v>1.37126947678295</v>
+        <v>1.26485227972841</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="F13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*F11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*F12)</f>
-        <v>4.25379343181818</v>
+        <v>4.1862485</v>
       </c>
       <c r="G13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*G11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*G12)</f>
-        <v>0.738261669984974</v>
+        <v>0.726538995867769</v>
       </c>
       <c r="H13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*H11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*H12)</f>
-        <v>3.51553176183321</v>
+        <v>3.45970950413223</v>
       </c>
       <c r="K13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*K11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*K12)</f>
-        <v>0.393831240764989</v>
+        <v>0.388212842171901</v>
       </c>
       <c r="L13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*L11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*L12)</f>
-        <v>3.12170052106822</v>
+        <v>3.07149666196033</v>
       </c>
       <c r="M13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*M11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*M12)</f>
-        <v>0.313126</v>
+        <v>0.17501</v>
       </c>
       <c r="N13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*N11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*N12)</f>
@@ -10301,24 +10577,24 @@
       </c>
       <c r="O13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*O11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*O12)</f>
-        <v>2.7824067303864</v>
+        <v>2.87287661877851</v>
       </c>
       <c r="P13" s="42" t="n">
         <f aca="false">IF(F13=0,0,O13/F13)</f>
-        <v>0.654100104996666</v>
+        <v>0.686265189173197</v>
       </c>
       <c r="Q13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*Q11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*Q12)</f>
-        <v>2.61096</v>
+        <v>2.531358357</v>
       </c>
       <c r="R13" s="45" t="n">
         <f aca="false">IF((Assumptions!$B$15+Assumptions!$B$16)=0,0,Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16)*R11+(1-Assumptions!$B$15/(Assumptions!$B$15+Assumptions!$B$16))*R12)</f>
-        <v>0.484572730386401</v>
+        <v>0.516528261778512</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -10329,28 +10605,28 @@
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="C17" s="37" t="n">
         <f aca="false">C6</f>
@@ -10375,7 +10651,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="C18" s="37" t="n">
         <f aca="false">C6</f>
@@ -10400,7 +10676,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="C19" s="37" t="n">
         <f aca="false">C6</f>
@@ -10425,7 +10701,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -10436,117 +10712,117 @@
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="G22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">'Fixed costs'!$I$24</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
       <c r="D23" s="19" t="n">
         <f aca="false">IF(ISNUMBER(E23),ROUNDUP(E23*(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF(F23&lt;=0,"never",ROUNDUP(C23/F23,0))</f>
-        <v>1470</v>
+        <v>1333</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">(Assumptions!$B$15*$O$11+Assumptions!$B$16*$O$12)+(1-Assumptions!$B$15-Assumptions!$B$16)*(Assumptions!$B$54*Assumptions!$B$56*'Credit shop'!$G$22-$C$29)+Assumptions!$B$15*Assumptions!$B$55*Assumptions!$B$56*'Credit shop'!$G$22</f>
-        <v>0.158310312909103</v>
+        <v>0.173119826770669</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">'Fixed costs'!$J$24</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">IF(ISNUMBER(E24),ROUNDUP(E24*(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF(F24&lt;=0,"never",ROUNDUP(C24/F24,0))</f>
-        <v>2245</v>
+        <v>2023</v>
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">(Assumptions!$B$15*$O$11+Assumptions!$B$16*$O$12)+(1-Assumptions!$B$15-Assumptions!$B$16)*(Assumptions!$B$54*Assumptions!$B$56*'Credit shop'!$G$22-$C$29)+Assumptions!$B$15*Assumptions!$B$55*Assumptions!$B$56*'Credit shop'!$G$22</f>
-        <v>0.158310312909103</v>
+        <v>0.173119826770669</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">'Fixed costs'!$K$24</f>
-        <v>736.5767</v>
+        <v>726.1707</v>
       </c>
       <c r="D25" s="19" t="n">
         <f aca="false">IF(ISNUMBER(E25),ROUNDUP(E25*(Assumptions!$B$15+Assumptions!$B$16),0),"never")</f>
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF(F25&lt;=0,"never",ROUNDUP(C25/F25,0))</f>
-        <v>4653</v>
+        <v>4195</v>
       </c>
       <c r="F25" s="37" t="n">
         <f aca="false">(Assumptions!$B$15*$O$11+Assumptions!$B$16*$O$12)+(1-Assumptions!$B$15-Assumptions!$B$16)*(Assumptions!$B$54*Assumptions!$B$56*'Credit shop'!$G$22-$C$29)+Assumptions!$B$15*Assumptions!$B$55*Assumptions!$B$56*'Credit shop'!$G$22</f>
-        <v>0.158310312909103</v>
+        <v>0.173119826770669</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C29" s="43" t="n">
         <f aca="false">Assumptions!$B$35+C30</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="C30" s="37" t="n">
         <f aca="false">Assumptions!$B$49*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
-        <v>0.020812</v>
+        <v>0.010406</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="C33" s="31" t="n">
         <v>7</v>
@@ -10554,33 +10830,33 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="C34" s="37" t="n">
         <f aca="false">C33/30*(M6+N6)</f>
-        <v>0.0702244666666667</v>
+        <v>0.0410876666666667</v>
       </c>
       <c r="D34" s="37" t="n">
         <f aca="false">C33/30*(M8+N8)</f>
-        <v>0.1115016</v>
+        <v>0.0653683333333333</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="C35" s="37" t="n">
         <f aca="false">IF(Assumptions!$B$51=0,0,(1/Assumptions!$B$51-1)*C34/12)</f>
-        <v>0.00877805833333333</v>
+        <v>0.00513595833333333</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="C36" s="37" t="n">
         <f aca="false">IF(Assumptions!$B$51=0,0,(1/Assumptions!$B$51-1)*D34/12)</f>
-        <v>0.0139377</v>
+        <v>0.00817104166666667</v>
       </c>
     </row>
   </sheetData>
@@ -10608,46 +10884,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>100</v>
@@ -10676,7 +10952,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="B6" s="68" t="n">
         <f aca="false">IF(B5&gt;=Assumptions!$B$39,3,IF(B5&gt;=Assumptions!$B$38,2,1))</f>
@@ -10713,7 +10989,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">B5-B8-B9</f>
@@ -10750,7 +11026,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$15,0)</f>
@@ -10787,7 +11063,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">ROUND(B5*Assumptions!$B$16,0)</f>
@@ -10824,7 +11100,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="B10" s="69" t="n">
         <f aca="false">B8+B9</f>
@@ -10861,7 +11137,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">ROUND(B7*Assumptions!$B$54+B8*Assumptions!$B$55,0)</f>
@@ -10898,7 +11174,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -10911,101 +11187,101 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="B13" s="37" t="n">
         <f aca="false">B8*'Unit economics'!$F$11+B9*'Unit economics'!$F$12</f>
-        <v>25.3110238177083</v>
+        <v>24.9145455052083</v>
       </c>
       <c r="C13" s="37" t="n">
         <f aca="false">C8*'Unit economics'!$F$11+C9*'Unit economics'!$F$12</f>
-        <v>118.894479317708</v>
+        <v>117.012012505208</v>
       </c>
       <c r="D13" s="37" t="n">
         <f aca="false">D8*'Unit economics'!$F$11+D9*'Unit economics'!$F$12</f>
-        <v>233.95863875</v>
+        <v>230.2436675</v>
       </c>
       <c r="E13" s="37" t="n">
         <f aca="false">E8*'Unit economics'!$F$11+E9*'Unit economics'!$F$12</f>
-        <v>586.811756817708</v>
+        <v>577.499347505208</v>
       </c>
       <c r="F13" s="37" t="n">
         <f aca="false">F8*'Unit economics'!$F$11+F9*'Unit economics'!$F$12</f>
-        <v>1169.79319375</v>
+        <v>1151.2183375</v>
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G8*'Unit economics'!$F$11+G9*'Unit economics'!$F$12</f>
-        <v>2339.5863875</v>
+        <v>2302.436675</v>
       </c>
       <c r="H13" s="37" t="n">
         <f aca="false">H8*'Unit economics'!$F$11+H9*'Unit economics'!$F$12</f>
-        <v>5848.96596875</v>
+        <v>5756.0916875</v>
       </c>
       <c r="I13" s="37" t="n">
         <f aca="false">I8*'Unit economics'!$F$11+I9*'Unit economics'!$F$12</f>
-        <v>11697.9319375</v>
+        <v>11512.183375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="B14" s="37" t="n">
         <f aca="false">-(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>-4.39282231547004</v>
+        <v>-4.32401202982955</v>
       </c>
       <c r="C14" s="37" t="n">
         <f aca="false">-(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>-20.6345790551395</v>
+        <v>-20.3078699389205</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">-(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>-40.6043918491736</v>
+        <v>-39.9596447727273</v>
       </c>
       <c r="E14" s="37" t="n">
         <f aca="false">-(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>-101.843362753487</v>
+        <v>-100.227159484375</v>
       </c>
       <c r="F14" s="37" t="n">
         <f aca="false">-(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>-203.021959245868</v>
+        <v>-199.798223863636</v>
       </c>
       <c r="G14" s="37" t="n">
         <f aca="false">-(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
-        <v>-406.043918491736</v>
+        <v>-399.596447727273</v>
       </c>
       <c r="H14" s="37" t="n">
         <f aca="false">-(H8*'Unit economics'!$G$11+H9*'Unit economics'!$G$12)</f>
-        <v>-1015.10979622934</v>
+        <v>-998.991119318182</v>
       </c>
       <c r="I14" s="37" t="n">
         <f aca="false">-(I8*'Unit economics'!$G$11+I9*'Unit economics'!$G$12)</f>
-        <v>-2030.21959245868</v>
+        <v>-1997.98223863636</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="B15" s="37" t="n">
         <f aca="false">B23*(1-Assumptions!$B$19)*(B8*'Unit economics'!$G$11+B9*'Unit economics'!$G$12)</f>
-        <v>1.75712892618802</v>
+        <v>1.72960481193182</v>
       </c>
       <c r="C15" s="37" t="n">
         <f aca="false">C23*(1-Assumptions!$B$19)*(C8*'Unit economics'!$G$11+C9*'Unit economics'!$G$12)</f>
-        <v>8.25383162205579</v>
+        <v>8.12314797556818</v>
       </c>
       <c r="D15" s="37" t="n">
         <f aca="false">D23*(1-Assumptions!$B$19)*(D8*'Unit economics'!$G$11+D9*'Unit economics'!$G$12)</f>
-        <v>16.2417567396694</v>
+        <v>15.9838579090909</v>
       </c>
       <c r="E15" s="37" t="n">
         <f aca="false">E23*(1-Assumptions!$B$19)*(E8*'Unit economics'!$G$11+E9*'Unit economics'!$G$12)</f>
-        <v>40.7373451013946</v>
+        <v>40.09086379375</v>
       </c>
       <c r="F15" s="37" t="n">
         <f aca="false">F23*(1-Assumptions!$B$19)*(F8*'Unit economics'!$G$11+F9*'Unit economics'!$G$12)</f>
-        <v>81.2087836983471</v>
+        <v>79.9192895454546</v>
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">G23*(1-Assumptions!$B$19)*(G8*'Unit economics'!$G$11+G9*'Unit economics'!$G$12)</f>
@@ -11022,44 +11298,44 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="B16" s="37" t="n">
         <f aca="false">-(B8*'Unit economics'!$K$11+B9*'Unit economics'!$K$12)</f>
-        <v>-2.34329181146395</v>
+        <v>-2.31031267989659</v>
       </c>
       <c r="C16" s="37" t="n">
         <f aca="false">-(C8*'Unit economics'!$K$11+C9*'Unit economics'!$K$12)</f>
-        <v>-11.0075791082937</v>
+        <v>-10.8509952076784</v>
       </c>
       <c r="D16" s="37" t="n">
         <f aca="false">-(D8*'Unit economics'!$K$11+D9*'Unit economics'!$K$12)</f>
-        <v>-21.6607182420744</v>
+        <v>-21.3517063194545</v>
       </c>
       <c r="E16" s="37" t="n">
         <f aca="false">-(E8*'Unit economics'!$K$11+E9*'Unit economics'!$K$12)</f>
-        <v>-54.3290155924425</v>
+        <v>-53.5544078465875</v>
       </c>
       <c r="F16" s="37" t="n">
         <f aca="false">-(F8*'Unit economics'!$K$11+F9*'Unit economics'!$K$12)</f>
-        <v>-108.303591210372</v>
+        <v>-106.758531597273</v>
       </c>
       <c r="G16" s="37" t="n">
         <f aca="false">-(G8*'Unit economics'!$K$11+G9*'Unit economics'!$K$12)</f>
-        <v>-216.607182420744</v>
+        <v>-213.517063194545</v>
       </c>
       <c r="H16" s="37" t="n">
         <f aca="false">-(H8*'Unit economics'!$K$11+H9*'Unit economics'!$K$12)</f>
-        <v>-541.51795605186</v>
+        <v>-533.792657986364</v>
       </c>
       <c r="I16" s="37" t="n">
         <f aca="false">-(I8*'Unit economics'!$K$11+I9*'Unit economics'!$K$12)</f>
-        <v>-1083.03591210372</v>
+        <v>-1067.58531597273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="B17" s="37" t="n">
         <f aca="false">B11*Assumptions!$B$56*'Credit shop'!$G$22</f>
@@ -11096,39 +11372,39 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="B18" s="43" t="n">
         <f aca="false">SUM(B13:B17)</f>
-        <v>23.2718063723343</v>
+        <v>22.9495933627859</v>
       </c>
       <c r="C18" s="43" t="n">
         <f aca="false">SUM(C13:C17)</f>
-        <v>113.144759308562</v>
+        <v>111.614901866409</v>
       </c>
       <c r="D18" s="43" t="n">
         <f aca="false">SUM(D13:D17)</f>
-        <v>223.212498462884</v>
+        <v>220.193387381372</v>
       </c>
       <c r="E18" s="43" t="n">
         <f aca="false">SUM(E13:E17)</f>
-        <v>556.629988478959</v>
+        <v>549.061908873781</v>
       </c>
       <c r="F18" s="43" t="n">
         <f aca="false">SUM(F13:F17)</f>
-        <v>1113.12272455905</v>
+        <v>1098.02716915149</v>
       </c>
       <c r="G18" s="43" t="n">
         <f aca="false">SUM(G13:G17)</f>
-        <v>2060.88811396603</v>
+        <v>2033.27599145669</v>
       </c>
       <c r="H18" s="43" t="n">
         <f aca="false">SUM(H13:H17)</f>
-        <v>5153.69016879277</v>
+        <v>5084.65986251942</v>
       </c>
       <c r="I18" s="43" t="n">
         <f aca="false">SUM(I13:I17)</f>
-        <v>10304.4405698302</v>
+        <v>10166.3799572835</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11144,7 +11420,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -11157,81 +11433,81 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="B21" s="37" t="n">
         <f aca="false">(B13+B14+B11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>291.362219679752</v>
+        <v>287.430203357438</v>
       </c>
       <c r="C21" s="37" t="n">
         <f aca="false">(C13+C14+C11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>1421.18161306818</v>
+        <v>1402.51252071281</v>
       </c>
       <c r="D21" s="37" t="n">
         <f aca="false">(D13+D14+D11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>2804.37658264463</v>
+        <v>2767.53389256198</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">(E13+E14+E11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>6989.59097670455</v>
+        <v>6897.23650418389</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">(F13+F14+F11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>13981.5391115703</v>
+        <v>13797.325661157</v>
       </c>
       <c r="G21" s="37" t="n">
         <f aca="false">(G13+G14+G11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>27922.7344214876</v>
+        <v>27554.3075206612</v>
       </c>
       <c r="H21" s="37" t="n">
         <f aca="false">(H13+H14+H11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>69827.0079545455</v>
+        <v>68905.9407024793</v>
       </c>
       <c r="I21" s="37" t="n">
         <f aca="false">(I13+I14+I11*Assumptions!$B$56*'Credit shop'!$C$21/(1+Assumptions!$B$7))*12</f>
-        <v>139613.672107438</v>
+        <v>137771.537603306</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="B22" s="37" t="n">
         <f aca="false">(B13*(1-Assumptions!$B$19)+B11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>101.09961146</v>
+        <v>99.57713474</v>
       </c>
       <c r="C22" s="37" t="n">
         <f aca="false">(C13*(1-Assumptions!$B$19)+C11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>479.98648058</v>
+        <v>472.75780802</v>
       </c>
       <c r="D22" s="37" t="n">
         <f aca="false">(D13*(1-Assumptions!$B$19)+D11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>945.2645328</v>
+        <v>930.9990432</v>
       </c>
       <c r="E22" s="37" t="n">
         <f aca="false">(E13*(1-Assumptions!$B$19)+E11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>2366.61026618</v>
+        <v>2330.85061442</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">(F13*(1-Assumptions!$B$19)+F11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>4722.417384</v>
+        <v>4651.089936</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">(G13*(1-Assumptions!$B$19)+G11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>9440.929488</v>
+        <v>9298.274592</v>
       </c>
       <c r="H22" s="37" t="n">
         <f aca="false">(H13*(1-Assumptions!$B$19)+H11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>23604.27636</v>
+        <v>23247.63912</v>
       </c>
       <c r="I22" s="37" t="n">
         <f aca="false">(I13*(1-Assumptions!$B$19)+I11*Assumptions!$B$56*'Credit shop'!$C$21*(1-Assumptions!$B$58))*Assumptions!$B$29*12</f>
-        <v>47204.64744</v>
+        <v>46491.37296</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IF(AND(Assumptions!$B$26="Y",B21&lt;=Assumptions!$B$27,B22&lt;=Assumptions!$B$28),1,0)</f>
@@ -11279,7 +11555,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -11292,44 +11568,44 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="B26" s="37" t="n">
         <f aca="false">B8*'Unit economics'!$M$11+B9*'Unit economics'!$M$12+B7*'Unit economics'!$C$30</f>
-        <v>3.819002</v>
+        <v>2.018764</v>
       </c>
       <c r="C26" s="37" t="n">
         <f aca="false">C8*'Unit economics'!$M$11+C9*'Unit economics'!$M$12+C7*'Unit economics'!$C$30</f>
-        <v>18.57471</v>
+        <v>9.802452</v>
       </c>
       <c r="D26" s="37" t="n">
         <f aca="false">D8*'Unit economics'!$M$11+D9*'Unit economics'!$M$12+D7*'Unit economics'!$C$30</f>
-        <v>36.88927</v>
+        <v>19.45922</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">E8*'Unit economics'!$M$11+E9*'Unit economics'!$M$12+E7*'Unit economics'!$C$30</f>
-        <v>92.35325</v>
+        <v>48.720892</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">F8*'Unit economics'!$M$11+F9*'Unit economics'!$M$12+F7*'Unit economics'!$C$30</f>
-        <v>184.44635</v>
+        <v>97.2961</v>
       </c>
       <c r="G26" s="37" t="n">
         <f aca="false">G8*'Unit economics'!$M$11+G9*'Unit economics'!$M$12+G7*'Unit economics'!$C$30</f>
-        <v>368.8927</v>
+        <v>194.5922</v>
       </c>
       <c r="H26" s="37" t="n">
         <f aca="false">H8*'Unit economics'!$M$11+H9*'Unit economics'!$M$12+H7*'Unit economics'!$C$30</f>
-        <v>922.23175</v>
+        <v>486.4805</v>
       </c>
       <c r="I26" s="37" t="n">
         <f aca="false">I8*'Unit economics'!$M$11+I9*'Unit economics'!$M$12+I7*'Unit economics'!$C$30</f>
-        <v>1844.4635</v>
+        <v>972.961</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="B27" s="37" t="n">
         <f aca="false">B7*Assumptions!$B$35+B10*Assumptions!$B$36</f>
@@ -11366,76 +11642,76 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="B28" s="37" t="n">
         <f aca="false">CHOOSE(B6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
       <c r="C28" s="37" t="n">
         <f aca="false">CHOOSE(C6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
       <c r="D28" s="37" t="n">
         <f aca="false">CHOOSE(D6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>232.68245</v>
+        <v>230.60125</v>
       </c>
       <c r="E28" s="37" t="n">
         <f aca="false">CHOOSE(E6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
       <c r="F28" s="37" t="n">
         <f aca="false">CHOOSE(F6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
       <c r="G28" s="37" t="n">
         <f aca="false">CHOOSE(G6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>355.32145</v>
+        <v>350.11845</v>
       </c>
       <c r="H28" s="37" t="n">
         <f aca="false">CHOOSE(H6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>736.5767</v>
+        <v>726.1707</v>
       </c>
       <c r="I28" s="37" t="n">
         <f aca="false">CHOOSE(I6,'Fixed costs'!$I$24,'Fixed costs'!$J$24,'Fixed costs'!$K$24)</f>
-        <v>736.5767</v>
+        <v>726.1707</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="B29" s="45" t="n">
         <f aca="false">B26+B27+B28</f>
-        <v>237.561452</v>
+        <v>233.680014</v>
       </c>
       <c r="C29" s="45" t="n">
         <f aca="false">C26+C27+C28</f>
-        <v>256.53716</v>
+        <v>245.683702</v>
       </c>
       <c r="D29" s="45" t="n">
         <f aca="false">D26+D27+D28</f>
-        <v>280.12172</v>
+        <v>260.61047</v>
       </c>
       <c r="E29" s="45" t="n">
         <f aca="false">E26+E27+E28</f>
-        <v>474.0547</v>
+        <v>425.219342</v>
       </c>
       <c r="F29" s="45" t="n">
         <f aca="false">F26+F27+F28</f>
-        <v>592.5178</v>
+        <v>500.16455</v>
       </c>
       <c r="G29" s="45" t="n">
         <f aca="false">G26+G27+G28</f>
-        <v>829.71415</v>
+        <v>650.21065</v>
       </c>
       <c r="H29" s="45" t="n">
         <f aca="false">H26+H27+H28</f>
-        <v>1922.55845</v>
+        <v>1476.4012</v>
       </c>
       <c r="I29" s="45" t="n">
         <f aca="false">I26+I27+I28</f>
-        <v>3108.5402</v>
+        <v>2226.6317</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11451,7 +11727,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -11464,44 +11740,44 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="B32" s="43" t="n">
         <f aca="false">B18-B29</f>
-        <v>-214.289645627666</v>
+        <v>-210.730420637214</v>
       </c>
       <c r="C32" s="43" t="n">
         <f aca="false">C18-C29</f>
-        <v>-143.392400691438</v>
+        <v>-134.068800133591</v>
       </c>
       <c r="D32" s="43" t="n">
         <f aca="false">D18-D29</f>
-        <v>-56.9092215371157</v>
+        <v>-40.4170826186281</v>
       </c>
       <c r="E32" s="43" t="n">
         <f aca="false">E18-E29</f>
-        <v>82.5752884789591</v>
+        <v>123.842566873781</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">F18-F29</f>
-        <v>520.60492455905</v>
+        <v>597.862619151488</v>
       </c>
       <c r="G32" s="43" t="n">
         <f aca="false">G18-G29</f>
-        <v>1231.17396396603</v>
+        <v>1383.06534145669</v>
       </c>
       <c r="H32" s="43" t="n">
         <f aca="false">H18-H29</f>
-        <v>3231.13171879277</v>
+        <v>3608.25866251942</v>
       </c>
       <c r="I32" s="43" t="n">
         <f aca="false">I18-I29</f>
-        <v>7195.90036983016</v>
+        <v>7939.74825728347</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="B33" s="37" t="n">
         <f aca="false">MAX(0,B32)*12</f>
@@ -11517,28 +11793,28 @@
       </c>
       <c r="E33" s="37" t="n">
         <f aca="false">MAX(0,E32)*12</f>
-        <v>990.903461747509</v>
+        <v>1486.11080248537</v>
       </c>
       <c r="F33" s="37" t="n">
         <f aca="false">MAX(0,F32)*12</f>
-        <v>6247.2590947086</v>
+        <v>7174.35142981785</v>
       </c>
       <c r="G33" s="37" t="n">
         <f aca="false">MAX(0,G32)*12</f>
-        <v>14774.0875675924</v>
+        <v>16596.7840974803</v>
       </c>
       <c r="H33" s="37" t="n">
         <f aca="false">MAX(0,H32)*12</f>
-        <v>38773.5806255132</v>
+        <v>43299.1039502331</v>
       </c>
       <c r="I33" s="37" t="n">
         <f aca="false">MAX(0,I32)*12</f>
-        <v>86350.804437962</v>
+        <v>95276.9790874017</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="B34" s="37" t="n">
         <f aca="false">IF(B33&lt;=Assumptions!$B$41,0,IF(B33&lt;Assumptions!$B$42,Assumptions!$B$43*(B33-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*B33)))/12</f>
@@ -11562,94 +11838,94 @@
       </c>
       <c r="G34" s="37" t="n">
         <f aca="false">IF(G33&lt;=Assumptions!$B$41,0,IF(G33&lt;Assumptions!$B$42,Assumptions!$B$43*(G33-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*G33)))/12</f>
-        <v>103.987062613037</v>
+        <v>135.124794998622</v>
       </c>
       <c r="H34" s="37" t="n">
         <f aca="false">IF(H33&lt;=Assumptions!$B$41,0,IF(H33&lt;Assumptions!$B$42,Assumptions!$B$43*(H33-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*H33)))/12</f>
-        <v>662.382002352517</v>
+        <v>739.693025816482</v>
       </c>
       <c r="I34" s="37" t="n">
         <f aca="false">IF(I33&lt;=Assumptions!$B$41,0,IF(I33&lt;Assumptions!$B$42,Assumptions!$B$43*(I33-Assumptions!$B$41),MAX(4*Assumptions!$B$44,Assumptions!$B$43*I33)))/12</f>
-        <v>1475.15957581518</v>
+        <v>1627.64839274311</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="B35" s="43" t="n">
         <f aca="false">B32-B34</f>
-        <v>-214.289645627666</v>
+        <v>-210.730420637214</v>
       </c>
       <c r="C35" s="43" t="n">
         <f aca="false">C32-C34</f>
-        <v>-143.392400691438</v>
+        <v>-134.068800133591</v>
       </c>
       <c r="D35" s="43" t="n">
         <f aca="false">D32-D34</f>
-        <v>-56.9092215371157</v>
+        <v>-40.4170826186281</v>
       </c>
       <c r="E35" s="43" t="n">
         <f aca="false">E32-E34</f>
-        <v>82.5752884789591</v>
+        <v>123.842566873781</v>
       </c>
       <c r="F35" s="43" t="n">
         <f aca="false">F32-F34</f>
-        <v>520.60492455905</v>
+        <v>597.862619151488</v>
       </c>
       <c r="G35" s="43" t="n">
         <f aca="false">G32-G34</f>
-        <v>1127.186901353</v>
+        <v>1247.94054645807</v>
       </c>
       <c r="H35" s="43" t="n">
         <f aca="false">H32-H34</f>
-        <v>2568.74971644025</v>
+        <v>2868.56563670294</v>
       </c>
       <c r="I35" s="43" t="n">
         <f aca="false">I32-I34</f>
-        <v>5720.74079401498</v>
+        <v>6312.09986454036</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="B36" s="37" t="n">
         <f aca="false">B35*12</f>
-        <v>-2571.47574753199</v>
+        <v>-2528.76504764657</v>
       </c>
       <c r="C36" s="37" t="n">
         <f aca="false">C35*12</f>
-        <v>-1720.70880829725</v>
+        <v>-1608.82560160309</v>
       </c>
       <c r="D36" s="37" t="n">
         <f aca="false">D35*12</f>
-        <v>-682.910658445389</v>
+        <v>-485.004991423538</v>
       </c>
       <c r="E36" s="37" t="n">
         <f aca="false">E35*12</f>
-        <v>990.903461747509</v>
+        <v>1486.11080248537</v>
       </c>
       <c r="F36" s="37" t="n">
         <f aca="false">F35*12</f>
-        <v>6247.2590947086</v>
+        <v>7174.35142981785</v>
       </c>
       <c r="G36" s="37" t="n">
         <f aca="false">G35*12</f>
-        <v>13526.242816236</v>
+        <v>14975.2865574969</v>
       </c>
       <c r="H36" s="37" t="n">
         <f aca="false">H35*12</f>
-        <v>30824.996597283</v>
+        <v>34422.7876404353</v>
       </c>
       <c r="I36" s="37" t="n">
         <f aca="false">I35*12</f>
-        <v>68648.8895281798</v>
+        <v>75745.1983744843</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="B37" s="6" t="str">
         <f aca="false">IF(B33&lt;Assumptions!$B$42,"yes","no: full-time rates")</f>
@@ -11697,7 +11973,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -11710,187 +11986,187 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="B40" s="37" t="n">
         <f aca="false">IF(B5=0,0,B29/B5)</f>
-        <v>2.37561452</v>
+        <v>2.33680014</v>
       </c>
       <c r="C40" s="37" t="n">
         <f aca="false">IF(C5=0,0,C29/C5)</f>
-        <v>0.51307432</v>
+        <v>0.491367404</v>
       </c>
       <c r="D40" s="37" t="n">
         <f aca="false">IF(D5=0,0,D29/D5)</f>
-        <v>0.28012172</v>
+        <v>0.26061047</v>
       </c>
       <c r="E40" s="37" t="n">
         <f aca="false">IF(E5=0,0,E29/E5)</f>
-        <v>0.18962188</v>
+        <v>0.1700877368</v>
       </c>
       <c r="F40" s="37" t="n">
         <f aca="false">IF(F5=0,0,F29/F5)</f>
-        <v>0.11850356</v>
+        <v>0.10003291</v>
       </c>
       <c r="G40" s="37" t="n">
         <f aca="false">IF(G5=0,0,G29/G5)</f>
-        <v>0.082971415</v>
+        <v>0.065021065</v>
       </c>
       <c r="H40" s="37" t="n">
         <f aca="false">IF(H5=0,0,H29/H5)</f>
-        <v>0.076902338</v>
+        <v>0.059056048</v>
       </c>
       <c r="I40" s="37" t="n">
         <f aca="false">IF(I5=0,0,I29/I5)</f>
-        <v>0.062170804</v>
+        <v>0.044532634</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="B41" s="37" t="n">
         <f aca="false">IF(B10=0,0,B29/B10)</f>
-        <v>39.5935753333333</v>
+        <v>38.946669</v>
       </c>
       <c r="C41" s="37" t="n">
         <f aca="false">IF(C10=0,0,C29/C10)</f>
-        <v>9.16204142857143</v>
+        <v>8.77441792857143</v>
       </c>
       <c r="D41" s="37" t="n">
         <f aca="false">IF(D10=0,0,D29/D10)</f>
-        <v>5.09312218181818</v>
+        <v>4.73837218181818</v>
       </c>
       <c r="E41" s="37" t="n">
         <f aca="false">IF(E10=0,0,E29/E10)</f>
-        <v>3.43517898550725</v>
+        <v>3.08129957971015</v>
       </c>
       <c r="F41" s="37" t="n">
         <f aca="false">IF(F10=0,0,F29/F10)</f>
-        <v>2.15461018181818</v>
+        <v>1.81878018181818</v>
       </c>
       <c r="G41" s="37" t="n">
         <f aca="false">IF(G10=0,0,G29/G10)</f>
-        <v>1.50857118181818</v>
+        <v>1.18220118181818</v>
       </c>
       <c r="H41" s="37" t="n">
         <f aca="false">IF(H10=0,0,H29/H10)</f>
-        <v>1.39822432727273</v>
+        <v>1.07374632727273</v>
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">IF(I10=0,0,I29/I10)</f>
-        <v>1.13037825454545</v>
+        <v>0.809684254545455</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
       <c r="B42" s="37" t="n">
         <f aca="false">IF(B10=0,0,B18/B10)</f>
-        <v>3.87863439538904</v>
+        <v>3.82493222713099</v>
       </c>
       <c r="C42" s="37" t="n">
         <f aca="false">IF(C10=0,0,C18/C10)</f>
-        <v>4.04088426102008</v>
+        <v>3.98624649522889</v>
       </c>
       <c r="D42" s="37" t="n">
         <f aca="false">IF(D10=0,0,D18/D10)</f>
-        <v>4.05840906296153</v>
+        <v>4.00351613420676</v>
       </c>
       <c r="E42" s="37" t="n">
         <f aca="false">IF(E10=0,0,E18/E10)</f>
-        <v>4.03355064115188</v>
+        <v>3.97870948459262</v>
       </c>
       <c r="F42" s="37" t="n">
         <f aca="false">IF(F10=0,0,F18/F10)</f>
-        <v>4.04771899839654</v>
+        <v>3.99282606964177</v>
       </c>
       <c r="G42" s="37" t="n">
         <f aca="false">IF(G10=0,0,G18/G10)</f>
-        <v>3.74706929812006</v>
+        <v>3.69686543901217</v>
       </c>
       <c r="H42" s="37" t="n">
         <f aca="false">IF(H10=0,0,H18/H10)</f>
-        <v>3.74813830457656</v>
+        <v>3.69793444546867</v>
       </c>
       <c r="I42" s="37" t="n">
         <f aca="false">IF(I10=0,0,I18/I10)</f>
-        <v>3.74706929812006</v>
+        <v>3.69686543901217</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="B43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="C43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="D43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="E43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="F43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="G43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="H43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
       <c r="I43" s="37" t="n">
         <f aca="false">'Unit economics'!$C$29</f>
-        <v>0.030812</v>
+        <v>0.020406</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="B44" s="18" t="n">
         <f aca="false">IF(B18=0,0,B32/B18)</f>
-        <v>-9.20812257541019</v>
+        <v>-9.18231610059486</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">IF(C18=0,0,C32/C18)</f>
-        <v>-1.26733577027978</v>
+        <v>-1.20117294278551</v>
       </c>
       <c r="D44" s="18" t="n">
         <f aca="false">IF(D18=0,0,D32/D18)</f>
-        <v>-0.254955353884803</v>
+        <v>-0.183552662953617</v>
       </c>
       <c r="E44" s="18" t="n">
         <f aca="false">IF(E18=0,0,E32/E18)</f>
-        <v>0.148348616114995</v>
+        <v>0.225553011185575</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">IF(F18=0,0,F32/F18)</f>
-        <v>0.467697687840558</v>
+        <v>0.544488001707182</v>
       </c>
       <c r="G44" s="18" t="n">
         <f aca="false">IF(G18=0,0,G32/G18)</f>
-        <v>0.597399711135568</v>
+        <v>0.680215252266776</v>
       </c>
       <c r="H44" s="18" t="n">
         <f aca="false">IF(H18=0,0,H32/H18)</f>
-        <v>0.626954980405748</v>
+        <v>0.70963619201296</v>
       </c>
       <c r="I44" s="18" t="n">
         <f aca="false">IF(I18=0,0,I32/I18)</f>
-        <v>0.698330037527575</v>
+        <v>0.780980869360014</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11906,7 +12182,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -11919,44 +12195,44 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="B47" s="37" t="n">
         <f aca="false">B8*'Unit economics'!$Q$11+B9*'Unit economics'!$Q$12</f>
-        <v>15.609</v>
+        <v>15.122545515</v>
       </c>
       <c r="C47" s="37" t="n">
         <f aca="false">C8*'Unit economics'!$Q$11+C9*'Unit economics'!$Q$12</f>
-        <v>73.05012</v>
+        <v>70.812429369</v>
       </c>
       <c r="D47" s="37" t="n">
         <f aca="false">D8*'Unit economics'!$Q$11+D9*'Unit economics'!$Q$12</f>
-        <v>143.6028</v>
+        <v>139.224709635</v>
       </c>
       <c r="E47" s="37" t="n">
         <f aca="false">E8*'Unit economics'!$Q$11+E9*'Unit economics'!$Q$12</f>
-        <v>360.25572</v>
+        <v>349.261848639</v>
       </c>
       <c r="F47" s="37" t="n">
         <f aca="false">F8*'Unit economics'!$Q$11+F9*'Unit economics'!$Q$12</f>
-        <v>718.014</v>
+        <v>696.123548175</v>
       </c>
       <c r="G47" s="37" t="n">
         <f aca="false">G8*'Unit economics'!$Q$11+G9*'Unit economics'!$Q$12</f>
-        <v>1436.028</v>
+        <v>1392.24709635</v>
       </c>
       <c r="H47" s="37" t="n">
         <f aca="false">H8*'Unit economics'!$Q$11+H9*'Unit economics'!$Q$12</f>
-        <v>3590.07</v>
+        <v>3480.617740875</v>
       </c>
       <c r="I47" s="37" t="n">
         <f aca="false">I8*'Unit economics'!$Q$11+I9*'Unit economics'!$Q$12</f>
-        <v>7180.14</v>
+        <v>6961.23548175</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="B48" s="37" t="n">
         <f aca="false">B7*Assumptions!$B$50*Assumptions!$B$6*(1+Assumptions!$B$8)</f>
@@ -11993,39 +12269,39 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="B49" s="43" t="n">
         <f aca="false">B18-(B47+B48+B27+B28)</f>
-        <v>-255.424563627666</v>
+        <v>-253.179122152214</v>
       </c>
       <c r="C49" s="43" t="n">
         <f aca="false">C18-(C47+C48+C27+C28)</f>
-        <v>-345.216770691438</v>
+        <v>-342.427737502591</v>
       </c>
       <c r="D49" s="43" t="n">
         <f aca="false">D18-(D47+D48+D27+D28)</f>
-        <v>-458.632851537116</v>
+        <v>-455.192672253628</v>
       </c>
       <c r="E49" s="43" t="n">
         <f aca="false">E18-(E47+E48+E27+E28)</f>
-        <v>-922.696341521041</v>
+        <v>-914.067549765219</v>
       </c>
       <c r="F49" s="43" t="n">
         <f aca="false">F18-(F47+F48+F27+F28)</f>
-        <v>-1488.01322544095</v>
+        <v>-1476.01532902351</v>
       </c>
       <c r="G49" s="43" t="n">
         <f aca="false">G18-(G47+G48+G27+G28)</f>
-        <v>-2786.06233603397</v>
+        <v>-2764.69055489331</v>
       </c>
       <c r="H49" s="43" t="n">
         <f aca="false">H18-(H47+H48+H27+H28)</f>
-        <v>-6811.95903120723</v>
+        <v>-6761.13107835558</v>
       </c>
       <c r="I49" s="43" t="n">
         <f aca="false">I18-(I47+I48+I27+I28)</f>
-        <v>-12890.2811301698</v>
+        <v>-12799.0312244665</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12041,7 +12317,7 @@
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="40" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="B51" s="40"/>
       <c r="C51" s="40"/>
@@ -12054,7 +12330,7 @@
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="40" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="B52" s="40"/>
       <c r="C52" s="40"/>
@@ -12067,7 +12343,7 @@
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="40" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="B53" s="40"/>
       <c r="C53" s="40"/>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -832,7 +832,7 @@
     <t xml:space="preserve">Max monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Founder prices are rounded UP to a .99 store price point, so a monthly discount can land under 25% (Pro €3.99 is −20%). In-app a founder year can lose on a learner who maxes every AI allowance; the cohort is closed (accounts created before sales open), so the loss is bounded: below.</t>
+    <t xml:space="preserve">Founder prices are rounded UP to a .99 store price point: Pro monthly €3.99 is −20% (owner's choice, 27 Oct 2026). In-app a founder year can lose on a learner who maxes every AI allowance; the cohort is closed (accounts created before sales open), so the loss is bounded: below.</t>
   </si>
   <si>
     <t xml:space="preserve">Founder rules to write: who qualifies (an account created before sales open), the month of Max (from when), the discount on the first year only, then the regular price with a reminder 30 days before renewal.</t>
@@ -874,7 +874,7 @@
     <t xml:space="preserve">Due review on Pro and Max (credits)</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice exercise (average of the prices below)</t>
+    <t xml:space="preserve">Practice: average price of one unit (sentence, text, scenario) below</t>
   </si>
   <si>
     <t xml:space="preserve">Due reviews a day of a steady Pro learner (for the comparison below)</t>
@@ -991,7 +991,7 @@
     <t xml:space="preserve">A due review: 1 on Free, free on Pro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reading (one exercise)</t>
+    <t xml:space="preserve">Reading (one sentence)</t>
   </si>
   <si>
     <t xml:space="preserve">Comprehension (one text)</t>
@@ -1000,16 +1000,16 @@
     <t xml:space="preserve">From the hand-written texts; no new text is generated.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dictation (one exercise)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Translation (one exercise)</t>
+    <t xml:space="preserve">Dictation (one sentence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translation (one sentence)</t>
   </si>
   <si>
     <t xml:space="preserve">Past the AI cap, graded by the learner.</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition (one exercise)</t>
+    <t xml:space="preserve">Composition (one sentence)</t>
   </si>
   <si>
     <t xml:space="preserve">Past the AI cap, without the tutor.</t>
@@ -1036,13 +1036,13 @@
     <t xml:space="preserve">Duel with anyone else</t>
   </si>
   <si>
-    <t xml:space="preserve">Score free; details and corrections in credits (price to set).</t>
+    <t xml:space="preserve">Score free; details and corrections: 1 credit.</t>
   </si>
   <si>
     <t xml:space="preserve">Solo game</t>
   </si>
   <si>
-    <t xml:space="preserve">Price to set (end of November 2026).</t>
+    <t xml:space="preserve">Depends on the game (end of November 2026).</t>
   </si>
   <si>
     <t xml:space="preserve">AI worst case: a user who uses every AI allowance to the full, every day</t>
@@ -2146,7 +2146,7 @@
     <t xml:space="preserve">Practice modes</t>
   </si>
   <si>
-    <t xml:space="preserve">Reading 1, comprehension 2, dictation 1, translation 1, composition 1, conversation 2; free inside a mission</t>
+    <t xml:space="preserve">Per sentence: reading, dictation, translation, composition 1. Per text: comprehension 2. Per scenario: conversation 2. Free inside a mission</t>
   </si>
   <si>
     <t xml:space="preserve">Pass only; practice never spends credits.</t>
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">PvP: async duels, real time between friends, friends list</t>
   </si>
   <si>
-    <t xml:space="preserve">With a friend free, others 2 credits; score free, corrections in credits</t>
+    <t xml:space="preserve">With a friend free, others 2 credits; score free, corrections 1 credit</t>
   </si>
   <si>
     <t xml:space="preserve">Beta this week.</t>
@@ -3268,11 +3268,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="97545314"/>
-        <c:axId val="63858619"/>
+        <c:axId val="40595436"/>
+        <c:axId val="7176966"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97545314"/>
+        <c:axId val="40595436"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3338,7 +3338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63858619"/>
+        <c:crossAx val="7176966"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3346,7 +3346,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63858619"/>
+        <c:axId val="7176966"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3422,7 +3422,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97545314"/>
+        <c:crossAx val="40595436"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -523,7 +523,7 @@
     <t xml:space="preserve">MAU</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner, 26 Oct 2026: about 100 sign-ups, 20–30 active.</t>
+    <t xml:space="preserve">Database, 27 Oct 2026: learners active on 2 days or more in the last 30 (181 on at least one day, 21 on 3 or more). MAU here and in every sheet means that: a learner seen once is not a learner yet.</t>
   </si>
   <si>
     <t xml:space="preserve">Sales open (end of early access)</t>
@@ -3268,11 +3268,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40595436"/>
-        <c:axId val="7176966"/>
+        <c:axId val="53878338"/>
+        <c:axId val="60884359"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40595436"/>
+        <c:axId val="53878338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3338,7 +3338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7176966"/>
+        <c:crossAx val="60884359"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3346,7 +3346,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7176966"/>
+        <c:axId val="60884359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3422,7 +3422,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40595436"/>
+        <c:crossAx val="53878338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B41" s="15" t="n">
         <f aca="false">Assumptions!$B$59</f>
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">IF(OR(B41=0,NOT(ISNUMBER(B42))),0,B42/B41)</f>
-        <v>53.32</v>
+        <v>38.0857142857143</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B45" s="18" t="n">
         <f aca="false">IF(OR(B41=0,B44=0,NOT(ISNUMBER(B42))),0,(B42/B41)^(1/B44)-1)</f>
-        <v>1.18342833104302</v>
+        <v>1.04381358016159</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="B46" s="19" t="n">
         <f aca="true">IF(B45=0,0,B41*(1+B45)^(MAX(0,DATE(2026,12,31)-TODAY())/30.44))</f>
-        <v>132.470673737166</v>
+        <v>161.052800839913</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B47" s="19" t="n">
         <f aca="true">IF(B45=0,0,B41*(1+B45)^(MAX(0,Assumptions!$B$60-TODAY())/30.44))</f>
-        <v>34.8960247260582</v>
+        <v>47.4950218571389</v>
       </c>
     </row>
   </sheetData>
@@ -5698,7 +5698,7 @@
         <v>162</v>
       </c>
       <c r="B59" s="31" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>163</v>

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -487,7 +487,7 @@
     <t xml:space="preserve">% of Pro</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro learners who run past their 120 a day. Max never buys (unlimited, shop hidden).</t>
+    <t xml:space="preserve">Pro learners who run past their 180 a day. Max never buys (unlimited, shop hidden).</t>
   </si>
   <si>
     <t xml:space="preserve">Credit packs: packs bought per buyer per month</t>
@@ -973,7 +973,7 @@
     <t xml:space="preserve">Bought and earned credits never expire (owner's decision) and survive a change of plan. They never raise a plan's AI caps. The shop is hidden from Max (unlimited).</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposal for the missions' 65 a day: three daily missions of 15 and a bonus of 10 for all three (55), and weekly missions worth about 70 (10 a day). A practice exercise asked by a mission costs nothing.</t>
+    <t xml:space="preserve">Proposal for the missions' 35 a day: three daily missions of 8 and a bonus of 6 for all three (30), and weekly missions worth about 35 (5 a day). A practice exercise asked by a mission costs nothing.</t>
   </si>
   <si>
     <t xml:space="preserve">What a credit buys (owner's decisions, 27 Oct 2026). Max: everything included; inside a mission: free</t>
@@ -2083,10 +2083,10 @@
     <t xml:space="preserve">Credit refill</t>
   </si>
   <si>
-    <t xml:space="preserve">60 a day; the refill stops at 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120 a day; the refill stops at 200</t>
+    <t xml:space="preserve">90 a day; the refill stops at 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 a day; the refill stops at 250</t>
   </si>
   <si>
     <t xml:space="preserve">Unlimited</t>
@@ -3268,11 +3268,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53878338"/>
-        <c:axId val="60884359"/>
+        <c:axId val="43151916"/>
+        <c:axId val="11856945"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53878338"/>
+        <c:axId val="43151916"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3338,7 +3338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60884359"/>
+        <c:crossAx val="11856945"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3346,7 +3346,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60884359"/>
+        <c:axId val="11856945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3422,7 +3422,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53878338"/>
+        <c:crossAx val="43151916"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6841,7 +6841,7 @@
         <v>275</v>
       </c>
       <c r="B5" s="31" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6849,7 +6849,7 @@
         <v>276</v>
       </c>
       <c r="B6" s="31" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6857,7 +6857,7 @@
         <v>277</v>
       </c>
       <c r="B7" s="31" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6865,7 +6865,7 @@
         <v>278</v>
       </c>
       <c r="B8" s="31" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">(B7-B5)*30</f>
-        <v>1800</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">B25+B26</f>
-        <v>3600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="B28" s="37" t="n">
         <f aca="false">B27*MIN(D16:D19)/100</f>
-        <v>27.6646153846154</v>
+        <v>34.5807692307692</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B29" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$10=0,0,B28/Assumptions!$B$10)</f>
-        <v>5.54401109912132</v>
+        <v>6.93001387390165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B31" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$10=0,0,B28/(1+B30)/Assumptions!$B$10)</f>
-        <v>3.69600739941421</v>
+        <v>4.62000924926777</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">B13-B5</f>
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/business/tsuji-costs.xlsx
+++ b/docs/business/tsuji-costs.xlsx
@@ -17,7 +17,8 @@
     <sheet name="Fixed costs" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Unit economics" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Projection" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Offer review" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Paid acquisition" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Offer review" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="784">
   <si>
     <t xml:space="preserve">Tsuji — cost overview</t>
   </si>
@@ -1924,6 +1925,171 @@
   </si>
   <si>
     <t xml:space="preserve">Steady-state snapshot: churn and growth over time are not modelled. The founder discount applies to the share of annual payers set in Assumptions; trials are costed in 'Unit economics'. Income tax is not included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid acquisition: buy a core of committed learners fast, then let them bring the rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = input · every cost per sign-up is an assumption until the December test measures it · a sign-up = a new account or guest; engaged = studies on 2 days or more in its first 30; core = still studying at day 30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channels (assumptions to replace with the test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per sign-up (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-up → engaged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engaged → core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok Spark Ads (best organic videos boosted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source asked at sign-up + campaign window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pixel, no SDK: optimised on views and link clicks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Ads (search results)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple's AdServices attribution (no ATT, no third party)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppTweak 2025: median education CPI in the US $2.91.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google App campaigns (Android)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Play install referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53% of early-access learners are on Android.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micro-influencers (10k–100k, FR and EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A creator code (the referral code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid post marked as advertising (French law of June 2023).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram Reels boost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source asked at sign-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off by default: Meta education installs are dear in Europe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured in early access: sign-up → engaged 17.5% (35 of 200). The test must beat it, or the money buys visitors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What one engaged learner is worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of engaged learners who pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin of a payer per month (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months a payer stays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engaged referees each engaged learner brings, over its life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of one engaged learner, direct (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">… with the learners it refers (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target: cost per engaged learner (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop-loss: a channel above this multiple of the target, two weeks running, is cut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget by month (€): test, scale to the target, then halve once organic and referrals carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dec 2026 (test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the budget buys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engaged learners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core learners (still studying at day 30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per engaged learner (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per core learner (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of those engaged learners, with referrals (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net: value minus spend (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within target?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engaged learners bought by the end of March (toward 1,333 active)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid acquisition does not pay for itself in revenue: an engaged learner is worth about €2 with its referrals and costs about €5. It buys speed: a core that refers, reviews the app and fills the leaderboard and the library while the organic channels grow. Cut it when organic and referral sign-ups pass 60% of the total.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No advertising pixel or SDK (privacy promise, docs/adr/0012 and 0022): each channel is measured in aggregate, by its own console, Apple's AdServices or the Play install referrer, the creator's code, and a closed 'source' value asked at sign-up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix activation first: at 17.5% sign-up → engaged, every euro buys mostly visitors. Account after the first ride and a reliable boot come before the first euro.</t>
   </si>
   <si>
     <t xml:space="preserve">The offer as decided (26 Oct 2026), compared with the code today</t>
@@ -2585,7 +2751,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2867,6 +3033,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3268,11 +3450,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="43151916"/>
-        <c:axId val="11856945"/>
+        <c:axId val="59416394"/>
+        <c:axId val="55413498"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43151916"/>
+        <c:axId val="59416394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3338,7 +3520,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11856945"/>
+        <c:crossAx val="55413498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3346,7 +3528,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11856945"/>
+        <c:axId val="55413498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3422,7 +3604,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43151916"/>
+        <c:crossAx val="59416394"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4303,6 +4485,824 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="44" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="44" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B14" s="61" t="n">
+        <f aca="false">Assumptions!$B$15+Assumptions!$B$16</f>
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <f aca="false">'Unit economics'!$O$13</f>
+        <v>2.87287661877851</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B16" s="71" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B18" s="37" t="n">
+        <f aca="false">B14*B15*B16</f>
+        <v>1.58008214032818</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B19" s="37" t="n">
+        <f aca="false">B18*(1+B17)</f>
+        <v>2.05410678242664</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B21" s="46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="60" t="str">
+        <f aca="false">A6</f>
+        <v>TikTok Spark Ads (best organic videos boosted)</v>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="72" t="n">
+        <f aca="false">SUM(B25:H25)</f>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="60" t="str">
+        <f aca="false">A7</f>
+        <v>Apple Ads (search results)</v>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I26" s="72" t="n">
+        <f aca="false">SUM(B26:H26)</f>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="60" t="str">
+        <f aca="false">A8</f>
+        <v>Google App campaigns (Android)</v>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" s="72" t="n">
+        <f aca="false">SUM(B27:H27)</f>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="60" t="str">
+        <f aca="false">A9</f>
+        <v>Micro-influencers (10k–100k, FR and EN)</v>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="72" t="n">
+        <f aca="false">SUM(B28:H28)</f>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="60" t="str">
+        <f aca="false">A10</f>
+        <v>Instagram Reels boost</v>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="72" t="n">
+        <f aca="false">SUM(B29:H29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="B30" s="73" t="n">
+        <f aca="false">SUM(B25:B29)</f>
+        <v>400</v>
+      </c>
+      <c r="C30" s="73" t="n">
+        <f aca="false">SUM(C25:C29)</f>
+        <v>700</v>
+      </c>
+      <c r="D30" s="73" t="n">
+        <f aca="false">SUM(D25:D29)</f>
+        <v>700</v>
+      </c>
+      <c r="E30" s="73" t="n">
+        <f aca="false">SUM(E25:E29)</f>
+        <v>700</v>
+      </c>
+      <c r="F30" s="73" t="n">
+        <f aca="false">SUM(F25:F29)</f>
+        <v>300</v>
+      </c>
+      <c r="G30" s="73" t="n">
+        <f aca="false">SUM(G25:G29)</f>
+        <v>200</v>
+      </c>
+      <c r="H30" s="73" t="n">
+        <f aca="false">SUM(H25:H29)</f>
+        <v>125</v>
+      </c>
+      <c r="I30" s="73" t="n">
+        <f aca="false">SUM(I25:I29)</f>
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>657</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(B25:B29/$B$6:$B$10)</f>
+        <v>297.5</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(C25:C29/$B$6:$B$10)</f>
+        <v>535</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(D25:D29/$B$6:$B$10)</f>
+        <v>535</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(E25:E29/$B$6:$B$10)</f>
+        <v>535</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(F25:F29/$B$6:$B$10)</f>
+        <v>217.5</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(G25:G29/$B$6:$B$10)</f>
+        <v>145</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <f aca="false">SUMPRODUCT(H25:H29/$B$6:$B$10)</f>
+        <v>82.5</v>
+      </c>
+      <c r="I33" s="69" t="n">
+        <f aca="false">SUM(B33:H33)</f>
+        <v>2347.5</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(B25:B29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>70.5</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(C25:C29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>123</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(D25:D29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>123</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(E25:E29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>123</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(F25:F29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>46.5</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(G25:G29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>31</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <f aca="false">SUMPRODUCT(H25:H29/$B$6:$B$10*$C$6:$C$10)</f>
+        <v>18.5</v>
+      </c>
+      <c r="I34" s="69" t="n">
+        <f aca="false">SUM(B34:H34)</f>
+        <v>535.5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="B35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(B25:B29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>29.85</v>
+      </c>
+      <c r="C35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(C25:C29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>51.6</v>
+      </c>
+      <c r="D35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(D25:D29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>51.6</v>
+      </c>
+      <c r="E35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(E25:E29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>51.6</v>
+      </c>
+      <c r="F35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(F25:F29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>19.05</v>
+      </c>
+      <c r="G35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(G25:G29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>12.7</v>
+      </c>
+      <c r="H35" s="69" t="n">
+        <f aca="false">SUMPRODUCT(H25:H29/$B$6:$B$10*$C$6:$C$10*$D$6:$D$10)</f>
+        <v>7.7</v>
+      </c>
+      <c r="I35" s="69" t="n">
+        <f aca="false">SUM(B35:H35)</f>
+        <v>224.1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B36" s="37" t="n">
+        <f aca="false">IF(B34=0,0,B30/B34)</f>
+        <v>5.67375886524823</v>
+      </c>
+      <c r="C36" s="37" t="n">
+        <f aca="false">IF(C34=0,0,C30/C34)</f>
+        <v>5.69105691056911</v>
+      </c>
+      <c r="D36" s="37" t="n">
+        <f aca="false">IF(D34=0,0,D30/D34)</f>
+        <v>5.69105691056911</v>
+      </c>
+      <c r="E36" s="37" t="n">
+        <f aca="false">IF(E34=0,0,E30/E34)</f>
+        <v>5.69105691056911</v>
+      </c>
+      <c r="F36" s="37" t="n">
+        <f aca="false">IF(F34=0,0,F30/F34)</f>
+        <v>6.45161290322581</v>
+      </c>
+      <c r="G36" s="37" t="n">
+        <f aca="false">IF(G34=0,0,G30/G34)</f>
+        <v>6.45161290322581</v>
+      </c>
+      <c r="H36" s="37" t="n">
+        <f aca="false">IF(H34=0,0,H30/H34)</f>
+        <v>6.75675675675676</v>
+      </c>
+      <c r="I36" s="37" t="n">
+        <f aca="false">IF(I34=0,0,I30/I34)</f>
+        <v>5.83566760037348</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B37" s="37" t="n">
+        <f aca="false">IF(B35=0,0,B30/B35)</f>
+        <v>13.4003350083752</v>
+      </c>
+      <c r="C37" s="37" t="n">
+        <f aca="false">IF(C35=0,0,C30/C35)</f>
+        <v>13.5658914728682</v>
+      </c>
+      <c r="D37" s="37" t="n">
+        <f aca="false">IF(D35=0,0,D30/D35)</f>
+        <v>13.5658914728682</v>
+      </c>
+      <c r="E37" s="37" t="n">
+        <f aca="false">IF(E35=0,0,E30/E35)</f>
+        <v>13.5658914728682</v>
+      </c>
+      <c r="F37" s="37" t="n">
+        <f aca="false">IF(F35=0,0,F30/F35)</f>
+        <v>15.748031496063</v>
+      </c>
+      <c r="G37" s="37" t="n">
+        <f aca="false">IF(G35=0,0,G30/G35)</f>
+        <v>15.748031496063</v>
+      </c>
+      <c r="H37" s="37" t="n">
+        <f aca="false">IF(H35=0,0,H30/H35)</f>
+        <v>16.2337662337662</v>
+      </c>
+      <c r="I37" s="37" t="n">
+        <f aca="false">IF(I35=0,0,I30/I35)</f>
+        <v>13.9446675591254</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B38" s="74" t="n">
+        <f aca="false">B34*$B$19</f>
+        <v>144.814528161078</v>
+      </c>
+      <c r="C38" s="74" t="n">
+        <f aca="false">C34*$B$19</f>
+        <v>252.655134238476</v>
+      </c>
+      <c r="D38" s="74" t="n">
+        <f aca="false">D34*$B$19</f>
+        <v>252.655134238476</v>
+      </c>
+      <c r="E38" s="74" t="n">
+        <f aca="false">E34*$B$19</f>
+        <v>252.655134238476</v>
+      </c>
+      <c r="F38" s="74" t="n">
+        <f aca="false">F34*$B$19</f>
+        <v>95.5159653828386</v>
+      </c>
+      <c r="G38" s="74" t="n">
+        <f aca="false">G34*$B$19</f>
+        <v>63.6773102552258</v>
+      </c>
+      <c r="H38" s="74" t="n">
+        <f aca="false">H34*$B$19</f>
+        <v>38.0009754748928</v>
+      </c>
+      <c r="I38" s="72" t="n">
+        <f aca="false">SUM(B38:H38)</f>
+        <v>1099.97418198946</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="B39" s="72" t="n">
+        <f aca="false">B38-B30</f>
+        <v>-255.185471838922</v>
+      </c>
+      <c r="C39" s="72" t="n">
+        <f aca="false">C38-C30</f>
+        <v>-447.344865761524</v>
+      </c>
+      <c r="D39" s="72" t="n">
+        <f aca="false">D38-D30</f>
+        <v>-447.344865761524</v>
+      </c>
+      <c r="E39" s="72" t="n">
+        <f aca="false">E38-E30</f>
+        <v>-447.344865761524</v>
+      </c>
+      <c r="F39" s="72" t="n">
+        <f aca="false">F38-F30</f>
+        <v>-204.484034617161</v>
+      </c>
+      <c r="G39" s="72" t="n">
+        <f aca="false">G38-G30</f>
+        <v>-136.322689744774</v>
+      </c>
+      <c r="H39" s="72" t="n">
+        <f aca="false">H38-H30</f>
+        <v>-86.9990245251072</v>
+      </c>
+      <c r="I39" s="72" t="n">
+        <f aca="false">SUM(B39:H39)</f>
+        <v>-2025.02581801054</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="I40" s="8" t="str">
+        <f aca="false">IF(I36&lt;=$B$20,"yes","NO: fix activation before spending more")</f>
+        <v>NO: fix activation before spending more</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="I41" s="69" t="n">
+        <f aca="false">SUM(B34:E34)</f>
+        <v>439.5</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="40" t="s">
+        <v>667</v>
+      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+    </row>
+    <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="40" t="s">
+        <v>668</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+    </row>
+    <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="40" t="s">
+        <v>669</v>
+      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A45:I45"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4316,7 +5316,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
@@ -4326,7 +5326,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>616</v>
+        <v>671</v>
       </c>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
@@ -4344,10 +5344,10 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>617</v>
+        <v>672</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>618</v>
+        <v>673</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>188</v>
@@ -4356,175 +5356,175 @@
         <v>191</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>619</v>
+        <v>674</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>620</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
-        <v>621</v>
+      <c r="A5" s="75" t="s">
+        <v>676</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>622</v>
+        <v>677</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>623</v>
+        <v>678</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>624</v>
+        <v>679</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>625</v>
+        <v>680</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>626</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
-        <v>627</v>
+      <c r="A6" s="75" t="s">
+        <v>682</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>629</v>
+        <v>684</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>632</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
-        <v>633</v>
+      <c r="A7" s="75" t="s">
+        <v>688</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>634</v>
+        <v>689</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>635</v>
+        <v>690</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>636</v>
+        <v>691</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>638</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>639</v>
+      <c r="A8" s="75" t="s">
+        <v>694</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>209</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>642</v>
+        <v>697</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>644</v>
+      <c r="A9" s="75" t="s">
+        <v>699</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>618</v>
+        <v>673</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>618</v>
+        <v>673</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>647</v>
+      <c r="A10" s="75" t="s">
+        <v>702</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>650</v>
+        <v>705</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
-        <v>651</v>
+      <c r="A11" s="75" t="s">
+        <v>706</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>652</v>
+        <v>707</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>654</v>
+      <c r="A12" s="75" t="s">
+        <v>709</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>655</v>
+        <v>710</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>658</v>
+      <c r="A13" s="75" t="s">
+        <v>713</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>286</v>
@@ -4533,313 +5533,313 @@
         <v>286</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>660</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>661</v>
+      <c r="A14" s="75" t="s">
+        <v>716</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>662</v>
+        <v>717</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>665</v>
+      <c r="A15" s="75" t="s">
+        <v>720</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>666</v>
+        <v>721</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>666</v>
+        <v>721</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>667</v>
+        <v>722</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>668</v>
+        <v>723</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>669</v>
+        <v>724</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="s">
-        <v>670</v>
+      <c r="A16" s="75" t="s">
+        <v>725</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>672</v>
+        <v>727</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="s">
-        <v>674</v>
+      <c r="A17" s="75" t="s">
+        <v>729</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>675</v>
+        <v>730</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>672</v>
+        <v>727</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>676</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71" t="s">
-        <v>677</v>
+      <c r="A18" s="75" t="s">
+        <v>732</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>678</v>
+        <v>733</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>679</v>
+        <v>734</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>680</v>
+        <v>735</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>681</v>
+        <v>736</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>682</v>
+        <v>737</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
-        <v>683</v>
+      <c r="A19" s="75" t="s">
+        <v>738</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>684</v>
+        <v>739</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>685</v>
+        <v>740</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>686</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71" t="s">
-        <v>687</v>
+      <c r="A20" s="75" t="s">
+        <v>742</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>688</v>
+        <v>743</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>689</v>
+        <v>744</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>691</v>
+        <v>746</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>692</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
-        <v>693</v>
+      <c r="A21" s="75" t="s">
+        <v>748</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>694</v>
+        <v>749</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>696</v>
+        <v>751</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>697</v>
+        <v>752</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>698</v>
+        <v>753</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="s">
-        <v>699</v>
+      <c r="A22" s="75" t="s">
+        <v>754</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>700</v>
+        <v>755</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>700</v>
+        <v>755</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>701</v>
+        <v>756</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>702</v>
+        <v>757</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
-        <v>703</v>
+      <c r="A23" s="75" t="s">
+        <v>758</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>209</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="s">
-        <v>705</v>
+      <c r="A24" s="75" t="s">
+        <v>760</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>706</v>
+        <v>761</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>706</v>
+        <v>761</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>209</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>707</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>708</v>
+      <c r="A25" s="75" t="s">
+        <v>763</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>709</v>
+        <v>764</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>709</v>
+        <v>764</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>710</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71" t="s">
-        <v>711</v>
+      <c r="A26" s="75" t="s">
+        <v>766</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>712</v>
+        <v>767</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>713</v>
+        <v>768</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>714</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71" t="s">
-        <v>715</v>
+      <c r="A27" s="75" t="s">
+        <v>770</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>716</v>
+        <v>771</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>717</v>
+        <v>772</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>718</v>
+        <v>773</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="71" t="s">
-        <v>719</v>
+      <c r="A28" s="75" t="s">
+        <v>774</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>720</v>
+        <v>775</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>720</v>
+        <v>775</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4852,7 +5852,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>721</v>
+        <v>776</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -4865,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>722</v>
+        <v>777</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -4877,7 +5877,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>723</v>
+        <v>778</v>
       </c>
       <c r="C32" s="40"/>
       <c r="D32" s="40"/>
@@ -4889,7 +5889,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>724</v>
+        <v>779</v>
       </c>
       <c r="C33" s="40"/>
       <c r="D33" s="40"/>
@@ -4901,7 +5901,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>725</v>
+        <v>780</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
@@ -4913,7 +5913,7 @@
         <v>5</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>726</v>
+        <v>781</v>
       </c>
       <c r="C35" s="40"/>
       <c r="D35" s="40"/>
@@ -4925,7 +5925,7 @@
         <v>6</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>727</v>
+        <v>782</v>
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -4937,7 +5937,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>728</v>
+        <v>783</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="40"/>
